--- a/outputs/20260331_bond_results_tier2_oas.xlsx
+++ b/outputs/20260331_bond_results_tier2_oas.xlsx
@@ -639,13 +639,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>104.0220754720771</v>
+        <v>105.1154580384535</v>
       </c>
       <c r="C2">
-        <v>103.5224083287196</v>
+        <v>104.5686647903086</v>
       </c>
       <c r="D2">
-        <v>0.4996671433574704</v>
+        <v>0.5467932481448372</v>
       </c>
       <c r="E2" t="s">
         <v>74</v>
@@ -656,13 +656,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>99.75822460369528</v>
+        <v>100.7756175079176</v>
       </c>
       <c r="C3">
-        <v>99.28872582794379</v>
+        <v>100.2619680611294</v>
       </c>
       <c r="D3">
-        <v>0.4694987757514895</v>
+        <v>0.5136494467881789</v>
       </c>
       <c r="E3" t="s">
         <v>75</v>
@@ -673,13 +673,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>108.9681076179426</v>
+        <v>110.1237240644939</v>
       </c>
       <c r="C4">
-        <v>108.4339114056407</v>
+        <v>109.5391284468971</v>
       </c>
       <c r="D4">
-        <v>0.5341962123018789</v>
+        <v>0.5845956175967899</v>
       </c>
       <c r="E4" t="s">
         <v>76</v>
@@ -690,13 +690,13 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>104.7436286973097</v>
+        <v>105.8361185670691</v>
       </c>
       <c r="C5">
-        <v>104.2389848579257</v>
+        <v>105.2839323099615</v>
       </c>
       <c r="D5">
-        <v>0.5046438393840731</v>
+        <v>0.5521862571075928</v>
       </c>
       <c r="E5" t="s">
         <v>77</v>
@@ -707,13 +707,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>102.5744104125446</v>
+        <v>103.6338523418523</v>
       </c>
       <c r="C6">
-        <v>102.08522427061</v>
+        <v>103.0986118874581</v>
       </c>
       <c r="D6">
-        <v>0.4891861419345247</v>
+        <v>0.5352404543941844</v>
       </c>
       <c r="E6" t="s">
         <v>78</v>
@@ -724,13 +724,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>101.0609568484924</v>
+        <v>102.0978097213062</v>
       </c>
       <c r="C7">
-        <v>100.5823420566048</v>
+        <v>101.5741615162282</v>
       </c>
       <c r="D7">
-        <v>0.4786147918876509</v>
+        <v>0.5236482050779472</v>
       </c>
       <c r="E7" t="s">
         <v>79</v>
@@ -741,13 +741,13 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>107.3375682156093</v>
+        <v>108.4692111507591</v>
       </c>
       <c r="C8">
-        <v>106.814593009018</v>
+        <v>107.8969222215455</v>
       </c>
       <c r="D8">
-        <v>0.5229752065913402</v>
+        <v>0.5722889292135989</v>
       </c>
       <c r="E8" t="s">
         <v>80</v>
@@ -758,13 +758,13 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>95.24176320954227</v>
+        <v>96.33882578692447</v>
       </c>
       <c r="C9">
-        <v>94.75621716128023</v>
+        <v>95.8066131153081</v>
       </c>
       <c r="D9">
-        <v>0.4855460482620373</v>
+        <v>0.532212671616378</v>
       </c>
       <c r="E9" t="s">
         <v>74</v>
@@ -775,13 +775,13 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>73.60161094434996</v>
+        <v>74.41890051508943</v>
       </c>
       <c r="C10">
-        <v>73.23525199842599</v>
+        <v>74.01755318519791</v>
       </c>
       <c r="D10">
-        <v>0.3663589459239631</v>
+        <v>0.4013473298915216</v>
       </c>
       <c r="E10" t="s">
         <v>75</v>
@@ -792,13 +792,13 @@
         <v>6</v>
       </c>
       <c r="B11">
-        <v>120.0924900017271</v>
+        <v>121.4764067561591</v>
       </c>
       <c r="C11">
-        <v>125.1786874320714</v>
+        <v>126.6106337531658</v>
       </c>
       <c r="D11">
-        <v>-5.086197430344313</v>
+        <v>-5.13422699700665</v>
       </c>
       <c r="E11" t="s">
         <v>76</v>
@@ -809,13 +809,13 @@
         <v>6</v>
       </c>
       <c r="B12">
-        <v>85.69970363146484</v>
+        <v>86.66783951911705</v>
       </c>
       <c r="C12">
-        <v>85.26575270573331</v>
+        <v>86.19240648072113</v>
       </c>
       <c r="D12">
-        <v>0.433950925731537</v>
+        <v>0.47543303839592</v>
       </c>
       <c r="E12" t="s">
         <v>77</v>
@@ -826,13 +826,13 @@
         <v>6</v>
       </c>
       <c r="B13">
-        <v>99.64356623953029</v>
+        <v>100.7848883549282</v>
       </c>
       <c r="C13">
-        <v>100.4159784230989</v>
+        <v>101.5426466128448</v>
       </c>
       <c r="D13">
-        <v>-0.7724121835686049</v>
+        <v>-0.7577582579165778</v>
       </c>
       <c r="E13" t="s">
         <v>78</v>
@@ -843,13 +843,13 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>90.73125007836276</v>
+        <v>91.77298372210633</v>
       </c>
       <c r="C14">
-        <v>90.37367373926377</v>
+        <v>91.37418439788996</v>
       </c>
       <c r="D14">
-        <v>0.3575763390989977</v>
+        <v>0.3987993242163697</v>
       </c>
       <c r="E14" t="s">
         <v>79</v>
@@ -860,13 +860,13 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <v>99.88971558751128</v>
+        <v>101.0419802309117</v>
       </c>
       <c r="C15">
-        <v>99.37866115528897</v>
+        <v>100.4816687536794</v>
       </c>
       <c r="D15">
-        <v>0.5110544322223092</v>
+        <v>0.5603114772322755</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
@@ -877,13 +877,13 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <v>95.39219293148223</v>
+        <v>96.48932139738542</v>
       </c>
       <c r="C16">
-        <v>94.90666642224389</v>
+        <v>95.95712893635105</v>
       </c>
       <c r="D16">
-        <v>0.4855265092383405</v>
+        <v>0.53219246103437</v>
       </c>
       <c r="E16" t="s">
         <v>74</v>
@@ -894,13 +894,13 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>73.76607035269963</v>
+        <v>74.58361211109931</v>
       </c>
       <c r="C17">
-        <v>73.39959896710236</v>
+        <v>74.18214070742582</v>
       </c>
       <c r="D17">
-        <v>0.366471385597265</v>
+        <v>0.4014714036734972</v>
       </c>
       <c r="E17" t="s">
         <v>75</v>
@@ -911,13 +911,13 @@
         <v>7</v>
       </c>
       <c r="B18">
-        <v>120.1985263816161</v>
+        <v>121.5815482677632</v>
       </c>
       <c r="C18">
-        <v>125.2949588296011</v>
+        <v>126.7265345388706</v>
       </c>
       <c r="D18">
-        <v>-5.096432447984938</v>
+        <v>-5.144986271107427</v>
       </c>
       <c r="E18" t="s">
         <v>76</v>
@@ -928,13 +928,13 @@
         <v>7</v>
       </c>
       <c r="B19">
-        <v>85.86190183107436</v>
+        <v>86.83027664330724</v>
       </c>
       <c r="C19">
-        <v>85.42784441762879</v>
+        <v>86.35472604230277</v>
       </c>
       <c r="D19">
-        <v>0.4340574134455721</v>
+        <v>0.4755506010044712</v>
       </c>
       <c r="E19" t="s">
         <v>77</v>
@@ -945,13 +945,13 @@
         <v>7</v>
       </c>
       <c r="B20">
-        <v>99.77520342056268</v>
+        <v>100.9161303942225</v>
       </c>
       <c r="C20">
-        <v>100.5543078391439</v>
+        <v>101.6808741175448</v>
       </c>
       <c r="D20">
-        <v>-0.7791044185812552</v>
+        <v>-0.7647437233222973</v>
       </c>
       <c r="E20" t="s">
         <v>78</v>
@@ -962,13 +962,13 @@
         <v>7</v>
       </c>
       <c r="B21">
-        <v>90.87950182559403</v>
+        <v>91.92123896861784</v>
       </c>
       <c r="C21">
-        <v>90.52262595777412</v>
+        <v>91.5231710908881</v>
       </c>
       <c r="D21">
-        <v>0.3568758678199089</v>
+        <v>0.3980678777297442</v>
       </c>
       <c r="E21" t="s">
         <v>79</v>
@@ -979,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="B22">
-        <v>100.0418392738597</v>
+        <v>101.1942086782235</v>
       </c>
       <c r="C22">
-        <v>99.53074484986367</v>
+        <v>100.6338532552567</v>
       </c>
       <c r="D22">
-        <v>0.5110944239960133</v>
+        <v>0.5603554229667651</v>
       </c>
       <c r="E22" t="s">
         <v>80</v>
@@ -996,13 +996,13 @@
         <v>8</v>
       </c>
       <c r="B23">
-        <v>95.4748983266237</v>
+        <v>96.57221873968803</v>
       </c>
       <c r="C23">
-        <v>94.98940961954915</v>
+        <v>96.04006018955891</v>
       </c>
       <c r="D23">
-        <v>0.4854887070745519</v>
+        <v>0.5321585501291111</v>
       </c>
       <c r="E23" t="s">
         <v>74</v>
@@ -1013,13 +1013,13 @@
         <v>8</v>
       </c>
       <c r="B24">
-        <v>73.85248296041117</v>
+        <v>74.67028035782489</v>
       </c>
       <c r="C24">
-        <v>73.4858965814559</v>
+        <v>74.26868357078146</v>
       </c>
       <c r="D24">
-        <v>0.3665863789552617</v>
+        <v>0.4015967870434309</v>
       </c>
       <c r="E24" t="s">
         <v>75</v>
@@ -1030,13 +1030,13 @@
         <v>8</v>
       </c>
       <c r="B25">
-        <v>120.2467076086366</v>
+        <v>121.6292294317772</v>
       </c>
       <c r="C25">
-        <v>125.3680393671173</v>
+        <v>126.7996663175015</v>
       </c>
       <c r="D25">
-        <v>-5.121331758480721</v>
+        <v>-5.170436885724286</v>
       </c>
       <c r="E25" t="s">
         <v>76</v>
@@ -1047,13 +1047,13 @@
         <v>8</v>
       </c>
       <c r="B26">
-        <v>85.94925473898182</v>
+        <v>86.9178812304288</v>
       </c>
       <c r="C26">
-        <v>85.51508407170373</v>
+        <v>86.44220720771948</v>
       </c>
       <c r="D26">
-        <v>0.4341706672780958</v>
+        <v>0.4756740227093275</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
@@ -1064,13 +1064,13 @@
         <v>8</v>
       </c>
       <c r="B27">
-        <v>99.84219640821829</v>
+        <v>100.9829966181432</v>
       </c>
       <c r="C27">
-        <v>100.6323493876123</v>
+        <v>101.7590497562514</v>
       </c>
       <c r="D27">
-        <v>-0.7901529793939659</v>
+        <v>-0.7760531381082245</v>
       </c>
       <c r="E27" t="s">
         <v>78</v>
@@ -1081,13 +1081,13 @@
         <v>8</v>
       </c>
       <c r="B28">
-        <v>90.95959069389538</v>
+        <v>92.00148392506469</v>
       </c>
       <c r="C28">
-        <v>90.60369521015001</v>
+        <v>91.60441721058912</v>
       </c>
       <c r="D28">
-        <v>0.3558954837453712</v>
+        <v>0.3970667144755708</v>
       </c>
       <c r="E28" t="s">
         <v>79</v>
@@ -1098,13 +1098,13 @@
         <v>8</v>
       </c>
       <c r="B29">
-        <v>100.1263648505255</v>
+        <v>101.2789406746142</v>
       </c>
       <c r="C29">
-        <v>99.6152129478405</v>
+        <v>100.7185207530573</v>
       </c>
       <c r="D29">
-        <v>0.5111519026850431</v>
+        <v>0.5604199215569281</v>
       </c>
       <c r="E29" t="s">
         <v>80</v>
@@ -1115,13 +1115,13 @@
         <v>9</v>
       </c>
       <c r="B30">
-        <v>102.3359174057807</v>
+        <v>103.3585915459385</v>
       </c>
       <c r="C30">
-        <v>101.8715678703822</v>
+        <v>102.850865491178</v>
       </c>
       <c r="D30">
-        <v>0.4643495353985827</v>
+        <v>0.5077260547604823</v>
       </c>
       <c r="E30" t="s">
         <v>74</v>
@@ -1132,13 +1132,13 @@
         <v>9</v>
       </c>
       <c r="B31">
-        <v>97.71068116704582</v>
+        <v>98.67217376717042</v>
       </c>
       <c r="C31">
-        <v>97.27134861013447</v>
+        <v>98.19186555594742</v>
       </c>
       <c r="D31">
-        <v>0.4393325569113529</v>
+        <v>0.4803082112230044</v>
       </c>
       <c r="E31" t="s">
         <v>75</v>
@@ -1149,13 +1149,13 @@
         <v>9</v>
       </c>
       <c r="B32">
-        <v>107.4317415694553</v>
+        <v>108.5079278613693</v>
       </c>
       <c r="C32">
-        <v>106.9397912681601</v>
+        <v>107.9700190964848</v>
       </c>
       <c r="D32">
-        <v>0.4919503012951765</v>
+        <v>0.53790876488452</v>
       </c>
       <c r="E32" t="s">
         <v>76</v>
@@ -1166,13 +1166,13 @@
         <v>9</v>
       </c>
       <c r="B33">
-        <v>104.0806177245923</v>
+        <v>105.1147402123058</v>
       </c>
       <c r="C33">
-        <v>103.6079623655854</v>
+        <v>104.5979623430945</v>
       </c>
       <c r="D33">
-        <v>0.4726553590068931</v>
+        <v>0.5167778692112819</v>
       </c>
       <c r="E33" t="s">
         <v>77</v>
@@ -1183,13 +1183,13 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>99.76875626505249</v>
+        <v>100.7566712878213</v>
       </c>
       <c r="C34">
-        <v>99.31730223773516</v>
+        <v>100.2630863513158</v>
       </c>
       <c r="D34">
-        <v>0.4514540273173253</v>
+        <v>0.4935849365055418</v>
       </c>
       <c r="E34" t="s">
         <v>78</v>
@@ -1200,13 +1200,13 @@
         <v>9</v>
       </c>
       <c r="B35">
-        <v>98.24468946953559</v>
+        <v>99.21451865798875</v>
       </c>
       <c r="C35">
-        <v>97.80153182466657</v>
+        <v>98.73001612473608</v>
       </c>
       <c r="D35">
-        <v>0.443157644869018</v>
+        <v>0.484502533252666</v>
       </c>
       <c r="E35" t="s">
         <v>79</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B36">
-        <v>106.7622185450956</v>
+        <v>107.82825186966</v>
       </c>
       <c r="C36">
-        <v>106.2749218859146</v>
+        <v>107.2954452711619</v>
       </c>
       <c r="D36">
-        <v>0.48729665918097</v>
+        <v>0.532806598498027</v>
       </c>
       <c r="E36" t="s">
         <v>80</v>
@@ -1234,13 +1234,13 @@
         <v>10</v>
       </c>
       <c r="B37">
-        <v>101.4610213564634</v>
+        <v>102.5136794836702</v>
       </c>
       <c r="C37">
-        <v>100.981680215796</v>
+        <v>101.9893266915487</v>
       </c>
       <c r="D37">
-        <v>0.4793411406674295</v>
+        <v>0.5243527921215758</v>
       </c>
       <c r="E37" t="s">
         <v>74</v>
@@ -1251,13 +1251,13 @@
         <v>10</v>
       </c>
       <c r="B38">
-        <v>96.60324345035491</v>
+        <v>97.58607556933374</v>
       </c>
       <c r="C38">
-        <v>96.15213787108587</v>
+        <v>97.09269585418089</v>
       </c>
       <c r="D38">
-        <v>0.4511055792690399</v>
+        <v>0.4933797151528552</v>
       </c>
       <c r="E38" t="s">
         <v>75</v>
@@ -1268,13 +1268,13 @@
         <v>10</v>
       </c>
       <c r="B39">
-        <v>106.8817729086246</v>
+        <v>107.9937979814371</v>
       </c>
       <c r="C39">
-        <v>106.3709051784696</v>
+        <v>107.4349558064454</v>
       </c>
       <c r="D39">
-        <v>0.5108677301549847</v>
+        <v>0.5588421749916819</v>
       </c>
       <c r="E39" t="s">
         <v>76</v>
@@ -1285,13 +1285,13 @@
         <v>10</v>
       </c>
       <c r="B40">
-        <v>103.0432233245174</v>
+        <v>104.1039995710743</v>
       </c>
       <c r="C40">
-        <v>102.5560996966545</v>
+        <v>103.5711766570884</v>
       </c>
       <c r="D40">
-        <v>0.4871236278629567</v>
+        <v>0.5328229139858536</v>
       </c>
       <c r="E40" t="s">
         <v>77</v>
@@ -1302,13 +1302,13 @@
         <v>10</v>
       </c>
       <c r="B41">
-        <v>99.02706774135959</v>
+        <v>100.0428997105366</v>
       </c>
       <c r="C41">
-        <v>98.5606646098865</v>
+        <v>99.53275462010339</v>
       </c>
       <c r="D41">
-        <v>0.4664031314730863</v>
+        <v>0.5101450904331699</v>
       </c>
       <c r="E41" t="s">
         <v>78</v>
@@ -1319,13 +1319,13 @@
         <v>10</v>
       </c>
       <c r="B42">
-        <v>97.39745734749938</v>
+        <v>98.39268643663493</v>
       </c>
       <c r="C42">
-        <v>96.94058600951793</v>
+        <v>97.89298273526779</v>
       </c>
       <c r="D42">
-        <v>0.456871337981454</v>
+        <v>0.4997037013671388</v>
       </c>
       <c r="E42" t="s">
         <v>79</v>
@@ -1336,13 +1336,13 @@
         <v>10</v>
       </c>
       <c r="B43">
-        <v>105.8979126319512</v>
+        <v>106.9948989913496</v>
       </c>
       <c r="C43">
-        <v>105.3940340768316</v>
+        <v>106.4437218983661</v>
       </c>
       <c r="D43">
-        <v>0.5038785551196128</v>
+        <v>0.551177092983508</v>
       </c>
       <c r="E43" t="s">
         <v>80</v>
@@ -1353,13 +1353,13 @@
         <v>11</v>
       </c>
       <c r="B44">
-        <v>98.37802410907982</v>
+        <v>99.47201795957578</v>
       </c>
       <c r="C44">
-        <v>97.90160175147012</v>
+        <v>98.98672511606186</v>
       </c>
       <c r="D44">
-        <v>0.4764223576096924</v>
+        <v>0.4852928435139177</v>
       </c>
       <c r="E44" t="s">
         <v>74</v>
@@ -1370,13 +1370,13 @@
         <v>11</v>
       </c>
       <c r="B45">
-        <v>83.1397037508717</v>
+        <v>84.08606389061133</v>
       </c>
       <c r="C45">
-        <v>82.71539415243942</v>
+        <v>83.62136958170026</v>
       </c>
       <c r="D45">
-        <v>0.4243095984322878</v>
+        <v>0.4646943089110636</v>
       </c>
       <c r="E45" t="s">
         <v>75</v>
@@ -1387,13 +1387,13 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>105.5243419009312</v>
+        <v>105.9564198308625</v>
       </c>
       <c r="C46">
-        <v>116.2563572272815</v>
+        <v>117.5587202713561</v>
       </c>
       <c r="D46">
-        <v>-10.73201532635029</v>
+        <v>-11.60230044049355</v>
       </c>
       <c r="E46" t="s">
         <v>76</v>
@@ -1404,13 +1404,13 @@
         <v>11</v>
       </c>
       <c r="B47">
-        <v>95.53696126256945</v>
+        <v>96.6312741371715</v>
       </c>
       <c r="C47">
-        <v>95.04693260434723</v>
+        <v>96.09548525965187</v>
       </c>
       <c r="D47">
-        <v>0.4900286582222151</v>
+        <v>0.5357888775196358</v>
       </c>
       <c r="E47" t="s">
         <v>77</v>
@@ -1421,13 +1421,13 @@
         <v>11</v>
       </c>
       <c r="B48">
-        <v>97.62762436528615</v>
+        <v>98.60787786136956</v>
       </c>
       <c r="C48">
-        <v>97.45674776548293</v>
+        <v>98.53944407953507</v>
       </c>
       <c r="D48">
-        <v>0.170876599803222</v>
+        <v>0.06843378183448579</v>
       </c>
       <c r="E48" t="s">
         <v>78</v>
@@ -1438,13 +1438,13 @@
         <v>11</v>
       </c>
       <c r="B49">
-        <v>92.01470863868212</v>
+        <v>93.06883056400432</v>
       </c>
       <c r="C49">
-        <v>91.54395655827831</v>
+        <v>92.55655496171133</v>
       </c>
       <c r="D49">
-        <v>0.4707520804038126</v>
+        <v>0.5122756022929877</v>
       </c>
       <c r="E49" t="s">
         <v>79</v>
@@ -1455,13 +1455,13 @@
         <v>11</v>
       </c>
       <c r="B50">
-        <v>104.3155426591737</v>
+        <v>105.2114526295368</v>
       </c>
       <c r="C50">
-        <v>104.7122435520568</v>
+        <v>105.8751403941589</v>
       </c>
       <c r="D50">
-        <v>-0.3967008928831177</v>
+        <v>-0.6636877646220398</v>
       </c>
       <c r="E50" t="s">
         <v>80</v>
@@ -1472,13 +1472,13 @@
         <v>12</v>
       </c>
       <c r="B51">
-        <v>99.12230890244987</v>
+        <v>100.2030421902598</v>
       </c>
       <c r="C51">
-        <v>98.6439736616594</v>
+        <v>99.72893477108643</v>
       </c>
       <c r="D51">
-        <v>0.4783352407904715</v>
+        <v>0.4741074191733645</v>
       </c>
       <c r="E51" t="s">
         <v>74</v>
@@ -1489,13 +1489,13 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>84.04000023902003</v>
+        <v>84.98867864861865</v>
       </c>
       <c r="C52">
-        <v>83.61463969425702</v>
+        <v>84.52285040838692</v>
       </c>
       <c r="D52">
-        <v>0.4253605447630093</v>
+        <v>0.4658282402317298</v>
       </c>
       <c r="E52" t="s">
         <v>75</v>
@@ -1506,13 +1506,13 @@
         <v>12</v>
       </c>
       <c r="B53">
-        <v>105.6352572156841</v>
+        <v>106.0208574581862</v>
       </c>
       <c r="C53">
-        <v>116.7563717776777</v>
+        <v>118.0550402805115</v>
       </c>
       <c r="D53">
-        <v>-11.12111456199365</v>
+        <v>-12.03418282232523</v>
       </c>
       <c r="E53" t="s">
         <v>76</v>
@@ -1523,13 +1523,13 @@
         <v>12</v>
       </c>
       <c r="B54">
-        <v>96.43207129624504</v>
+        <v>97.52647772084715</v>
       </c>
       <c r="C54">
-        <v>95.94110457889489</v>
+        <v>96.99138558648075</v>
       </c>
       <c r="D54">
-        <v>0.4909667173501475</v>
+        <v>0.5350921343664083</v>
       </c>
       <c r="E54" t="s">
         <v>77</v>
@@ -1540,13 +1540,13 @@
         <v>12</v>
       </c>
       <c r="B55">
-        <v>98.2886822063731</v>
+        <v>99.26934428349855</v>
       </c>
       <c r="C55">
-        <v>98.07878014390903</v>
+        <v>99.15991260575021</v>
       </c>
       <c r="D55">
-        <v>0.2099020624640673</v>
+        <v>0.1094316777483471</v>
       </c>
       <c r="E55" t="s">
         <v>78</v>
@@ -1557,13 +1557,13 @@
         <v>12</v>
       </c>
       <c r="B56">
-        <v>92.72147571103653</v>
+        <v>93.77624340310003</v>
       </c>
       <c r="C56">
-        <v>92.24962514901365</v>
+        <v>93.26186355922471</v>
       </c>
       <c r="D56">
-        <v>0.4718505620228797</v>
+        <v>0.514379843875318</v>
       </c>
       <c r="E56" t="s">
         <v>79</v>
@@ -1574,13 +1574,13 @@
         <v>12</v>
       </c>
       <c r="B57">
-        <v>104.889950818763</v>
+        <v>105.6129302612175</v>
       </c>
       <c r="C57">
-        <v>105.4952384271102</v>
+        <v>106.6582061475558</v>
       </c>
       <c r="D57">
-        <v>-0.6052876083472256</v>
+        <v>-1.045275886338274</v>
       </c>
       <c r="E57" t="s">
         <v>80</v>
@@ -1591,13 +1591,13 @@
         <v>13</v>
       </c>
       <c r="B58">
-        <v>99.20107622377031</v>
+        <v>100.2818482847748</v>
       </c>
       <c r="C58">
-        <v>98.72413520404163</v>
+        <v>99.80917027589152</v>
       </c>
       <c r="D58">
-        <v>0.4769410197286845</v>
+        <v>0.4726780088832925</v>
       </c>
       <c r="E58" t="s">
         <v>74</v>
@@ -1608,13 +1608,13 @@
         <v>13</v>
       </c>
       <c r="B59">
-        <v>84.12900679438403</v>
+        <v>85.07790852614671</v>
       </c>
       <c r="C59">
-        <v>83.7035451156863</v>
+        <v>84.61197101224813</v>
       </c>
       <c r="D59">
-        <v>0.4254616786977294</v>
+        <v>0.4659375138985808</v>
       </c>
       <c r="E59" t="s">
         <v>75</v>
@@ -1625,13 +1625,13 @@
         <v>13</v>
       </c>
       <c r="B60">
-        <v>105.6308709394853</v>
+        <v>106.0108091608466</v>
       </c>
       <c r="C60">
-        <v>116.8228571800388</v>
+        <v>118.1213929373784</v>
       </c>
       <c r="D60">
-        <v>-11.19198624055342</v>
+        <v>-12.11058377653181</v>
       </c>
       <c r="E60" t="s">
         <v>76</v>
@@ -1642,13 +1642,13 @@
         <v>13</v>
       </c>
       <c r="B61">
-        <v>96.52140199757301</v>
+        <v>97.61612122371976</v>
       </c>
       <c r="C61">
-        <v>96.03054564034218</v>
+        <v>97.08101119202739</v>
       </c>
       <c r="D61">
-        <v>0.4908563572308253</v>
+        <v>0.5351100316923691</v>
       </c>
       <c r="E61" t="s">
         <v>77</v>
@@ -1659,13 +1659,13 @@
         <v>13</v>
       </c>
       <c r="B62">
-        <v>98.36340879614363</v>
+        <v>99.34441712855754</v>
       </c>
       <c r="C62">
-        <v>98.15145101364369</v>
+        <v>99.23257605401143</v>
       </c>
       <c r="D62">
-        <v>0.2119577824999368</v>
+        <v>0.1118410745461063</v>
       </c>
       <c r="E62" t="s">
         <v>78</v>
@@ -1676,13 +1676,13 @@
         <v>13</v>
       </c>
       <c r="B63">
-        <v>92.79901016185275</v>
+        <v>93.85396081258612</v>
       </c>
       <c r="C63">
-        <v>92.32703643032779</v>
+        <v>93.33933775209736</v>
       </c>
       <c r="D63">
-        <v>0.4719737315249546</v>
+        <v>0.5146230604887592</v>
       </c>
       <c r="E63" t="s">
         <v>79</v>
@@ -1693,13 +1693,13 @@
         <v>13</v>
       </c>
       <c r="B64">
-        <v>104.9457933993003</v>
+        <v>105.6436172736399</v>
       </c>
       <c r="C64">
-        <v>105.5783755233831</v>
+        <v>106.7414300082584</v>
       </c>
       <c r="D64">
-        <v>-0.632582124082802</v>
+        <v>-1.097812734618543</v>
       </c>
       <c r="E64" t="s">
         <v>80</v>
@@ -1710,13 +1710,13 @@
         <v>14</v>
       </c>
       <c r="B65">
-        <v>95.36380417654928</v>
+        <v>96.4130403796259</v>
       </c>
       <c r="C65">
-        <v>94.88093926035407</v>
+        <v>95.88400757178771</v>
       </c>
       <c r="D65">
-        <v>0.4828649161952114</v>
+        <v>0.5290328078381918</v>
       </c>
       <c r="E65" t="s">
         <v>74</v>
@@ -1727,13 +1727,13 @@
         <v>14</v>
       </c>
       <c r="B66">
-        <v>90.92658473698067</v>
+        <v>91.88225788037744</v>
       </c>
       <c r="C66">
-        <v>90.47829714169127</v>
+        <v>91.39085753694501</v>
       </c>
       <c r="D66">
-        <v>0.4482875952894005</v>
+        <v>0.4914003434324314</v>
       </c>
       <c r="E66" t="s">
         <v>75</v>
@@ -1744,13 +1744,13 @@
         <v>14</v>
       </c>
       <c r="B67">
-        <v>100.7414142239768</v>
+        <v>101.8464154520094</v>
       </c>
       <c r="C67">
-        <v>100.4162669155631</v>
+        <v>101.4818319776218</v>
       </c>
       <c r="D67">
-        <v>0.3251473084137473</v>
+        <v>0.3645834743876577</v>
       </c>
       <c r="E67" t="s">
         <v>76</v>
@@ -1761,13 +1761,13 @@
         <v>14</v>
       </c>
       <c r="B68">
-        <v>94.02628415271447</v>
+        <v>95.03782309835292</v>
       </c>
       <c r="C68">
-        <v>93.55204195403952</v>
+        <v>94.51752006766084</v>
       </c>
       <c r="D68">
-        <v>0.4742421986749434</v>
+        <v>0.5203030306920766</v>
       </c>
       <c r="E68" t="s">
         <v>77</v>
@@ -1778,13 +1778,13 @@
         <v>14</v>
       </c>
       <c r="B69">
-        <v>96.03274406725637</v>
+        <v>97.06086537070478</v>
       </c>
       <c r="C69">
-        <v>95.64902569008426</v>
+        <v>96.63577834372155</v>
       </c>
       <c r="D69">
-        <v>0.3837183771721158</v>
+        <v>0.4250870269832205</v>
       </c>
       <c r="E69" t="s">
         <v>78</v>
@@ -1795,13 +1795,13 @@
         <v>14</v>
       </c>
       <c r="B70">
-        <v>94.1593636018434</v>
+        <v>95.16187901125555</v>
       </c>
       <c r="C70">
-        <v>93.73269219400157</v>
+        <v>94.69086426989995</v>
       </c>
       <c r="D70">
-        <v>0.4266714078418232</v>
+        <v>0.471014741355603</v>
       </c>
       <c r="E70" t="s">
         <v>79</v>
@@ -1812,13 +1812,13 @@
         <v>14</v>
       </c>
       <c r="B71">
-        <v>96.76973017629804</v>
+        <v>97.82631063883619</v>
       </c>
       <c r="C71">
-        <v>96.28928503808982</v>
+        <v>97.29747023324332</v>
       </c>
       <c r="D71">
-        <v>0.4804451382082249</v>
+        <v>0.5288404055928737</v>
       </c>
       <c r="E71" t="s">
         <v>80</v>
@@ -1829,13 +1829,13 @@
         <v>15</v>
       </c>
       <c r="B72">
-        <v>103.5845473344655</v>
+        <v>104.6792180229674</v>
       </c>
       <c r="C72">
-        <v>103.0841040064657</v>
+        <v>104.1315617733029</v>
       </c>
       <c r="D72">
-        <v>0.5004433279998324</v>
+        <v>0.5476562496645272</v>
       </c>
       <c r="E72" t="s">
         <v>74</v>
@@ -1846,13 +1846,13 @@
         <v>15</v>
       </c>
       <c r="B73">
-        <v>99.17944924946046</v>
+        <v>100.1967735217015</v>
       </c>
       <c r="C73">
-        <v>98.70970582749575</v>
+        <v>99.68284429077836</v>
       </c>
       <c r="D73">
-        <v>0.4697434219647079</v>
+        <v>0.5139292309231678</v>
       </c>
       <c r="E73" t="s">
         <v>75</v>
@@ -1863,13 +1863,13 @@
         <v>15</v>
       </c>
       <c r="B74">
-        <v>108.689958440656</v>
+        <v>109.847920061184</v>
       </c>
       <c r="C74">
-        <v>108.1543470909381</v>
+        <v>109.2617634035834</v>
       </c>
       <c r="D74">
-        <v>0.5356113497178825</v>
+        <v>0.5861566576005259</v>
       </c>
       <c r="E74" t="s">
         <v>76</v>
@@ -1880,13 +1880,13 @@
         <v>15</v>
       </c>
       <c r="B75">
-        <v>104.3649871576943</v>
+        <v>105.4585835212837</v>
       </c>
       <c r="C75">
-        <v>103.8595312239289</v>
+        <v>104.9054979941958</v>
       </c>
       <c r="D75">
-        <v>0.5054559337654183</v>
+        <v>0.5530855270879016</v>
       </c>
       <c r="E75" t="s">
         <v>77</v>
@@ -1897,13 +1897,13 @@
         <v>15</v>
       </c>
       <c r="B76">
-        <v>102.053081596357</v>
+        <v>103.113272512789</v>
       </c>
       <c r="C76">
-        <v>101.5632516047279</v>
+        <v>102.5773138891116</v>
       </c>
       <c r="D76">
-        <v>0.4898299916290512</v>
+        <v>0.5359586236773879</v>
       </c>
       <c r="E76" t="s">
         <v>78</v>
@@ -1914,13 +1914,13 @@
         <v>15</v>
       </c>
       <c r="B77">
-        <v>100.491998291222</v>
+        <v>101.5291884804354</v>
       </c>
       <c r="C77">
-        <v>100.0129390823392</v>
+        <v>101.0050405116882</v>
       </c>
       <c r="D77">
-        <v>0.4790592088828021</v>
+        <v>0.5241479687471724</v>
       </c>
       <c r="E77" t="s">
         <v>79</v>
@@ -1931,13 +1931,13 @@
         <v>15</v>
       </c>
       <c r="B78">
-        <v>107.0400172214894</v>
+        <v>108.173438576504</v>
       </c>
       <c r="C78">
-        <v>106.5159032126053</v>
+        <v>107.5998926447876</v>
       </c>
       <c r="D78">
-        <v>0.5241140088841405</v>
+        <v>0.5735459317164526</v>
       </c>
       <c r="E78" t="s">
         <v>80</v>
@@ -1948,13 +1948,13 @@
         <v>16</v>
       </c>
       <c r="B79">
-        <v>105.0201017128036</v>
+        <v>105.9871114113832</v>
       </c>
       <c r="C79">
-        <v>105.5638866098882</v>
+        <v>106.7301024474008</v>
       </c>
       <c r="D79">
-        <v>-0.543784897084592</v>
+        <v>-0.7429910360175853</v>
       </c>
       <c r="E79" t="s">
         <v>74</v>
@@ -1965,13 +1965,13 @@
         <v>16</v>
       </c>
       <c r="B80">
-        <v>88.45662000859446</v>
+        <v>89.45507941066013</v>
       </c>
       <c r="C80">
-        <v>88.00901560984266</v>
+        <v>88.96485605854673</v>
       </c>
       <c r="D80">
-        <v>0.4476043987517926</v>
+        <v>0.4902233521134036</v>
       </c>
       <c r="E80" t="s">
         <v>75</v>
@@ -1982,13 +1982,13 @@
         <v>16</v>
       </c>
       <c r="B81">
-        <v>112.2336541489613</v>
+        <v>113.0402070979181</v>
       </c>
       <c r="C81">
-        <v>127.3050483307837</v>
+        <v>128.7329756152818</v>
       </c>
       <c r="D81">
-        <v>-15.07139418182233</v>
+        <v>-15.69276851736372</v>
       </c>
       <c r="E81" t="s">
         <v>76</v>
@@ -1999,13 +1999,13 @@
         <v>16</v>
       </c>
       <c r="B82">
-        <v>101.6628681944953</v>
+        <v>102.8120788541112</v>
       </c>
       <c r="C82">
-        <v>101.1757580105783</v>
+        <v>102.2851321563011</v>
       </c>
       <c r="D82">
-        <v>0.4871101839169114</v>
+        <v>0.526946697810132</v>
       </c>
       <c r="E82" t="s">
         <v>77</v>
@@ -2016,13 +2016,13 @@
         <v>16</v>
       </c>
       <c r="B83">
-        <v>102.3836136533499</v>
+        <v>103.1703400907149</v>
       </c>
       <c r="C83">
-        <v>106.203093528509</v>
+        <v>107.3811608219766</v>
       </c>
       <c r="D83">
-        <v>-3.819479875159047</v>
+        <v>-4.210820731261663</v>
       </c>
       <c r="E83" t="s">
         <v>78</v>
@@ -2033,13 +2033,13 @@
         <v>16</v>
       </c>
       <c r="B84">
-        <v>98.80037790157094</v>
+        <v>99.75113283694851</v>
       </c>
       <c r="C84">
-        <v>99.1343610507643</v>
+        <v>100.2271598704196</v>
       </c>
       <c r="D84">
-        <v>-0.333983149193358</v>
+        <v>-0.4760270334710981</v>
       </c>
       <c r="E84" t="s">
         <v>79</v>
@@ -2050,13 +2050,13 @@
         <v>16</v>
       </c>
       <c r="B85">
-        <v>110.8671524781013</v>
+        <v>111.8519033653166</v>
       </c>
       <c r="C85">
-        <v>112.4243103786057</v>
+        <v>113.6689412180285</v>
       </c>
       <c r="D85">
-        <v>-1.557157900504322</v>
+        <v>-1.81703785271192</v>
       </c>
       <c r="E85" t="s">
         <v>80</v>
@@ -2067,13 +2067,13 @@
         <v>17</v>
       </c>
       <c r="B86">
-        <v>105.2997184887215</v>
+        <v>106.2485677026022</v>
       </c>
       <c r="C86">
-        <v>105.8687162311271</v>
+        <v>107.0348953260835</v>
       </c>
       <c r="D86">
-        <v>-0.568997742405557</v>
+        <v>-0.7863276234813128</v>
       </c>
       <c r="E86" t="s">
         <v>74</v>
@@ -2084,13 +2084,13 @@
         <v>17</v>
       </c>
       <c r="B87">
-        <v>88.8199133359759</v>
+        <v>89.81922360072706</v>
       </c>
       <c r="C87">
-        <v>88.37192436107166</v>
+        <v>89.32858227599357</v>
       </c>
       <c r="D87">
-        <v>0.4479889749042343</v>
+        <v>0.4906413247334882</v>
       </c>
       <c r="E87" t="s">
         <v>75</v>
@@ -2101,13 +2101,13 @@
         <v>17</v>
       </c>
       <c r="B88">
-        <v>112.345578093828</v>
+        <v>113.1404151410257</v>
       </c>
       <c r="C88">
-        <v>127.5150043712942</v>
+        <v>128.9415537858097</v>
       </c>
       <c r="D88">
-        <v>-15.16942627746614</v>
+        <v>-15.80113864478402</v>
       </c>
       <c r="E88" t="s">
         <v>76</v>
@@ -2118,13 +2118,13 @@
         <v>17</v>
       </c>
       <c r="B89">
-        <v>102.030963044057</v>
+        <v>103.1810006192113</v>
       </c>
       <c r="C89">
-        <v>101.5458343098374</v>
+        <v>102.656000108799</v>
       </c>
       <c r="D89">
-        <v>0.4851287342195434</v>
+        <v>0.5250005104122124</v>
       </c>
       <c r="E89" t="s">
         <v>77</v>
@@ -2135,13 +2135,13 @@
         <v>17</v>
       </c>
       <c r="B90">
-        <v>102.6475343008477</v>
+        <v>103.4253204577601</v>
       </c>
       <c r="C90">
-        <v>106.4513533898272</v>
+        <v>107.6286917562275</v>
       </c>
       <c r="D90">
-        <v>-3.803819088979566</v>
+        <v>-4.203371298467431</v>
       </c>
       <c r="E90" t="s">
         <v>78</v>
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="B91">
-        <v>99.09361224359954</v>
+        <v>100.0407125496528</v>
       </c>
       <c r="C91">
-        <v>99.41687883420246</v>
+        <v>100.5094266800555</v>
       </c>
       <c r="D91">
-        <v>-0.3232665906029268</v>
+        <v>-0.4687141304027165</v>
       </c>
       <c r="E91" t="s">
         <v>79</v>
@@ -2169,13 +2169,13 @@
         <v>17</v>
       </c>
       <c r="B92">
-        <v>111.1015534894571</v>
+        <v>112.0795737279496</v>
       </c>
       <c r="C92">
-        <v>112.7541455366619</v>
+        <v>113.9989852855838</v>
       </c>
       <c r="D92">
-        <v>-1.652592047204777</v>
+        <v>-1.919411557634206</v>
       </c>
       <c r="E92" t="s">
         <v>80</v>
@@ -2186,13 +2186,13 @@
         <v>18</v>
       </c>
       <c r="B93">
-        <v>94.9467735380338</v>
+        <v>95.99301733419716</v>
       </c>
       <c r="C93">
-        <v>94.48106047571562</v>
+        <v>95.49210008689452</v>
       </c>
       <c r="D93">
-        <v>0.4657130623181729</v>
+        <v>0.5009172473026382</v>
       </c>
       <c r="E93" t="s">
         <v>74</v>
@@ -2203,13 +2203,13 @@
         <v>18</v>
       </c>
       <c r="B94">
-        <v>89.88926479152117</v>
+        <v>90.85127446876787</v>
       </c>
       <c r="C94">
-        <v>89.44672955821744</v>
+        <v>90.36898931995047</v>
       </c>
       <c r="D94">
-        <v>0.4425352333037296</v>
+        <v>0.4822851488173967</v>
       </c>
       <c r="E94" t="s">
         <v>75</v>
@@ -2220,13 +2220,13 @@
         <v>18</v>
       </c>
       <c r="B95">
-        <v>100.4778790918704</v>
+        <v>101.4552923253667</v>
       </c>
       <c r="C95">
-        <v>100.5054883678873</v>
+        <v>101.5818090179145</v>
       </c>
       <c r="D95">
-        <v>-0.02760927601684671</v>
+        <v>-0.1265166925477956</v>
       </c>
       <c r="E95" t="s">
         <v>76</v>
@@ -2237,13 +2237,13 @@
         <v>18</v>
       </c>
       <c r="B96">
-        <v>94.95930183622755</v>
+        <v>95.98602088315612</v>
       </c>
       <c r="C96">
-        <v>94.5055044983572</v>
+        <v>95.4961969939945</v>
       </c>
       <c r="D96">
-        <v>0.4537973378703555</v>
+        <v>0.4898238891616131</v>
       </c>
       <c r="E96" t="s">
         <v>77</v>
@@ -2254,13 +2254,13 @@
         <v>18</v>
       </c>
       <c r="B97">
-        <v>93.9997553099243</v>
+        <v>94.99757786837378</v>
       </c>
       <c r="C97">
-        <v>93.67958956515267</v>
+        <v>94.66233223306031</v>
       </c>
       <c r="D97">
-        <v>0.3201657447716286</v>
+        <v>0.3352456353134698</v>
       </c>
       <c r="E97" t="s">
         <v>78</v>
@@ -2271,13 +2271,13 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>92.13770153546812</v>
+        <v>93.12297628217151</v>
       </c>
       <c r="C98">
-        <v>91.74061788260389</v>
+        <v>92.69644388028674</v>
       </c>
       <c r="D98">
-        <v>0.3970836528642394</v>
+        <v>0.4265324018847707</v>
       </c>
       <c r="E98" t="s">
         <v>79</v>
@@ -2288,13 +2288,13 @@
         <v>18</v>
       </c>
       <c r="B99">
-        <v>97.97490954190097</v>
+        <v>99.02555182142072</v>
       </c>
       <c r="C99">
-        <v>97.58154826591135</v>
+        <v>98.61560465369955</v>
       </c>
       <c r="D99">
-        <v>0.3933612759896192</v>
+        <v>0.409947167721171</v>
       </c>
       <c r="E99" t="s">
         <v>80</v>
@@ -2305,13 +2305,13 @@
         <v>19</v>
       </c>
       <c r="B100">
-        <v>102.2121674914168</v>
+        <v>103.1677478726515</v>
       </c>
       <c r="C100">
-        <v>101.7797434945288</v>
+        <v>102.695253375993</v>
       </c>
       <c r="D100">
-        <v>0.4324239968880192</v>
+        <v>0.4724944966584417</v>
       </c>
       <c r="E100" t="s">
         <v>74</v>
@@ -2322,13 +2322,13 @@
         <v>19</v>
       </c>
       <c r="B101">
-        <v>98.09726130693539</v>
+        <v>99.00490235526021</v>
       </c>
       <c r="C101">
-        <v>97.68481066698151</v>
+        <v>98.55426969281932</v>
       </c>
       <c r="D101">
-        <v>0.4124506399538888</v>
+        <v>0.4506326624408956</v>
       </c>
       <c r="E101" t="s">
         <v>75</v>
@@ -2339,13 +2339,13 @@
         <v>19</v>
       </c>
       <c r="B102">
-        <v>106.650113641482</v>
+        <v>107.6489550017925</v>
       </c>
       <c r="C102">
-        <v>106.1961132140083</v>
+        <v>107.1528825299406</v>
       </c>
       <c r="D102">
-        <v>0.4540004274736447</v>
+        <v>0.4960724718518605</v>
       </c>
       <c r="E102" t="s">
         <v>76</v>
@@ -2356,13 +2356,13 @@
         <v>19</v>
       </c>
       <c r="B103">
-        <v>103.9324028748898</v>
+        <v>104.9009806528988</v>
       </c>
       <c r="C103">
-        <v>103.4921941576754</v>
+        <v>104.419994945381</v>
       </c>
       <c r="D103">
-        <v>0.4402087172143609</v>
+        <v>0.4809857075178741</v>
       </c>
       <c r="E103" t="s">
         <v>77</v>
@@ -2373,13 +2373,13 @@
         <v>19</v>
       </c>
       <c r="B104">
-        <v>99.7447011209966</v>
+        <v>100.6709947684854</v>
       </c>
       <c r="C104">
-        <v>99.32374947303508</v>
+        <v>100.2110619903714</v>
       </c>
       <c r="D104">
-        <v>0.4209516479615161</v>
+        <v>0.4599327781140232</v>
       </c>
       <c r="E104" t="s">
         <v>78</v>
@@ -2390,13 +2390,13 @@
         <v>19</v>
       </c>
       <c r="B105">
-        <v>98.41217371330551</v>
+        <v>99.32421824253173</v>
       </c>
       <c r="C105">
-        <v>97.99771367581847</v>
+        <v>98.87138494906144</v>
       </c>
       <c r="D105">
-        <v>0.4144600374870322</v>
+        <v>0.4528332934702917</v>
       </c>
       <c r="E105" t="s">
         <v>79</v>
@@ -2407,13 +2407,13 @@
         <v>19</v>
       </c>
       <c r="B106">
-        <v>106.2728290874808</v>
+        <v>107.2665256187658</v>
       </c>
       <c r="C106">
-        <v>105.8211755963807</v>
+        <v>106.7730231379963</v>
       </c>
       <c r="D106">
-        <v>0.4516534911001173</v>
+        <v>0.4935024807695072</v>
       </c>
       <c r="E106" t="s">
         <v>80</v>
@@ -2424,13 +2424,13 @@
         <v>20</v>
       </c>
       <c r="B107">
-        <v>95.10556353990177</v>
+        <v>96.15102143887775</v>
       </c>
       <c r="C107">
-        <v>94.63933849568024</v>
+        <v>95.65036195558588</v>
       </c>
       <c r="D107">
-        <v>0.466225044221531</v>
+        <v>0.5006594832918694</v>
       </c>
       <c r="E107" t="s">
         <v>74</v>
@@ -2441,13 +2441,13 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>90.11357117947554</v>
+        <v>91.07641818131337</v>
       </c>
       <c r="C108">
-        <v>89.67087189131179</v>
+        <v>90.59371741793285</v>
       </c>
       <c r="D108">
-        <v>0.4426992881637517</v>
+        <v>0.4827007633805209</v>
       </c>
       <c r="E108" t="s">
         <v>75</v>
@@ -2458,13 +2458,13 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>100.5576813518843</v>
+        <v>101.5341203433234</v>
       </c>
       <c r="C109">
-        <v>100.5876986310121</v>
+        <v>101.663546068964</v>
       </c>
       <c r="D109">
-        <v>-0.03001727912784702</v>
+        <v>-0.1294257256405729</v>
       </c>
       <c r="E109" t="s">
         <v>76</v>
@@ -2475,13 +2475,13 @@
         <v>20</v>
       </c>
       <c r="B110">
-        <v>95.11542798090971</v>
+        <v>96.14266735539833</v>
       </c>
       <c r="C110">
-        <v>94.66274603724727</v>
+        <v>95.65373292913468</v>
       </c>
       <c r="D110">
-        <v>0.4526819436624407</v>
+        <v>0.4889344262636541</v>
       </c>
       <c r="E110" t="s">
         <v>77</v>
@@ -2492,13 +2492,13 @@
         <v>20</v>
       </c>
       <c r="B111">
-        <v>94.17647732944415</v>
+        <v>95.17648796355074</v>
       </c>
       <c r="C111">
-        <v>93.84836182785071</v>
+        <v>94.8310900205922</v>
       </c>
       <c r="D111">
-        <v>0.3281155015934445</v>
+        <v>0.3453979429585416</v>
       </c>
       <c r="E111" t="s">
         <v>78</v>
@@ -2509,13 +2509,13 @@
         <v>20</v>
       </c>
       <c r="B112">
-        <v>92.33772608581543</v>
+        <v>93.31834031613288</v>
       </c>
       <c r="C112">
-        <v>91.93532144223001</v>
+        <v>92.89135082283617</v>
       </c>
       <c r="D112">
-        <v>0.4024046435854274</v>
+        <v>0.426989493296702</v>
       </c>
       <c r="E112" t="s">
         <v>79</v>
@@ -2526,13 +2526,13 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>98.09115882103423</v>
+        <v>99.14403369690939</v>
       </c>
       <c r="C113">
-        <v>97.70081834309845</v>
+        <v>98.73489069320345</v>
       </c>
       <c r="D113">
-        <v>0.39034047793578</v>
+        <v>0.4091430037059354</v>
       </c>
       <c r="E113" t="s">
         <v>80</v>
@@ -2543,13 +2543,13 @@
         <v>21</v>
       </c>
       <c r="B114">
-        <v>102.4673755208844</v>
+        <v>103.4179381343352</v>
       </c>
       <c r="C114">
-        <v>102.0373067970155</v>
+        <v>102.9480457889545</v>
       </c>
       <c r="D114">
-        <v>0.4300687238688852</v>
+        <v>0.4698923453806145</v>
       </c>
       <c r="E114" t="s">
         <v>74</v>
@@ -2560,13 +2560,13 @@
         <v>21</v>
       </c>
       <c r="B115">
-        <v>98.47136053354687</v>
+        <v>99.37539006454523</v>
       </c>
       <c r="C115">
-        <v>98.06068752615961</v>
+        <v>98.9267265100824</v>
       </c>
       <c r="D115">
-        <v>0.4106730073872598</v>
+        <v>0.4486635544628257</v>
       </c>
       <c r="E115" t="s">
         <v>75</v>
@@ -2577,13 +2577,13 @@
         <v>21</v>
       </c>
       <c r="B116">
-        <v>106.773583431443</v>
+        <v>107.7661630461954</v>
       </c>
       <c r="C116">
-        <v>106.3225817212942</v>
+        <v>107.2733962174914</v>
       </c>
       <c r="D116">
-        <v>0.4510017101488017</v>
+        <v>0.4927668287039779</v>
       </c>
       <c r="E116" t="s">
         <v>76</v>
@@ -2594,13 +2594,13 @@
         <v>21</v>
       </c>
       <c r="B117">
-        <v>104.1508838208876</v>
+        <v>105.1142758571579</v>
       </c>
       <c r="C117">
-        <v>103.7131783282675</v>
+        <v>104.6360532152212</v>
       </c>
       <c r="D117">
-        <v>0.4377054926200685</v>
+        <v>0.4782226419367106</v>
       </c>
       <c r="E117" t="s">
         <v>77</v>
@@ -2611,13 +2611,13 @@
         <v>21</v>
       </c>
       <c r="B118">
-        <v>100.0582179812261</v>
+        <v>100.980198825307</v>
       </c>
       <c r="C118">
-        <v>99.6393668900951</v>
+        <v>100.5225888173844</v>
       </c>
       <c r="D118">
-        <v>0.4188510911309749</v>
+        <v>0.457610007922554</v>
       </c>
       <c r="E118" t="s">
         <v>78</v>
@@ -2628,13 +2628,13 @@
         <v>21</v>
       </c>
       <c r="B119">
-        <v>98.76512958715539</v>
+        <v>99.67328365417401</v>
       </c>
       <c r="C119">
-        <v>98.35257552693449</v>
+        <v>99.22256013782633</v>
       </c>
       <c r="D119">
-        <v>0.4125540602208986</v>
+        <v>0.4507235163476793</v>
       </c>
       <c r="E119" t="s">
         <v>79</v>
@@ -2645,13 +2645,13 @@
         <v>21</v>
       </c>
       <c r="B120">
-        <v>106.4206563244531</v>
+        <v>107.4084173574916</v>
       </c>
       <c r="C120">
-        <v>105.9718514827224</v>
+        <v>106.918056037689</v>
       </c>
       <c r="D120">
-        <v>0.4488048417306487</v>
+        <v>0.4903613198025596</v>
       </c>
       <c r="E120" t="s">
         <v>80</v>
@@ -2662,13 +2662,13 @@
         <v>22</v>
       </c>
       <c r="B121">
-        <v>102.3774859621691</v>
+        <v>103.3294695682517</v>
       </c>
       <c r="C121">
-        <v>101.9467481406841</v>
+        <v>102.8588378820989</v>
       </c>
       <c r="D121">
-        <v>0.430737821485053</v>
+        <v>0.4706316861528279</v>
       </c>
       <c r="E121" t="s">
         <v>74</v>
@@ -2679,13 +2679,13 @@
         <v>22</v>
       </c>
       <c r="B122">
-        <v>98.34126847799004</v>
+        <v>99.24627537767674</v>
       </c>
       <c r="C122">
-        <v>97.93010920464103</v>
+        <v>98.79707274288057</v>
       </c>
       <c r="D122">
-        <v>0.4111592733490141</v>
+        <v>0.4492026347961655</v>
       </c>
       <c r="E122" t="s">
         <v>75</v>
@@ -2696,13 +2696,13 @@
         <v>22</v>
       </c>
       <c r="B123">
-        <v>106.7280332516302</v>
+        <v>107.7224300452516</v>
       </c>
       <c r="C123">
-        <v>106.2761591653778</v>
+        <v>107.2287017061281</v>
       </c>
       <c r="D123">
-        <v>0.45187408625236</v>
+        <v>0.493728339123507</v>
       </c>
       <c r="E123" t="s">
         <v>76</v>
@@ -2713,13 +2713,13 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>104.0763123581759</v>
+        <v>105.0412050399416</v>
       </c>
       <c r="C124">
-        <v>103.6378800052529</v>
+        <v>104.5621802049236</v>
       </c>
       <c r="D124">
-        <v>0.4384323529230016</v>
+        <v>0.4790248350180519</v>
       </c>
       <c r="E124" t="s">
         <v>77</v>
@@ -2730,13 +2730,13 @@
         <v>22</v>
       </c>
       <c r="B125">
-        <v>99.94568429718623</v>
+        <v>100.8688408926409</v>
       </c>
       <c r="C125">
-        <v>99.52625570715593</v>
+        <v>100.4105918903368</v>
       </c>
       <c r="D125">
-        <v>0.4194285900303072</v>
+        <v>0.4582490023040577</v>
       </c>
       <c r="E125" t="s">
         <v>78</v>
@@ -2747,13 +2747,13 @@
         <v>22</v>
       </c>
       <c r="B126">
-        <v>98.63953628287602</v>
+        <v>99.54873435494861</v>
       </c>
       <c r="C126">
-        <v>98.22646529982602</v>
+        <v>99.0974381262578</v>
       </c>
       <c r="D126">
-        <v>0.4130709830500052</v>
+        <v>0.4512962286908078</v>
       </c>
       <c r="E126" t="s">
         <v>79</v>
@@ -2764,13 +2764,13 @@
         <v>22</v>
       </c>
       <c r="B127">
-        <v>106.3697575595519</v>
+        <v>107.3592556216988</v>
       </c>
       <c r="C127">
-        <v>105.9201171833248</v>
+        <v>106.8679732059513</v>
       </c>
       <c r="D127">
-        <v>0.4496403762271228</v>
+        <v>0.4912824157474915</v>
       </c>
       <c r="E127" t="s">
         <v>80</v>
@@ -2781,13 +2781,13 @@
         <v>23</v>
       </c>
       <c r="B128">
-        <v>104.5278248015921</v>
+        <v>105.3118050047556</v>
       </c>
       <c r="C128">
-        <v>104.1743524480789</v>
+        <v>104.9263155801877</v>
       </c>
       <c r="D128">
-        <v>0.3534723535131974</v>
+        <v>0.3854894245678935</v>
       </c>
       <c r="E128" t="s">
         <v>74</v>
@@ -2798,13 +2798,13 @@
         <v>23</v>
       </c>
       <c r="B129">
-        <v>100.9487715923447</v>
+        <v>101.7046574451652</v>
       </c>
       <c r="C129">
-        <v>100.6074893940462</v>
+        <v>101.3324667088139</v>
       </c>
       <c r="D129">
-        <v>0.341282198298515</v>
+        <v>0.3721907363513282</v>
       </c>
       <c r="E129" t="s">
         <v>75</v>
@@ -2815,13 +2815,13 @@
         <v>23</v>
       </c>
       <c r="B130">
-        <v>108.2728116432682</v>
+        <v>109.0839597999323</v>
       </c>
       <c r="C130">
-        <v>107.906578907909</v>
+        <v>108.684558012022</v>
       </c>
       <c r="D130">
-        <v>0.3662327353591905</v>
+        <v>0.3994017879103211</v>
       </c>
       <c r="E130" t="s">
         <v>76</v>
@@ -2832,13 +2832,13 @@
         <v>23</v>
       </c>
       <c r="B131">
-        <v>106.5080397353246</v>
+        <v>107.3057922915268</v>
       </c>
       <c r="C131">
-        <v>106.1478549565073</v>
+        <v>106.9129865630582</v>
       </c>
       <c r="D131">
-        <v>0.3601847788172705</v>
+        <v>0.3928057284685735</v>
       </c>
       <c r="E131" t="s">
         <v>77</v>
@@ -2849,13 +2849,13 @@
         <v>23</v>
       </c>
       <c r="B132">
-        <v>101.8726996062046</v>
+        <v>102.635631289818</v>
       </c>
       <c r="C132">
-        <v>101.528236312721</v>
+        <v>102.2599711031936</v>
       </c>
       <c r="D132">
-        <v>0.3444632934835141</v>
+        <v>0.3756601866243727</v>
       </c>
       <c r="E132" t="s">
         <v>78</v>
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="B133">
-        <v>100.7643839987419</v>
+        <v>101.5189483502285</v>
       </c>
       <c r="C133">
-        <v>100.4236984948509</v>
+        <v>101.1474082297092</v>
       </c>
       <c r="D133">
-        <v>0.3406855038910237</v>
+        <v>0.3715401205192279</v>
       </c>
       <c r="E133" t="s">
         <v>79</v>
@@ -2883,13 +2883,13 @@
         <v>23</v>
       </c>
       <c r="B134">
-        <v>108.4703717624015</v>
+        <v>109.2829371731832</v>
       </c>
       <c r="C134">
-        <v>108.1034990935441</v>
+        <v>108.8828376201636</v>
       </c>
       <c r="D134">
-        <v>0.3668726688573827</v>
+        <v>0.4000995530195581</v>
       </c>
       <c r="E134" t="s">
         <v>80</v>
@@ -2900,13 +2900,13 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>103.9775159406122</v>
+        <v>105.1284023161301</v>
       </c>
       <c r="C135">
-        <v>103.9169854179734</v>
+        <v>105.0859316020547</v>
       </c>
       <c r="D135">
-        <v>0.06053052263874292</v>
+        <v>0.04247071407533554</v>
       </c>
       <c r="E135" t="s">
         <v>74</v>
@@ -2917,13 +2917,13 @@
         <v>24</v>
       </c>
       <c r="B136">
-        <v>85.09707160301141</v>
+        <v>86.07315641801466</v>
       </c>
       <c r="C136">
-        <v>84.6595215452023</v>
+        <v>85.59386815828965</v>
       </c>
       <c r="D136">
-        <v>0.4375500578091192</v>
+        <v>0.4792882597250099</v>
       </c>
       <c r="E136" t="s">
         <v>75</v>
@@ -2934,13 +2934,13 @@
         <v>24</v>
       </c>
       <c r="B137">
-        <v>116.1393405595133</v>
+        <v>117.2375197086842</v>
       </c>
       <c r="C137">
-        <v>128.5417171389083</v>
+        <v>130.0121963907025</v>
       </c>
       <c r="D137">
-        <v>-12.40237657939502</v>
+        <v>-12.7746766820183</v>
       </c>
       <c r="E137" t="s">
         <v>76</v>
@@ -2951,13 +2951,13 @@
         <v>24</v>
       </c>
       <c r="B138">
-        <v>98.40165252841592</v>
+        <v>99.54048448460627</v>
       </c>
       <c r="C138">
-        <v>97.89384347655248</v>
+        <v>98.98456840194457</v>
       </c>
       <c r="D138">
-        <v>0.5078090518634468</v>
+        <v>0.555916082661696</v>
       </c>
       <c r="E138" t="s">
         <v>77</v>
@@ -2968,13 +2968,13 @@
         <v>24</v>
       </c>
       <c r="B139">
-        <v>102.2639048158162</v>
+        <v>103.2570523397522</v>
       </c>
       <c r="C139">
-        <v>105.945375711794</v>
+        <v>107.1438685146882</v>
       </c>
       <c r="D139">
-        <v>-3.681470895977796</v>
+        <v>-3.886816174936058</v>
       </c>
       <c r="E139" t="s">
         <v>78</v>
@@ -2985,13 +2985,13 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>97.5291043677598</v>
+        <v>98.57022473638658</v>
       </c>
       <c r="C140">
-        <v>97.88464103130707</v>
+        <v>98.98422715667209</v>
       </c>
       <c r="D140">
-        <v>-0.3555366635472694</v>
+        <v>-0.414002420285513</v>
       </c>
       <c r="E140" t="s">
         <v>79</v>
@@ -3002,13 +3002,13 @@
         <v>24</v>
       </c>
       <c r="B141">
-        <v>110.3141169315341</v>
+        <v>111.5356190669388</v>
       </c>
       <c r="C141">
-        <v>110.3323698110944</v>
+        <v>111.5751259715148</v>
       </c>
       <c r="D141">
-        <v>-0.01825287956025079</v>
+        <v>-0.03950690457598682</v>
       </c>
       <c r="E141" t="s">
         <v>80</v>
@@ -3019,13 +3019,13 @@
         <v>25</v>
       </c>
       <c r="B142">
-        <v>104.0220754720771</v>
+        <v>105.1154580384535</v>
       </c>
       <c r="C142">
-        <v>103.5224083287196</v>
+        <v>104.5686647903086</v>
       </c>
       <c r="D142">
-        <v>0.4996671433574704</v>
+        <v>0.5467932481448372</v>
       </c>
       <c r="E142" t="s">
         <v>74</v>
@@ -3036,13 +3036,13 @@
         <v>25</v>
       </c>
       <c r="B143">
-        <v>99.75822460369528</v>
+        <v>100.7756175079176</v>
       </c>
       <c r="C143">
-        <v>99.28872582794379</v>
+        <v>100.2619680611294</v>
       </c>
       <c r="D143">
-        <v>0.4694987757514895</v>
+        <v>0.5136494467881789</v>
       </c>
       <c r="E143" t="s">
         <v>75</v>
@@ -3053,13 +3053,13 @@
         <v>25</v>
       </c>
       <c r="B144">
-        <v>108.9681076179426</v>
+        <v>110.1237240644939</v>
       </c>
       <c r="C144">
-        <v>108.4339114056407</v>
+        <v>109.5391284468971</v>
       </c>
       <c r="D144">
-        <v>0.5341962123018789</v>
+        <v>0.5845956175967899</v>
       </c>
       <c r="E144" t="s">
         <v>76</v>
@@ -3070,13 +3070,13 @@
         <v>25</v>
       </c>
       <c r="B145">
-        <v>104.7436286973097</v>
+        <v>105.8361185670691</v>
       </c>
       <c r="C145">
-        <v>104.2389848579257</v>
+        <v>105.2839323099615</v>
       </c>
       <c r="D145">
-        <v>0.5046438393840731</v>
+        <v>0.5521862571075928</v>
       </c>
       <c r="E145" t="s">
         <v>77</v>
@@ -3087,13 +3087,13 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>102.5744104125446</v>
+        <v>103.6338523418523</v>
       </c>
       <c r="C146">
-        <v>102.08522427061</v>
+        <v>103.0986118874581</v>
       </c>
       <c r="D146">
-        <v>0.4891861419345247</v>
+        <v>0.5352404543941844</v>
       </c>
       <c r="E146" t="s">
         <v>78</v>
@@ -3104,13 +3104,13 @@
         <v>25</v>
       </c>
       <c r="B147">
-        <v>101.0609568484924</v>
+        <v>102.0978097213062</v>
       </c>
       <c r="C147">
-        <v>100.5823420566048</v>
+        <v>101.5741615162282</v>
       </c>
       <c r="D147">
-        <v>0.4786147918876509</v>
+        <v>0.5236482050779472</v>
       </c>
       <c r="E147" t="s">
         <v>79</v>
@@ -3121,13 +3121,13 @@
         <v>25</v>
       </c>
       <c r="B148">
-        <v>107.3375682156093</v>
+        <v>108.4692111507591</v>
       </c>
       <c r="C148">
-        <v>106.814593009018</v>
+        <v>107.8969222215455</v>
       </c>
       <c r="D148">
-        <v>0.5229752065913402</v>
+        <v>0.5722889292135989</v>
       </c>
       <c r="E148" t="s">
         <v>80</v>
@@ -3138,13 +3138,13 @@
         <v>26</v>
       </c>
       <c r="B149">
-        <v>105.4595640321176</v>
+        <v>106.6046380096089</v>
       </c>
       <c r="C149">
-        <v>105.4689032478662</v>
+        <v>106.6393212347798</v>
       </c>
       <c r="D149">
-        <v>-0.009339215748610741</v>
+        <v>-0.03468322517089462</v>
       </c>
       <c r="E149" t="s">
         <v>74</v>
@@ -3155,13 +3155,13 @@
         <v>26</v>
       </c>
       <c r="B150">
-        <v>86.89426811774716</v>
+        <v>87.87556204389158</v>
       </c>
       <c r="C150">
-        <v>86.45437445578507</v>
+        <v>87.39372257400748</v>
       </c>
       <c r="D150">
-        <v>0.4398936619620883</v>
+        <v>0.4818394698840933</v>
       </c>
       <c r="E150" t="s">
         <v>75</v>
@@ -3172,13 +3172,13 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>116.8306367987324</v>
+        <v>117.8917336091301</v>
       </c>
       <c r="C151">
-        <v>129.660567067145</v>
+        <v>131.1264825509882</v>
       </c>
       <c r="D151">
-        <v>-12.82993026841262</v>
+        <v>-13.23474894185804</v>
       </c>
       <c r="E151" t="s">
         <v>76</v>
@@ -3189,13 +3189,13 @@
         <v>26</v>
       </c>
       <c r="B152">
-        <v>100.1939510037527</v>
+        <v>101.3374402158813</v>
       </c>
       <c r="C152">
-        <v>99.68499977657747</v>
+        <v>100.7802347111032</v>
       </c>
       <c r="D152">
-        <v>0.5089512271752596</v>
+        <v>0.5572055047780964</v>
       </c>
       <c r="E152" t="s">
         <v>77</v>
@@ -3206,13 +3206,13 @@
         <v>26</v>
       </c>
       <c r="B153">
-        <v>103.5101253999971</v>
+        <v>104.4787474196186</v>
       </c>
       <c r="C153">
-        <v>107.2899636931662</v>
+        <v>108.4873893334412</v>
       </c>
       <c r="D153">
-        <v>-3.779838293169036</v>
+        <v>-4.008641913822601</v>
       </c>
       <c r="E153" t="s">
         <v>78</v>
@@ -3223,13 +3223,13 @@
         <v>26</v>
       </c>
       <c r="B154">
-        <v>98.98732347177878</v>
+        <v>100.0187126612355</v>
       </c>
       <c r="C154">
-        <v>99.37569196962151</v>
+        <v>100.4762413461995</v>
       </c>
       <c r="D154">
-        <v>-0.388368497842734</v>
+        <v>-0.4575286849640605</v>
       </c>
       <c r="E154" t="s">
         <v>79</v>
@@ -3240,13 +3240,13 @@
         <v>26</v>
       </c>
       <c r="B155">
-        <v>111.8025168289397</v>
+        <v>113.0176762047963</v>
       </c>
       <c r="C155">
-        <v>111.9508009861512</v>
+        <v>113.195603647147</v>
       </c>
       <c r="D155">
-        <v>-0.1482841572114921</v>
+        <v>-0.1779274423507502</v>
       </c>
       <c r="E155" t="s">
         <v>80</v>
@@ -3257,13 +3257,13 @@
         <v>27</v>
       </c>
       <c r="B156">
-        <v>107.2896254834492</v>
+        <v>108.0056687479765</v>
       </c>
       <c r="C156">
-        <v>106.9674048694846</v>
+        <v>107.6545178251891</v>
       </c>
       <c r="D156">
-        <v>0.3222206139646602</v>
+        <v>0.3511509227873972</v>
       </c>
       <c r="E156" t="s">
         <v>74</v>
@@ -3274,13 +3274,13 @@
         <v>27</v>
       </c>
       <c r="B157">
-        <v>102.10558395724</v>
+        <v>102.7860073297745</v>
       </c>
       <c r="C157">
-        <v>101.7993913662782</v>
+        <v>102.4523249425679</v>
       </c>
       <c r="D157">
-        <v>0.3061925909617713</v>
+        <v>0.3336823872065509</v>
       </c>
       <c r="E157" t="s">
         <v>75</v>
@@ -3291,13 +3291,13 @@
         <v>27</v>
       </c>
       <c r="B158">
-        <v>112.7463305068503</v>
+        <v>113.4998863989837</v>
       </c>
       <c r="C158">
-        <v>112.4072302062136</v>
+        <v>113.130338707468</v>
       </c>
       <c r="D158">
-        <v>0.3391003006367015</v>
+        <v>0.3695476915157627</v>
       </c>
       <c r="E158" t="s">
         <v>76</v>
@@ -3308,13 +3308,13 @@
         <v>27</v>
       </c>
       <c r="B159">
-        <v>109.7568123364182</v>
+        <v>110.4896541977476</v>
       </c>
       <c r="C159">
-        <v>109.4270326478764</v>
+        <v>110.1302650430697</v>
       </c>
       <c r="D159">
-        <v>0.3297796885418336</v>
+        <v>0.359389154677956</v>
       </c>
       <c r="E159" t="s">
         <v>77</v>
@@ -3325,13 +3325,13 @@
         <v>27</v>
       </c>
       <c r="B160">
-        <v>103.8017018328303</v>
+        <v>104.493934577418</v>
       </c>
       <c r="C160">
-        <v>103.49019547762</v>
+        <v>104.1544606394554</v>
       </c>
       <c r="D160">
-        <v>0.3115063552102413</v>
+        <v>0.3394739379625378</v>
       </c>
       <c r="E160" t="s">
         <v>78</v>
@@ -3342,13 +3342,13 @@
         <v>27</v>
       </c>
       <c r="B161">
-        <v>102.1789560866576</v>
+        <v>102.860027922522</v>
       </c>
       <c r="C161">
-        <v>101.8724718392536</v>
+        <v>102.5260274674709</v>
       </c>
       <c r="D161">
-        <v>0.3064842474040574</v>
+        <v>0.3340004550511111</v>
       </c>
       <c r="E161" t="s">
         <v>79</v>
@@ -3359,13 +3359,13 @@
         <v>27</v>
       </c>
       <c r="B162">
-        <v>112.6626816940227</v>
+        <v>113.4155121418517</v>
       </c>
       <c r="C162">
-        <v>112.3239076832955</v>
+        <v>113.0463202730954</v>
       </c>
       <c r="D162">
-        <v>0.3387740107271924</v>
+        <v>0.3691918687563174</v>
       </c>
       <c r="E162" t="s">
         <v>80</v>
@@ -3376,13 +3376,13 @@
         <v>28</v>
       </c>
       <c r="B163">
-        <v>104.7849850405636</v>
+        <v>105.9319383400366</v>
       </c>
       <c r="C163">
-        <v>104.7604157922432</v>
+        <v>105.930547015975</v>
       </c>
       <c r="D163">
-        <v>0.02456924832038965</v>
+        <v>0.001391324061629007</v>
       </c>
       <c r="E163" t="s">
         <v>74</v>
@@ -3393,13 +3393,13 @@
         <v>28</v>
       </c>
       <c r="B164">
-        <v>86.07562467520063</v>
+        <v>87.05498503561535</v>
       </c>
       <c r="C164">
-        <v>85.63660136029488</v>
+        <v>86.57409458357574</v>
       </c>
       <c r="D164">
-        <v>0.4390233149057536</v>
+        <v>0.4808904520396027</v>
       </c>
       <c r="E164" t="s">
         <v>75</v>
@@ -3410,13 +3410,13 @@
         <v>28</v>
       </c>
       <c r="B165">
-        <v>116.5278090918739</v>
+        <v>117.606670232214</v>
       </c>
       <c r="C165">
-        <v>129.1443944553361</v>
+        <v>130.6126851236392</v>
       </c>
       <c r="D165">
-        <v>-12.61658536346221</v>
+        <v>-13.0060148914252</v>
       </c>
       <c r="E165" t="s">
         <v>76</v>
@@ -3427,13 +3427,13 @@
         <v>28</v>
       </c>
       <c r="B166">
-        <v>99.38261983012734</v>
+        <v>100.5243230211515</v>
       </c>
       <c r="C166">
-        <v>98.87406033559533</v>
+        <v>99.96769645383722</v>
       </c>
       <c r="D166">
-        <v>0.5085594945320082</v>
+        <v>0.5566265673143107</v>
       </c>
       <c r="E166" t="s">
         <v>77</v>
@@ -3444,13 +3444,13 @@
         <v>28</v>
       </c>
       <c r="B167">
-        <v>102.9422903799259</v>
+        <v>103.9241368543301</v>
       </c>
       <c r="C167">
-        <v>106.6691385763148</v>
+        <v>107.8673630631875</v>
       </c>
       <c r="D167">
-        <v>-3.726848196388886</v>
+        <v>-3.943226208857354</v>
       </c>
       <c r="E167" t="s">
         <v>78</v>
@@ -3461,13 +3461,13 @@
         <v>28</v>
       </c>
       <c r="B168">
-        <v>98.32087738739212</v>
+        <v>99.35676891219663</v>
       </c>
       <c r="C168">
-        <v>98.69010368787731</v>
+        <v>99.79055899613027</v>
       </c>
       <c r="D168">
-        <v>-0.3692263004851952</v>
+        <v>-0.4337900839336442</v>
       </c>
       <c r="E168" t="s">
         <v>79</v>
@@ -3478,13 +3478,13 @@
         <v>28</v>
       </c>
       <c r="B169">
-        <v>111.1316998524431</v>
+        <v>112.3489477413042</v>
       </c>
       <c r="C169">
-        <v>111.2172096338127</v>
+        <v>112.4615062046136</v>
       </c>
       <c r="D169">
-        <v>-0.08550978136965171</v>
+        <v>-0.1125584633093411</v>
       </c>
       <c r="E169" t="s">
         <v>80</v>
@@ -3495,13 +3495,13 @@
         <v>29</v>
       </c>
       <c r="B170">
-        <v>105.3010626644036</v>
+        <v>106.4468523576933</v>
       </c>
       <c r="C170">
-        <v>105.3033818981914</v>
+        <v>106.4737219197419</v>
       </c>
       <c r="D170">
-        <v>-0.002319233787801522</v>
+        <v>-0.02686956204857438</v>
       </c>
       <c r="E170" t="s">
         <v>74</v>
@@ -3512,13 +3512,13 @@
         <v>29</v>
       </c>
       <c r="B171">
-        <v>86.70120746053394</v>
+        <v>87.68201111150654</v>
       </c>
       <c r="C171">
-        <v>86.26153440095756</v>
+        <v>87.20041183105161</v>
       </c>
       <c r="D171">
-        <v>0.4396730595763785</v>
+        <v>0.4815992804549296</v>
       </c>
       <c r="E171" t="s">
         <v>75</v>
@@ -3529,13 +3529,13 @@
         <v>29</v>
       </c>
       <c r="B172">
-        <v>116.7557128825161</v>
+        <v>117.8209229423692</v>
       </c>
       <c r="C172">
-        <v>129.5430990322111</v>
+        <v>131.0096027728173</v>
       </c>
       <c r="D172">
-        <v>-12.78738614969495</v>
+        <v>-13.18867983044812</v>
       </c>
       <c r="E172" t="s">
         <v>76</v>
@@ -3546,13 +3546,13 @@
         <v>29</v>
       </c>
       <c r="B173">
-        <v>100.0028479618318</v>
+        <v>101.1459177346297</v>
       </c>
       <c r="C173">
-        <v>99.49399091715078</v>
+        <v>100.5888195129109</v>
       </c>
       <c r="D173">
-        <v>0.5088570446810223</v>
+        <v>0.5570982217188458</v>
       </c>
       <c r="E173" t="s">
         <v>77</v>
@@ -3563,13 +3563,13 @@
         <v>29</v>
       </c>
       <c r="B174">
-        <v>103.3740748226295</v>
+        <v>104.3454580580801</v>
       </c>
       <c r="C174">
-        <v>107.1461863206336</v>
+        <v>108.3438050387351</v>
       </c>
       <c r="D174">
-        <v>-3.772111498004108</v>
+        <v>-3.998346980654929</v>
       </c>
       <c r="E174" t="s">
         <v>78</v>
@@ -3580,13 +3580,13 @@
         <v>29</v>
       </c>
       <c r="B175">
-        <v>98.82975499646653</v>
+        <v>99.86228430223792</v>
       </c>
       <c r="C175">
-        <v>99.21576031847466</v>
+        <v>100.316279586175</v>
       </c>
       <c r="D175">
-        <v>-0.3860053220081312</v>
+        <v>-0.453995283937104</v>
       </c>
       <c r="E175" t="s">
         <v>79</v>
@@ -3597,13 +3597,13 @@
         <v>29</v>
       </c>
       <c r="B176">
-        <v>111.6445838889559</v>
+        <v>112.8605251025283</v>
       </c>
       <c r="C176">
-        <v>111.7791460571568</v>
+        <v>113.0238164588337</v>
       </c>
       <c r="D176">
-        <v>-0.1345621682009153</v>
+        <v>-0.1632913563054075</v>
       </c>
       <c r="E176" t="s">
         <v>80</v>
@@ -3614,13 +3614,13 @@
         <v>30</v>
       </c>
       <c r="B177">
-        <v>105.3737234624052</v>
+        <v>106.5192137086707</v>
       </c>
       <c r="C177">
-        <v>105.3738506193608</v>
+        <v>106.5441668562187</v>
       </c>
       <c r="D177">
-        <v>-0.000127156955556984</v>
+        <v>-0.02495314754798983</v>
       </c>
       <c r="E177" t="s">
         <v>74</v>
@@ -3631,13 +3631,13 @@
         <v>30</v>
       </c>
       <c r="B178">
-        <v>86.79148512634291</v>
+        <v>87.77255355289672</v>
       </c>
       <c r="C178">
-        <v>86.35169266056458</v>
+        <v>87.29082430982187</v>
       </c>
       <c r="D178">
-        <v>0.439792465778325</v>
+        <v>0.4817292430748523</v>
       </c>
       <c r="E178" t="s">
         <v>75</v>
@@ -3648,13 +3648,13 @@
         <v>30</v>
       </c>
       <c r="B179">
-        <v>116.8082926608809</v>
+        <v>117.8719449155789</v>
       </c>
       <c r="C179">
-        <v>129.5792305227406</v>
+        <v>131.0452396135622</v>
       </c>
       <c r="D179">
-        <v>-12.77093786185964</v>
+        <v>-13.17329469798329</v>
       </c>
       <c r="E179" t="s">
         <v>76</v>
@@ -3665,13 +3665,13 @@
         <v>30</v>
       </c>
       <c r="B180">
-        <v>100.0907381378793</v>
+        <v>101.2340160556509</v>
       </c>
       <c r="C180">
-        <v>99.58179392738927</v>
+        <v>100.6768236654227</v>
       </c>
       <c r="D180">
-        <v>0.5089442104900428</v>
+        <v>0.5571923902281384</v>
       </c>
       <c r="E180" t="s">
         <v>77</v>
@@ -3682,13 +3682,13 @@
         <v>30</v>
       </c>
       <c r="B181">
-        <v>103.4474438036495</v>
+        <v>104.4177867884324</v>
       </c>
       <c r="C181">
-        <v>107.20201630778</v>
+        <v>108.3994264193737</v>
       </c>
       <c r="D181">
-        <v>-3.754572504130536</v>
+        <v>-3.981639630941359</v>
       </c>
       <c r="E181" t="s">
         <v>78</v>
@@ -3699,13 +3699,13 @@
         <v>30</v>
       </c>
       <c r="B182">
-        <v>98.90423751103759</v>
+        <v>99.93631752137345</v>
       </c>
       <c r="C182">
-        <v>99.28307772075725</v>
+        <v>100.3835455799018</v>
       </c>
       <c r="D182">
-        <v>-0.3788402097196553</v>
+        <v>-0.447228058528367</v>
       </c>
       <c r="E182" t="s">
         <v>79</v>
@@ -3716,13 +3716,13 @@
         <v>30</v>
       </c>
       <c r="B183">
-        <v>111.7180719189746</v>
+        <v>112.9336961838004</v>
       </c>
       <c r="C183">
-        <v>111.8530832157546</v>
+        <v>113.0977612120159</v>
       </c>
       <c r="D183">
-        <v>-0.1350112967800072</v>
+        <v>-0.1640650282154752</v>
       </c>
       <c r="E183" t="s">
         <v>80</v>
@@ -3733,13 +3733,13 @@
         <v>31</v>
       </c>
       <c r="B184">
-        <v>105.2181246207249</v>
+        <v>106.1638558956194</v>
       </c>
       <c r="C184">
-        <v>105.7980199260865</v>
+        <v>106.9643774694308</v>
       </c>
       <c r="D184">
-        <v>-0.5798953053616032</v>
+        <v>-0.8005215738113236</v>
       </c>
       <c r="E184" t="s">
         <v>74</v>
@@ -3750,13 +3750,13 @@
         <v>31</v>
       </c>
       <c r="B185">
-        <v>88.72593561715595</v>
+        <v>89.72508587917869</v>
       </c>
       <c r="C185">
-        <v>88.27802084011495</v>
+        <v>89.23452455877084</v>
       </c>
       <c r="D185">
-        <v>0.4479147770410066</v>
+        <v>0.4905613204078492</v>
       </c>
       <c r="E185" t="s">
         <v>75</v>
@@ -3767,13 +3767,13 @@
         <v>31</v>
       </c>
       <c r="B186">
-        <v>112.277679300603</v>
+        <v>113.0749317232717</v>
       </c>
       <c r="C186">
-        <v>127.481548505867</v>
+        <v>128.9087943036423</v>
       </c>
       <c r="D186">
-        <v>-15.20386920526396</v>
+        <v>-15.83386258037062</v>
       </c>
       <c r="E186" t="s">
         <v>76</v>
@@ -3784,13 +3784,13 @@
         <v>31</v>
       </c>
       <c r="B187">
-        <v>101.9360485353379</v>
+        <v>103.0859438865139</v>
       </c>
       <c r="C187">
-        <v>101.4511046915571</v>
+        <v>102.5611418011301</v>
       </c>
       <c r="D187">
-        <v>0.4849438437808544</v>
+        <v>0.5248020853837545</v>
       </c>
       <c r="E187" t="s">
         <v>77</v>
@@ -3801,13 +3801,13 @@
         <v>31</v>
       </c>
       <c r="B188">
-        <v>102.5531795932143</v>
+        <v>103.3328323755397</v>
       </c>
       <c r="C188">
-        <v>106.4012005691019</v>
+        <v>107.5789717140579</v>
       </c>
       <c r="D188">
-        <v>-3.848020975887636</v>
+        <v>-4.246139338518148</v>
       </c>
       <c r="E188" t="s">
         <v>78</v>
@@ -3818,13 +3818,13 @@
         <v>31</v>
       </c>
       <c r="B189">
-        <v>99.0106718402906</v>
+        <v>99.95861909309265</v>
       </c>
       <c r="C189">
-        <v>99.35337095237134</v>
+        <v>100.4461677073993</v>
       </c>
       <c r="D189">
-        <v>-0.3426991120807372</v>
+        <v>-0.4875486143066183</v>
       </c>
       <c r="E189" t="s">
         <v>79</v>
@@ -3835,13 +3835,13 @@
         <v>31</v>
       </c>
       <c r="B190">
-        <v>111.0209327404927</v>
+        <v>112.000393812621</v>
       </c>
       <c r="C190">
-        <v>112.6753332652917</v>
+        <v>113.9202699563049</v>
       </c>
       <c r="D190">
-        <v>-1.654400524799058</v>
+        <v>-1.919876143683908</v>
       </c>
       <c r="E190" t="s">
         <v>80</v>
@@ -3852,13 +3852,13 @@
         <v>32</v>
       </c>
       <c r="B191">
-        <v>99.69779138181589</v>
+        <v>100.8240944044176</v>
       </c>
       <c r="C191">
-        <v>99.21080801528696</v>
+        <v>100.3003423591722</v>
       </c>
       <c r="D191">
-        <v>0.486983366528932</v>
+        <v>0.5237520452454305</v>
       </c>
       <c r="E191" t="s">
         <v>74</v>
@@ -3869,13 +3869,13 @@
         <v>32</v>
       </c>
       <c r="B192">
-        <v>83.34929611118592</v>
+        <v>84.2836055533258</v>
       </c>
       <c r="C192">
-        <v>82.93042770598619</v>
+        <v>83.82481389515691</v>
       </c>
       <c r="D192">
-        <v>0.4188684051997313</v>
+        <v>0.4587916581688916</v>
       </c>
       <c r="E192" t="s">
         <v>75</v>
@@ -3886,13 +3886,13 @@
         <v>32</v>
       </c>
       <c r="B193">
-        <v>110.4013213183169</v>
+        <v>111.1182773465411</v>
       </c>
       <c r="C193">
-        <v>119.2916402939302</v>
+        <v>120.6228088623101</v>
       </c>
       <c r="D193">
-        <v>-8.890318975613312</v>
+        <v>-9.504531515768988</v>
       </c>
       <c r="E193" t="s">
         <v>76</v>
@@ -3903,13 +3903,13 @@
         <v>32</v>
       </c>
       <c r="B194">
-        <v>95.75622147921801</v>
+        <v>96.84130925638279</v>
       </c>
       <c r="C194">
-        <v>95.26995414906592</v>
+        <v>96.30875228426825</v>
       </c>
       <c r="D194">
-        <v>0.4862673301520886</v>
+        <v>0.5325569721145342</v>
       </c>
       <c r="E194" t="s">
         <v>77</v>
@@ -3920,13 +3920,13 @@
         <v>32</v>
       </c>
       <c r="B195">
-        <v>99.51207511264332</v>
+        <v>100.488676006138</v>
       </c>
       <c r="C195">
-        <v>99.65328168536482</v>
+        <v>100.7515577624174</v>
       </c>
       <c r="D195">
-        <v>-0.1412065727215008</v>
+        <v>-0.2628817562794268</v>
       </c>
       <c r="E195" t="s">
         <v>78</v>
@@ -3937,13 +3937,13 @@
         <v>32</v>
       </c>
       <c r="B196">
-        <v>93.59010452398235</v>
+        <v>94.64672372011594</v>
       </c>
       <c r="C196">
-        <v>93.13606374564206</v>
+        <v>94.15577419669935</v>
       </c>
       <c r="D196">
-        <v>0.4540407783402856</v>
+        <v>0.4909495234165888</v>
       </c>
       <c r="E196" t="s">
         <v>79</v>
@@ -3954,13 +3954,13 @@
         <v>32</v>
       </c>
       <c r="B197">
-        <v>106.0031860967938</v>
+        <v>107.1500659186886</v>
       </c>
       <c r="C197">
-        <v>105.6998352548413</v>
+        <v>106.8640350904843</v>
       </c>
       <c r="D197">
-        <v>0.3033508419525504</v>
+        <v>0.286030828204261</v>
       </c>
       <c r="E197" t="s">
         <v>80</v>
@@ -3971,13 +3971,13 @@
         <v>33</v>
       </c>
       <c r="B198">
-        <v>104.8266151892294</v>
+        <v>105.9743868481432</v>
       </c>
       <c r="C198">
-        <v>104.8080264438685</v>
+        <v>105.9780062642165</v>
       </c>
       <c r="D198">
-        <v>0.01858874536088706</v>
+        <v>-0.00361941607330607</v>
       </c>
       <c r="E198" t="s">
         <v>74</v>
@@ -3988,13 +3988,13 @@
         <v>33</v>
       </c>
       <c r="B199">
-        <v>86.12428178044395</v>
+        <v>87.10349474633861</v>
       </c>
       <c r="C199">
-        <v>85.68532444212526</v>
+        <v>86.62267469384834</v>
       </c>
       <c r="D199">
-        <v>0.4389573383186871</v>
+        <v>0.480820052490273</v>
       </c>
       <c r="E199" t="s">
         <v>75</v>
@@ -4005,13 +4005,13 @@
         <v>33</v>
       </c>
       <c r="B200">
-        <v>116.5301805349674</v>
+        <v>117.6074170491206</v>
       </c>
       <c r="C200">
-        <v>129.1908839578251</v>
+        <v>130.6590152806878</v>
       </c>
       <c r="D200">
-        <v>-12.66070342285775</v>
+        <v>-13.05159823156713</v>
       </c>
       <c r="E200" t="s">
         <v>76</v>
@@ -4022,13 +4022,13 @@
         <v>33</v>
       </c>
       <c r="B201">
-        <v>99.42974970214284</v>
+        <v>100.5714255085385</v>
       </c>
       <c r="C201">
-        <v>98.92123090621584</v>
+        <v>100.0147096564405</v>
       </c>
       <c r="D201">
-        <v>0.508518795927003</v>
+        <v>0.5567158520980371</v>
       </c>
       <c r="E201" t="s">
         <v>77</v>
@@ -4039,13 +4039,13 @@
         <v>33</v>
       </c>
       <c r="B202">
-        <v>102.969373509034</v>
+        <v>103.9487709330207</v>
       </c>
       <c r="C202">
-        <v>106.7173736845409</v>
+        <v>107.9154541110874</v>
       </c>
       <c r="D202">
-        <v>-3.748000175506817</v>
+        <v>-3.966683178066731</v>
       </c>
       <c r="E202" t="s">
         <v>78</v>
@@ -4056,13 +4056,13 @@
         <v>33</v>
       </c>
       <c r="B203">
-        <v>98.36024557043449</v>
+        <v>99.39601405607644</v>
       </c>
       <c r="C203">
-        <v>98.73869395653283</v>
+        <v>99.83900773811122</v>
       </c>
       <c r="D203">
-        <v>-0.3784483860983414</v>
+        <v>-0.442993682034782</v>
       </c>
       <c r="E203" t="s">
         <v>79</v>
@@ -4073,13 +4073,13 @@
         <v>33</v>
       </c>
       <c r="B204">
-        <v>111.1697494493872</v>
+        <v>112.3878540698479</v>
       </c>
       <c r="C204">
-        <v>111.2637680201757</v>
+        <v>112.5079031054908</v>
       </c>
       <c r="D204">
-        <v>-0.09401857078859166</v>
+        <v>-0.1200490356429356</v>
       </c>
       <c r="E204" t="s">
         <v>80</v>
@@ -4090,13 +4090,13 @@
         <v>34</v>
       </c>
       <c r="B205">
-        <v>104.9845853810213</v>
+        <v>106.1317226617122</v>
       </c>
       <c r="C205">
-        <v>104.9729401021907</v>
+        <v>106.1430600350614</v>
       </c>
       <c r="D205">
-        <v>0.01164527883055655</v>
+        <v>-0.01133737334926366</v>
       </c>
       <c r="E205" t="s">
         <v>74</v>
@@ -4107,13 +4107,13 @@
         <v>34</v>
       </c>
       <c r="B206">
-        <v>86.31621190339678</v>
+        <v>87.2959742296127</v>
       </c>
       <c r="C206">
-        <v>85.87700738561318</v>
+        <v>86.81488507546139</v>
       </c>
       <c r="D206">
-        <v>0.4392045177835939</v>
+        <v>0.4810891541513058</v>
       </c>
       <c r="E206" t="s">
         <v>75</v>
@@ -4124,13 +4124,13 @@
         <v>34</v>
       </c>
       <c r="B207">
-        <v>116.6054828402575</v>
+        <v>117.6787623076328</v>
       </c>
       <c r="C207">
-        <v>129.3082526947479</v>
+        <v>130.775863079238</v>
       </c>
       <c r="D207">
-        <v>-12.70276985449044</v>
+        <v>-13.09710077160521</v>
       </c>
       <c r="E207" t="s">
         <v>76</v>
@@ -4141,13 +4141,13 @@
         <v>34</v>
       </c>
       <c r="B208">
-        <v>99.62074277855037</v>
+        <v>100.7629049081905</v>
       </c>
       <c r="C208">
-        <v>99.11210238696036</v>
+        <v>100.206052008825</v>
       </c>
       <c r="D208">
-        <v>0.5086403915900064</v>
+        <v>0.5568528993655235</v>
       </c>
       <c r="E208" t="s">
         <v>77</v>
@@ -4158,13 +4158,13 @@
         <v>34</v>
       </c>
       <c r="B209">
-        <v>103.1036993562629</v>
+        <v>104.0804692156369</v>
       </c>
       <c r="C209">
-        <v>106.8598888633765</v>
+        <v>108.0578338844063</v>
       </c>
       <c r="D209">
-        <v>-3.756189507113589</v>
+        <v>-3.977364668769454</v>
       </c>
       <c r="E209" t="s">
         <v>78</v>
@@ -4175,13 +4175,13 @@
         <v>34</v>
       </c>
       <c r="B210">
-        <v>98.51621687304754</v>
+        <v>99.55093441875491</v>
       </c>
       <c r="C210">
-        <v>98.89725941561396</v>
+        <v>99.99765988840093</v>
       </c>
       <c r="D210">
-        <v>-0.3810425425664192</v>
+        <v>-0.4467254696460259</v>
       </c>
       <c r="E210" t="s">
         <v>79</v>
@@ -4192,13 +4192,13 @@
         <v>34</v>
       </c>
       <c r="B211">
-        <v>111.3281965199446</v>
+        <v>112.5456089745531</v>
       </c>
       <c r="C211">
-        <v>111.4356249255143</v>
+        <v>112.6799605251706</v>
       </c>
       <c r="D211">
-        <v>-0.1074284055697632</v>
+        <v>-0.1343515506174384</v>
       </c>
       <c r="E211" t="s">
         <v>80</v>
@@ -4209,13 +4209,13 @@
         <v>35</v>
       </c>
       <c r="B212">
-        <v>104.2909972394141</v>
+        <v>105.3032182069975</v>
       </c>
       <c r="C212">
-        <v>104.7700330363211</v>
+        <v>105.9361616681434</v>
       </c>
       <c r="D212">
-        <v>-0.4790357969070698</v>
+        <v>-0.6329434611458993</v>
       </c>
       <c r="E212" t="s">
         <v>74</v>
@@ -4226,13 +4226,13 @@
         <v>35</v>
       </c>
       <c r="B213">
-        <v>87.51172713837647</v>
+        <v>88.50778955233017</v>
       </c>
       <c r="C213">
-        <v>87.0652045154315</v>
+        <v>88.01874153740805</v>
       </c>
       <c r="D213">
-        <v>0.4465226229449684</v>
+        <v>0.489048014922119</v>
       </c>
       <c r="E213" t="s">
         <v>75</v>
@@ -4243,13 +4243,13 @@
         <v>35</v>
       </c>
       <c r="B214">
-        <v>111.937093127601</v>
+        <v>112.7732134407346</v>
       </c>
       <c r="C214">
-        <v>126.7575335030407</v>
+        <v>128.1888642451241</v>
       </c>
       <c r="D214">
-        <v>-14.82044037543972</v>
+        <v>-15.41565080438953</v>
       </c>
       <c r="E214" t="s">
         <v>76</v>
@@ -4260,13 +4260,13 @@
         <v>35</v>
       </c>
       <c r="B215">
-        <v>100.7019866521191</v>
+        <v>101.8488912507005</v>
       </c>
       <c r="C215">
-        <v>100.2093213133105</v>
+        <v>101.3164332871295</v>
       </c>
       <c r="D215">
-        <v>0.4926653388085924</v>
+        <v>0.5324579635709625</v>
       </c>
       <c r="E215" t="s">
         <v>77</v>
@@ -4277,13 +4277,13 @@
         <v>35</v>
       </c>
       <c r="B216">
-        <v>101.7028822563921</v>
+        <v>102.51189043772</v>
       </c>
       <c r="C216">
-        <v>105.5601165033912</v>
+        <v>106.7399270233294</v>
       </c>
       <c r="D216">
-        <v>-3.857234246999141</v>
+        <v>-4.228036585609416</v>
       </c>
       <c r="E216" t="s">
         <v>78</v>
@@ -4294,13 +4294,13 @@
         <v>35</v>
       </c>
       <c r="B217">
-        <v>98.04182790897947</v>
+        <v>99.00169573919328</v>
       </c>
       <c r="C217">
-        <v>98.40198975503013</v>
+        <v>99.49528319896208</v>
       </c>
       <c r="D217">
-        <v>-0.3601618460506586</v>
+        <v>-0.4935874597688041</v>
       </c>
       <c r="E217" t="s">
         <v>79</v>
@@ -4311,13 +4311,13 @@
         <v>35</v>
       </c>
       <c r="B218">
-        <v>110.2463201333841</v>
+        <v>111.2478242719145</v>
       </c>
       <c r="C218">
-        <v>111.5617761353572</v>
+        <v>112.8056541152003</v>
       </c>
       <c r="D218">
-        <v>-1.315456001973033</v>
+        <v>-1.557829843285802</v>
       </c>
       <c r="E218" t="s">
         <v>80</v>
@@ -4328,13 +4328,13 @@
         <v>36</v>
       </c>
       <c r="B219">
-        <v>99.75888549638287</v>
+        <v>100.8677411640088</v>
       </c>
       <c r="C219">
-        <v>99.48001706113618</v>
+        <v>100.5194660865707</v>
       </c>
       <c r="D219">
-        <v>0.278868435246693</v>
+        <v>0.3482750774381032</v>
       </c>
       <c r="E219" t="s">
         <v>74</v>
@@ -4345,13 +4345,13 @@
         <v>36</v>
       </c>
       <c r="B220">
-        <v>93.96654415700533</v>
+        <v>94.94358756246466</v>
       </c>
       <c r="C220">
-        <v>93.58628506358451</v>
+        <v>94.50679329135846</v>
       </c>
       <c r="D220">
-        <v>0.3802590934208183</v>
+        <v>0.4367942711061943</v>
       </c>
       <c r="E220" t="s">
         <v>75</v>
@@ -4362,13 +4362,13 @@
         <v>36</v>
       </c>
       <c r="B221">
-        <v>106.3062717354229</v>
+        <v>107.5235488049557</v>
       </c>
       <c r="C221">
-        <v>107.6126815717389</v>
+        <v>108.7307333453135</v>
       </c>
       <c r="D221">
-        <v>-1.306409836316035</v>
+        <v>-1.207184540357758</v>
       </c>
       <c r="E221" t="s">
         <v>76</v>
@@ -4379,13 +4379,13 @@
         <v>36</v>
       </c>
       <c r="B222">
-        <v>95.10317249615269</v>
+        <v>96.10015408740998</v>
       </c>
       <c r="C222">
-        <v>94.63181354382382</v>
+        <v>95.57880119641251</v>
       </c>
       <c r="D222">
-        <v>0.4713589523288704</v>
+        <v>0.5213528909974627</v>
       </c>
       <c r="E222" t="s">
         <v>77</v>
@@ -4396,13 +4396,13 @@
         <v>36</v>
       </c>
       <c r="B223">
-        <v>101.4712360651436</v>
+        <v>102.5783046126734</v>
       </c>
       <c r="C223">
-        <v>104.1072705422047</v>
+        <v>105.1649346930565</v>
       </c>
       <c r="D223">
-        <v>-2.636034477061173</v>
+        <v>-2.586630080383117</v>
       </c>
       <c r="E223" t="s">
         <v>78</v>
@@ -4413,13 +4413,13 @@
         <v>36</v>
       </c>
       <c r="B224">
-        <v>99.46602335842503</v>
+        <v>100.5509429402955</v>
       </c>
       <c r="C224">
-        <v>100.871042975581</v>
+        <v>101.8849083022197</v>
       </c>
       <c r="D224">
-        <v>-1.405019617155958</v>
+        <v>-1.3339653619242</v>
       </c>
       <c r="E224" t="s">
         <v>79</v>
@@ -4430,13 +4430,13 @@
         <v>36</v>
       </c>
       <c r="B225">
-        <v>98.69010214102545</v>
+        <v>99.74732326282555</v>
       </c>
       <c r="C225">
-        <v>98.23309937907948</v>
+        <v>99.23171960595603</v>
       </c>
       <c r="D225">
-        <v>0.4570027619459722</v>
+        <v>0.5156036568695157</v>
       </c>
       <c r="E225" t="s">
         <v>80</v>
@@ -4447,13 +4447,13 @@
         <v>37</v>
       </c>
       <c r="B226">
-        <v>102.1099054630026</v>
+        <v>102.9788395111185</v>
       </c>
       <c r="C226">
-        <v>102.464798002353</v>
+        <v>103.5448494051459</v>
       </c>
       <c r="D226">
-        <v>-0.3548925393503168</v>
+        <v>-0.5660098940274167</v>
       </c>
       <c r="E226" t="s">
         <v>74</v>
@@ -4464,13 +4464,13 @@
         <v>37</v>
       </c>
       <c r="B227">
-        <v>96.45900018718199</v>
+        <v>97.41751620250511</v>
       </c>
       <c r="C227">
-        <v>96.21656473400157</v>
+        <v>97.19573269563608</v>
       </c>
       <c r="D227">
-        <v>0.2424354531804198</v>
+        <v>0.2217835068690306</v>
       </c>
       <c r="E227" t="s">
         <v>75</v>
@@ -4481,13 +4481,13 @@
         <v>37</v>
       </c>
       <c r="B228">
-        <v>106.29453466203</v>
+        <v>106.9051916589118</v>
       </c>
       <c r="C228">
-        <v>109.9104372493387</v>
+        <v>111.0706053802266</v>
       </c>
       <c r="D228">
-        <v>-3.615902587308682</v>
+        <v>-4.165413721314806</v>
       </c>
       <c r="E228" t="s">
         <v>76</v>
@@ -4498,13 +4498,13 @@
         <v>37</v>
       </c>
       <c r="B229">
-        <v>102.25633387237</v>
+        <v>103.2218571011637</v>
       </c>
       <c r="C229">
-        <v>102.3797881401163</v>
+        <v>103.4376053871798</v>
       </c>
       <c r="D229">
-        <v>-0.1234542677462684</v>
+        <v>-0.2157482860161224</v>
       </c>
       <c r="E229" t="s">
         <v>77</v>
@@ -4515,13 +4515,13 @@
         <v>37</v>
       </c>
       <c r="B230">
-        <v>100.2713615759946</v>
+        <v>101.0121282587471</v>
       </c>
       <c r="C230">
-        <v>101.5285418314337</v>
+        <v>102.580062098668</v>
       </c>
       <c r="D230">
-        <v>-1.25718025543911</v>
+        <v>-1.567933839920912</v>
       </c>
       <c r="E230" t="s">
         <v>78</v>
@@ -4532,13 +4532,13 @@
         <v>37</v>
       </c>
       <c r="B231">
-        <v>98.62168152436766</v>
+        <v>99.45555039089793</v>
       </c>
       <c r="C231">
-        <v>99.15796195662985</v>
+        <v>100.1780873777897</v>
       </c>
       <c r="D231">
-        <v>-0.5362804322621884</v>
+        <v>-0.7225369868918108</v>
       </c>
       <c r="E231" t="s">
         <v>79</v>
@@ -4549,13 +4549,13 @@
         <v>37</v>
       </c>
       <c r="B232">
-        <v>105.1778371109086</v>
+        <v>106.0769037513821</v>
       </c>
       <c r="C232">
-        <v>106.1654368696064</v>
+        <v>107.2738817188122</v>
       </c>
       <c r="D232">
-        <v>-0.9875997586978116</v>
+        <v>-1.196977967430087</v>
       </c>
       <c r="E232" t="s">
         <v>80</v>
@@ -4566,13 +4566,13 @@
         <v>38</v>
       </c>
       <c r="B233">
-        <v>97.0988394477497</v>
+        <v>98.16509669911179</v>
       </c>
       <c r="C233">
-        <v>96.62595814192505</v>
+        <v>97.64342019542923</v>
       </c>
       <c r="D233">
-        <v>0.4728813058246431</v>
+        <v>0.5216765036825564</v>
       </c>
       <c r="E233" t="s">
         <v>74</v>
@@ -4583,13 +4583,13 @@
         <v>38</v>
       </c>
       <c r="B234">
-        <v>93.01536004690939</v>
+        <v>93.97491249100848</v>
       </c>
       <c r="C234">
-        <v>92.57083456526981</v>
+        <v>93.4847906805737</v>
       </c>
       <c r="D234">
-        <v>0.4445254816395874</v>
+        <v>0.4901218104347862</v>
       </c>
       <c r="E234" t="s">
         <v>75</v>
@@ -4600,13 +4600,13 @@
         <v>38</v>
       </c>
       <c r="B235">
-        <v>102.287683821039</v>
+        <v>103.4165131544842</v>
       </c>
       <c r="C235">
-        <v>102.3114681465581</v>
+        <v>103.3981210560324</v>
       </c>
       <c r="D235">
-        <v>-0.02378432551910237</v>
+        <v>0.01839209845182666</v>
       </c>
       <c r="E235" t="s">
         <v>76</v>
@@ -4617,13 +4617,13 @@
         <v>38</v>
       </c>
       <c r="B236">
-        <v>94.88600525747428</v>
+        <v>95.89582196526598</v>
       </c>
       <c r="C236">
-        <v>94.40863719853549</v>
+        <v>95.37108734606319</v>
       </c>
       <c r="D236">
-        <v>0.4773680589387936</v>
+        <v>0.5247346192027891</v>
       </c>
       <c r="E236" t="s">
         <v>77</v>
@@ -4634,13 +4634,13 @@
         <v>38</v>
       </c>
       <c r="B237">
-        <v>98.54753600852592</v>
+        <v>99.59299444279445</v>
       </c>
       <c r="C237">
-        <v>98.56361803260164</v>
+        <v>99.57052898774369</v>
       </c>
       <c r="D237">
-        <v>-0.01608202407571468</v>
+        <v>0.02246545505076369</v>
       </c>
       <c r="E237" t="s">
         <v>78</v>
@@ -4651,13 +4651,13 @@
         <v>38</v>
       </c>
       <c r="B238">
-        <v>96.76671307010268</v>
+        <v>97.78630911871389</v>
       </c>
       <c r="C238">
-        <v>96.53224791890533</v>
+        <v>97.50525685651849</v>
       </c>
       <c r="D238">
-        <v>0.2344651511973552</v>
+        <v>0.2810522621954021</v>
       </c>
       <c r="E238" t="s">
         <v>79</v>
@@ -4668,13 +4668,13 @@
         <v>38</v>
       </c>
       <c r="B239">
-        <v>97.48087284905395</v>
+        <v>98.54301154475608</v>
       </c>
       <c r="C239">
-        <v>97.00538507432753</v>
+        <v>98.01498331122335</v>
       </c>
       <c r="D239">
-        <v>0.4754877747264175</v>
+        <v>0.5280282335327371</v>
       </c>
       <c r="E239" t="s">
         <v>80</v>
@@ -4685,13 +4685,13 @@
         <v>39</v>
       </c>
       <c r="B240">
-        <v>97.95335619205494</v>
+        <v>99.02281344787123</v>
       </c>
       <c r="C240">
-        <v>97.46294648634596</v>
+        <v>98.48366633695767</v>
       </c>
       <c r="D240">
-        <v>0.4904097057089842</v>
+        <v>0.5391471109135608</v>
       </c>
       <c r="E240" t="s">
         <v>74</v>
@@ -4702,13 +4702,13 @@
         <v>39</v>
       </c>
       <c r="B241">
-        <v>90.69757061155819</v>
+        <v>91.63493322956487</v>
       </c>
       <c r="C241">
-        <v>90.25216845706632</v>
+        <v>91.14684645409672</v>
       </c>
       <c r="D241">
-        <v>0.4454021544918731</v>
+        <v>0.4880867754681475</v>
       </c>
       <c r="E241" t="s">
         <v>75</v>
@@ -4719,13 +4719,13 @@
         <v>39</v>
       </c>
       <c r="B242">
-        <v>106.8758803115513</v>
+        <v>108.0598199234432</v>
       </c>
       <c r="C242">
-        <v>106.927919033471</v>
+        <v>108.0519813161868</v>
       </c>
       <c r="D242">
-        <v>-0.05203872191970049</v>
+        <v>0.007838607256431374</v>
       </c>
       <c r="E242" t="s">
         <v>76</v>
@@ -4736,13 +4736,13 @@
         <v>39</v>
       </c>
       <c r="B243">
-        <v>94.1916171073627</v>
+        <v>95.18659544334118</v>
       </c>
       <c r="C243">
-        <v>93.71622075305861</v>
+        <v>94.66558861637306</v>
       </c>
       <c r="D243">
-        <v>0.4753963543040953</v>
+        <v>0.5210068269681187</v>
       </c>
       <c r="E243" t="s">
         <v>77</v>
@@ -4753,13 +4753,13 @@
         <v>39</v>
       </c>
       <c r="B244">
-        <v>100.4869365727204</v>
+        <v>101.5722019292022</v>
       </c>
       <c r="C244">
-        <v>100.3726950935344</v>
+        <v>101.3994976834685</v>
       </c>
       <c r="D244">
-        <v>0.1142414791859778</v>
+        <v>0.1727042457337262</v>
       </c>
       <c r="E244" t="s">
         <v>78</v>
@@ -4770,13 +4770,13 @@
         <v>39</v>
       </c>
       <c r="B245">
-        <v>97.4433626535958</v>
+        <v>98.4808469998255</v>
       </c>
       <c r="C245">
-        <v>97.09025511746826</v>
+        <v>98.07251738609004</v>
       </c>
       <c r="D245">
-        <v>0.3531075361275384</v>
+        <v>0.4083296137354608</v>
       </c>
       <c r="E245" t="s">
         <v>79</v>
@@ -4787,13 +4787,13 @@
         <v>39</v>
       </c>
       <c r="B246">
-        <v>98.53993568035864</v>
+        <v>99.60107683493416</v>
       </c>
       <c r="C246">
-        <v>98.04612924944144</v>
+        <v>99.05637761942452</v>
       </c>
       <c r="D246">
-        <v>0.4938064309172034</v>
+        <v>0.5446992155096382</v>
       </c>
       <c r="E246" t="s">
         <v>80</v>
@@ -4804,13 +4804,13 @@
         <v>40</v>
       </c>
       <c r="B247">
-        <v>99.93391165605684</v>
+        <v>101.0181118960055</v>
       </c>
       <c r="C247">
-        <v>99.46166825563921</v>
+        <v>100.4962319700286</v>
       </c>
       <c r="D247">
-        <v>0.472243400417625</v>
+        <v>0.5218799259768758</v>
       </c>
       <c r="E247" t="s">
         <v>74</v>
@@ -4821,13 +4821,13 @@
         <v>40</v>
       </c>
       <c r="B248">
-        <v>95.4823034654316</v>
+        <v>96.46230600582925</v>
       </c>
       <c r="C248">
-        <v>95.03262366794578</v>
+        <v>95.96668266888663</v>
       </c>
       <c r="D248">
-        <v>0.449679797485814</v>
+        <v>0.4956233369426144</v>
       </c>
       <c r="E248" t="s">
         <v>75</v>
@@ -4838,13 +4838,13 @@
         <v>40</v>
       </c>
       <c r="B249">
-        <v>105.2139345945639</v>
+        <v>106.3621012523803</v>
       </c>
       <c r="C249">
-        <v>105.3450446702521</v>
+        <v>106.4499457144937</v>
       </c>
       <c r="D249">
-        <v>-0.1311100756882411</v>
+        <v>-0.08784446211338093</v>
       </c>
       <c r="E249" t="s">
         <v>76</v>
@@ -4855,13 +4855,13 @@
         <v>40</v>
       </c>
       <c r="B250">
-        <v>96.87739161780291</v>
+        <v>97.90300091002037</v>
       </c>
       <c r="C250">
-        <v>96.40152464239556</v>
+        <v>97.37872817769438</v>
       </c>
       <c r="D250">
-        <v>0.4758669754073566</v>
+        <v>0.5242727323259828</v>
       </c>
       <c r="E250" t="s">
         <v>77</v>
@@ -4872,13 +4872,13 @@
         <v>40</v>
       </c>
       <c r="B251">
-        <v>102.0402640286727</v>
+        <v>103.1108373109026</v>
       </c>
       <c r="C251">
-        <v>102.0757713319637</v>
+        <v>103.1076264853885</v>
       </c>
       <c r="D251">
-        <v>-0.03550730329104113</v>
+        <v>0.003210825514145199</v>
       </c>
       <c r="E251" t="s">
         <v>78</v>
@@ -4889,13 +4889,13 @@
         <v>40</v>
       </c>
       <c r="B252">
-        <v>100.1151975985494</v>
+        <v>101.1609129303753</v>
       </c>
       <c r="C252">
-        <v>99.882750412768</v>
+        <v>100.8806888467894</v>
       </c>
       <c r="D252">
-        <v>0.2324471857814245</v>
+        <v>0.2802240835859351</v>
       </c>
       <c r="E252" t="s">
         <v>79</v>
@@ -4906,13 +4906,13 @@
         <v>40</v>
       </c>
       <c r="B253">
-        <v>99.69137671809699</v>
+        <v>100.7690978692146</v>
       </c>
       <c r="C253">
-        <v>99.22583076676187</v>
+        <v>100.2502733713774</v>
       </c>
       <c r="D253">
-        <v>0.4655459513351161</v>
+        <v>0.5188244978372012</v>
       </c>
       <c r="E253" t="s">
         <v>80</v>
@@ -4923,13 +4923,13 @@
         <v>41</v>
       </c>
       <c r="B254">
-        <v>98.77145696237329</v>
+        <v>99.85487381677454</v>
       </c>
       <c r="C254">
-        <v>98.29443836555393</v>
+        <v>99.32788937215882</v>
       </c>
       <c r="D254">
-        <v>0.477018596819363</v>
+        <v>0.5269844446157208</v>
       </c>
       <c r="E254" t="s">
         <v>74</v>
@@ -4940,13 +4940,13 @@
         <v>41</v>
       </c>
       <c r="B255">
-        <v>93.93733869732861</v>
+        <v>94.9144002743341</v>
       </c>
       <c r="C255">
-        <v>93.48708639156487</v>
+        <v>94.41809957387186</v>
       </c>
       <c r="D255">
-        <v>0.4502523057637404</v>
+        <v>0.4963007004622426</v>
       </c>
       <c r="E255" t="s">
         <v>75</v>
@@ -4957,13 +4957,13 @@
         <v>41</v>
       </c>
       <c r="B256">
-        <v>104.5525501596561</v>
+        <v>105.7081078409398</v>
       </c>
       <c r="C256">
-        <v>104.6028881022282</v>
+        <v>105.7077283810024</v>
       </c>
       <c r="D256">
-        <v>-0.05033794257212776</v>
+        <v>0.0003794599374202789</v>
       </c>
       <c r="E256" t="s">
         <v>76</v>
@@ -4974,13 +4974,13 @@
         <v>41</v>
       </c>
       <c r="B257">
-        <v>95.8985187933762</v>
+        <v>96.92208932154243</v>
       </c>
       <c r="C257">
-        <v>95.41972004732519</v>
+        <v>96.39475909210201</v>
       </c>
       <c r="D257">
-        <v>0.4787987460510124</v>
+        <v>0.5273302294404232</v>
       </c>
       <c r="E257" t="s">
         <v>77</v>
@@ -4991,13 +4991,13 @@
         <v>41</v>
       </c>
       <c r="B258">
-        <v>100.6677320581488</v>
+        <v>101.7435458112634</v>
       </c>
       <c r="C258">
-        <v>100.6742238207586</v>
+        <v>101.7047086506689</v>
       </c>
       <c r="D258">
-        <v>-0.006491762609826424</v>
+        <v>0.03883716059448261</v>
       </c>
       <c r="E258" t="s">
         <v>78</v>
@@ -5008,13 +5008,13 @@
         <v>41</v>
       </c>
       <c r="B259">
-        <v>98.59178396197821</v>
+        <v>99.63911561166846</v>
       </c>
       <c r="C259">
-        <v>98.34328812686381</v>
+        <v>99.33915317232423</v>
       </c>
       <c r="D259">
-        <v>0.2484958351143973</v>
+        <v>0.2999624393442275</v>
       </c>
       <c r="E259" t="s">
         <v>79</v>
@@ -5025,13 +5025,13 @@
         <v>41</v>
       </c>
       <c r="B260">
-        <v>98.91392227681436</v>
+        <v>99.99041956338732</v>
       </c>
       <c r="C260">
-        <v>98.44041091118926</v>
+        <v>99.46331659711723</v>
       </c>
       <c r="D260">
-        <v>0.4735113656251002</v>
+        <v>0.5271029662700926</v>
       </c>
       <c r="E260" t="s">
         <v>80</v>
@@ -5042,13 +5042,13 @@
         <v>42</v>
       </c>
       <c r="B261">
-        <v>104.6763040056989</v>
+        <v>105.7668964244049</v>
       </c>
       <c r="C261">
-        <v>104.1781915624264</v>
+        <v>105.2218257479713</v>
       </c>
       <c r="D261">
-        <v>0.4981124432724613</v>
+        <v>0.5450706764336104</v>
       </c>
       <c r="E261" t="s">
         <v>74</v>
@@ -5059,13 +5059,13 @@
         <v>42</v>
       </c>
       <c r="B262">
-        <v>100.6486473496843</v>
+        <v>101.6653663321179</v>
       </c>
       <c r="C262">
-        <v>100.1798707433967</v>
+        <v>101.1525262512727</v>
       </c>
       <c r="D262">
-        <v>0.4687766062875625</v>
+        <v>0.5128400808451516</v>
       </c>
       <c r="E262" t="s">
         <v>75</v>
@@ -5076,13 +5076,13 @@
         <v>42</v>
       </c>
       <c r="B263">
-        <v>109.3599356057686</v>
+        <v>110.5111236469724</v>
       </c>
       <c r="C263">
-        <v>108.8282821131344</v>
+        <v>109.9293297362552</v>
       </c>
       <c r="D263">
-        <v>0.5316534926342342</v>
+        <v>0.5817939107172236</v>
       </c>
       <c r="E263" t="s">
         <v>76</v>
@@ -5093,13 +5093,13 @@
         <v>42</v>
       </c>
       <c r="B264">
-        <v>105.2909436332016</v>
+        <v>106.380867041297</v>
       </c>
       <c r="C264">
-        <v>104.7879339789492</v>
+        <v>105.8304855623082</v>
       </c>
       <c r="D264">
-        <v>0.5030096542523808</v>
+        <v>0.5503814789888253</v>
       </c>
       <c r="E264" t="s">
         <v>77</v>
@@ -5110,13 +5110,13 @@
         <v>42</v>
       </c>
       <c r="B265">
-        <v>103.3776256018114</v>
+        <v>104.4351626775522</v>
       </c>
       <c r="C265">
-        <v>102.8897640019107</v>
+        <v>103.9013930442189</v>
       </c>
       <c r="D265">
-        <v>0.4878615999006115</v>
+        <v>0.5337696333333213</v>
       </c>
       <c r="E265" t="s">
         <v>78</v>
@@ -5127,13 +5127,13 @@
         <v>42</v>
       </c>
       <c r="B266">
-        <v>101.9426946123216</v>
+        <v>102.9782807017467</v>
       </c>
       <c r="C266">
-        <v>101.4650952201558</v>
+        <v>102.4557648467703</v>
       </c>
       <c r="D266">
-        <v>0.4775993921657999</v>
+        <v>0.5225158549763762</v>
       </c>
       <c r="E266" t="s">
         <v>79</v>
@@ -5144,13 +5144,13 @@
         <v>42</v>
       </c>
       <c r="B267">
-        <v>107.7511661347915</v>
+        <v>108.8792016783001</v>
       </c>
       <c r="C267">
-        <v>107.230331409887</v>
+        <v>108.3092717753193</v>
       </c>
       <c r="D267">
-        <v>0.5208347249045886</v>
+        <v>0.5699299029808316</v>
       </c>
       <c r="E267" t="s">
         <v>80</v>
@@ -5161,13 +5161,13 @@
         <v>43</v>
       </c>
       <c r="B268">
-        <v>102.0768467241502</v>
+        <v>102.0924526785123</v>
       </c>
       <c r="C268">
         <v>100.6593702253671</v>
       </c>
       <c r="D268">
-        <v>1.417476498783103</v>
+        <v>1.43308245314519</v>
       </c>
       <c r="E268" t="s">
         <v>74</v>
@@ -5178,13 +5178,13 @@
         <v>43</v>
       </c>
       <c r="B269">
-        <v>99.41933809689638</v>
+        <v>99.43453775972728</v>
       </c>
       <c r="C269">
         <v>94.82639485154259</v>
       </c>
       <c r="D269">
-        <v>4.592943245353794</v>
+        <v>4.608142908184689</v>
       </c>
       <c r="E269" t="s">
         <v>75</v>
@@ -5195,13 +5195,13 @@
         <v>43</v>
       </c>
       <c r="B270">
-        <v>104.8053913514331</v>
+        <v>104.8214144576205</v>
       </c>
       <c r="C270">
         <v>106.8603008051049</v>
       </c>
       <c r="D270">
-        <v>-2.054909453671812</v>
+        <v>-2.038886347484407</v>
       </c>
       <c r="E270" t="s">
         <v>76</v>
@@ -5212,13 +5212,13 @@
         <v>43</v>
       </c>
       <c r="B271">
-        <v>103.8517579021454</v>
+        <v>103.867635212684</v>
       </c>
       <c r="C271">
         <v>103.0012187306053</v>
       </c>
       <c r="D271">
-        <v>0.8505391715401203</v>
+        <v>0.8664164820787477</v>
       </c>
       <c r="E271" t="s">
         <v>77</v>
@@ -5229,13 +5229,13 @@
         <v>43</v>
       </c>
       <c r="B272">
-        <v>99.78512101229272</v>
+        <v>99.80037659761402</v>
       </c>
       <c r="C272">
         <v>97.16990811870947</v>
       </c>
       <c r="D272">
-        <v>2.615212893583248</v>
+        <v>2.630468478904547</v>
       </c>
       <c r="E272" t="s">
         <v>78</v>
@@ -5246,13 +5246,13 @@
         <v>43</v>
       </c>
       <c r="B273">
-        <v>99.00209249274737</v>
+        <v>99.01722836524706</v>
       </c>
       <c r="C273">
         <v>95.32951894740243</v>
       </c>
       <c r="D273">
-        <v>3.672573545344932</v>
+        <v>3.68770941784463</v>
       </c>
       <c r="E273" t="s">
         <v>79</v>
@@ -5263,13 +5263,13 @@
         <v>43</v>
       </c>
       <c r="B274">
-        <v>105.2470950339659</v>
+        <v>105.2631856697423</v>
       </c>
       <c r="C274">
         <v>106.2918637866056</v>
       </c>
       <c r="D274">
-        <v>-1.044768752639712</v>
+        <v>-1.028678116863318</v>
       </c>
       <c r="E274" t="s">
         <v>80</v>
@@ -5280,13 +5280,13 @@
         <v>44</v>
       </c>
       <c r="B275">
-        <v>101.7762670264058</v>
+        <v>101.7972870955471</v>
       </c>
       <c r="C275">
         <v>98.81308516143419</v>
       </c>
       <c r="D275">
-        <v>2.963181864971588</v>
+        <v>2.984201934112889</v>
       </c>
       <c r="E275" t="s">
         <v>74</v>
@@ -5297,13 +5297,13 @@
         <v>44</v>
       </c>
       <c r="B276">
-        <v>97.88068262317917</v>
+        <v>97.90086566974898</v>
       </c>
       <c r="C276">
         <v>92.02091591348469</v>
       </c>
       <c r="D276">
-        <v>5.859766709694483</v>
+        <v>5.879949756264296</v>
       </c>
       <c r="E276" t="s">
         <v>75</v>
@@ -5314,13 +5314,13 @@
         <v>44</v>
       </c>
       <c r="B277">
-        <v>105.8336905807349</v>
+        <v>105.8555826243062</v>
       </c>
       <c r="C277">
         <v>106.1398485349762</v>
       </c>
       <c r="D277">
-        <v>-0.3061579542412858</v>
+        <v>-0.284265910669987</v>
       </c>
       <c r="E277" t="s">
         <v>76</v>
@@ -5331,13 +5331,13 @@
         <v>44</v>
       </c>
       <c r="B278">
-        <v>103.9218405287459</v>
+        <v>103.943320303873</v>
       </c>
       <c r="C278">
         <v>100.8819306925373</v>
       </c>
       <c r="D278">
-        <v>3.039909836208579</v>
+        <v>3.061389611335713</v>
       </c>
       <c r="E278" t="s">
         <v>77</v>
@@ -5348,13 +5348,13 @@
         <v>44</v>
       </c>
       <c r="B279">
-        <v>98.87620045242988</v>
+        <v>98.89659875452175</v>
       </c>
       <c r="C279">
         <v>95.38298389033673</v>
       </c>
       <c r="D279">
-        <v>3.493216562093153</v>
+        <v>3.513614864185016</v>
       </c>
       <c r="E279" t="s">
         <v>78</v>
@@ -5365,13 +5365,13 @@
         <v>44</v>
       </c>
       <c r="B280">
-        <v>97.69428128793065</v>
+        <v>97.71442554656066</v>
       </c>
       <c r="C280">
         <v>93.18149303522414</v>
       </c>
       <c r="D280">
-        <v>4.512788252706514</v>
+        <v>4.532932511336526</v>
       </c>
       <c r="E280" t="s">
         <v>79</v>
@@ -5382,13 +5382,13 @@
         <v>44</v>
       </c>
       <c r="B281">
-        <v>106.0357683319409</v>
+        <v>106.0577025339777</v>
       </c>
       <c r="C281">
         <v>104.8033277727152</v>
       </c>
       <c r="D281">
-        <v>1.232440559225765</v>
+        <v>1.254374761262497</v>
       </c>
       <c r="E281" t="s">
         <v>80</v>
@@ -5399,13 +5399,13 @@
         <v>45</v>
       </c>
       <c r="B282">
-        <v>100.0736075288041</v>
+        <v>100.088383622782</v>
       </c>
       <c r="C282">
         <v>96.72101594129843</v>
       </c>
       <c r="D282">
-        <v>3.352591587505714</v>
+        <v>3.367367681483572</v>
       </c>
       <c r="E282" t="s">
         <v>74</v>
@@ -5416,13 +5416,13 @@
         <v>45</v>
       </c>
       <c r="B283">
-        <v>97.57384115184061</v>
+        <v>97.58824814967201</v>
       </c>
       <c r="C283">
         <v>91.14954815630998</v>
       </c>
       <c r="D283">
-        <v>6.424292995530635</v>
+        <v>6.438699993362036</v>
       </c>
       <c r="E283" t="s">
         <v>75</v>
@@ -5433,13 +5433,13 @@
         <v>45</v>
       </c>
       <c r="B284">
-        <v>102.6374159878014</v>
+        <v>102.6525706338838</v>
       </c>
       <c r="C284">
         <v>102.6395299556676</v>
       </c>
       <c r="D284">
-        <v>-0.002113967866179678</v>
+        <v>0.01304067821622823</v>
       </c>
       <c r="E284" t="s">
         <v>76</v>
@@ -5450,13 +5450,13 @@
         <v>45</v>
       </c>
       <c r="B285">
-        <v>101.766432453526</v>
+        <v>101.781458496924</v>
       </c>
       <c r="C285">
         <v>98.98584481263983</v>
       </c>
       <c r="D285">
-        <v>2.780587640886154</v>
+        <v>2.795613684284191</v>
       </c>
       <c r="E285" t="s">
         <v>77</v>
@@ -5467,13 +5467,13 @@
         <v>45</v>
       </c>
       <c r="B286">
-        <v>97.89411194856018</v>
+        <v>97.90856623509741</v>
       </c>
       <c r="C286">
         <v>93.36124283021515</v>
       </c>
       <c r="D286">
-        <v>4.532869118345033</v>
+        <v>4.547323404882263</v>
       </c>
       <c r="E286" t="s">
         <v>78</v>
@@ -5484,13 +5484,13 @@
         <v>45</v>
       </c>
       <c r="B287">
-        <v>97.15924518232273</v>
+        <v>97.17359096412363</v>
       </c>
       <c r="C287">
         <v>91.60584984557971</v>
       </c>
       <c r="D287">
-        <v>5.553395336743023</v>
+        <v>5.567741118543921</v>
       </c>
       <c r="E287" t="s">
         <v>79</v>
@@ -5501,13 +5501,13 @@
         <v>45</v>
       </c>
       <c r="B288">
-        <v>103.075388297183</v>
+        <v>103.0906076108652</v>
       </c>
       <c r="C288">
         <v>102.1252244071716</v>
       </c>
       <c r="D288">
-        <v>0.950163890011396</v>
+        <v>0.9653832036935626</v>
       </c>
       <c r="E288" t="s">
         <v>80</v>
@@ -5518,13 +5518,13 @@
         <v>46</v>
       </c>
       <c r="B289">
-        <v>104.7572915669167</v>
+        <v>104.7587697683337</v>
       </c>
       <c r="C289">
         <v>98.94832188364116</v>
       </c>
       <c r="D289">
-        <v>5.808969683275592</v>
+        <v>5.810447884692493</v>
       </c>
       <c r="E289" t="s">
         <v>74</v>
@@ -5535,13 +5535,13 @@
         <v>46</v>
       </c>
       <c r="B290">
-        <v>104.5409783662731</v>
+        <v>104.5424535153537</v>
       </c>
       <c r="C290">
         <v>92.41013040969538</v>
       </c>
       <c r="D290">
-        <v>12.13084795657768</v>
+        <v>12.13232310565833</v>
       </c>
       <c r="E290" t="s">
         <v>75</v>
@@ -5552,13 +5552,13 @@
         <v>46</v>
       </c>
       <c r="B291">
-        <v>104.9740523566447</v>
+        <v>104.9755336167136</v>
       </c>
       <c r="C291">
         <v>105.9812431249225</v>
       </c>
       <c r="D291">
-        <v>-1.007190768277823</v>
+        <v>-1.005709508208852</v>
       </c>
       <c r="E291" t="s">
         <v>76</v>
@@ -5569,13 +5569,13 @@
         <v>46</v>
       </c>
       <c r="B292">
-        <v>104.9335820608016</v>
+        <v>104.9350627498053</v>
       </c>
       <c r="C292">
         <v>101.0560846709772</v>
       </c>
       <c r="D292">
-        <v>3.877497389824399</v>
+        <v>3.878978078828098</v>
       </c>
       <c r="E292" t="s">
         <v>77</v>
@@ -5586,13 +5586,13 @@
         <v>46</v>
       </c>
       <c r="B293">
-        <v>104.5362940712262</v>
+        <v>104.537769154208</v>
       </c>
       <c r="C293">
         <v>95.53543150213483</v>
       </c>
       <c r="D293">
-        <v>9.00086256909141</v>
+        <v>9.002337652073223</v>
       </c>
       <c r="E293" t="s">
         <v>78</v>
@@ -5603,13 +5603,13 @@
         <v>46</v>
       </c>
       <c r="B294">
-        <v>104.4745754287514</v>
+        <v>104.4760496408384</v>
       </c>
       <c r="C294">
         <v>93.4270454069615</v>
       </c>
       <c r="D294">
-        <v>11.04753002178987</v>
+        <v>11.04900423387686</v>
       </c>
       <c r="E294" t="s">
         <v>79</v>
@@ -5620,13 +5620,13 @@
         <v>46</v>
       </c>
       <c r="B295">
-        <v>105.0407727564303</v>
+        <v>105.0422549579725</v>
       </c>
       <c r="C295">
         <v>104.8153944699362</v>
       </c>
       <c r="D295">
-        <v>0.2253782864940916</v>
+        <v>0.2268604880363227</v>
       </c>
       <c r="E295" t="s">
         <v>80</v>
@@ -5637,13 +5637,13 @@
         <v>47</v>
       </c>
       <c r="B296">
-        <v>100.2743745236309</v>
+        <v>100.2897049081669</v>
       </c>
       <c r="C296">
         <v>97.49091864322085</v>
       </c>
       <c r="D296">
-        <v>2.783455880410003</v>
+        <v>2.798786264946031</v>
       </c>
       <c r="E296" t="s">
         <v>74</v>
@@ -5654,13 +5654,13 @@
         <v>47</v>
       </c>
       <c r="B297">
-        <v>97.3721573557648</v>
+        <v>97.38704403665864</v>
       </c>
       <c r="C297">
         <v>91.16273755169843</v>
       </c>
       <c r="D297">
-        <v>6.209419804066371</v>
+        <v>6.224306484960209</v>
       </c>
       <c r="E297" t="s">
         <v>75</v>
@@ -5671,13 +5671,13 @@
         <v>47</v>
       </c>
       <c r="B298">
-        <v>103.2630934669346</v>
+        <v>103.2788807798821</v>
       </c>
       <c r="C298">
         <v>104.2671039189707</v>
       </c>
       <c r="D298">
-        <v>-1.004010452036127</v>
+        <v>-0.9882231390886744</v>
       </c>
       <c r="E298" t="s">
         <v>76</v>
@@ -5688,13 +5688,13 @@
         <v>47</v>
       </c>
       <c r="B299">
-        <v>101.9844224795024</v>
+        <v>102.0000143036421</v>
       </c>
       <c r="C299">
         <v>99.61334573305486</v>
       </c>
       <c r="D299">
-        <v>2.371076746447571</v>
+        <v>2.386668570587233</v>
       </c>
       <c r="E299" t="s">
         <v>77</v>
@@ -5705,13 +5705,13 @@
         <v>47</v>
       </c>
       <c r="B300">
-        <v>98.04459477005092</v>
+        <v>98.05958425611489</v>
       </c>
       <c r="C300">
         <v>94.18852051560059</v>
       </c>
       <c r="D300">
-        <v>3.856074254450334</v>
+        <v>3.871063740514302</v>
       </c>
       <c r="E300" t="s">
         <v>78</v>
@@ -5722,13 +5722,13 @@
         <v>47</v>
       </c>
       <c r="B301">
-        <v>97.25391427958546</v>
+        <v>97.26878288296112</v>
       </c>
       <c r="C301">
         <v>92.29017210793467</v>
       </c>
       <c r="D301">
-        <v>4.963742171650793</v>
+        <v>4.978610775026453</v>
       </c>
       <c r="E301" t="s">
         <v>79</v>
@@ -5739,13 +5739,13 @@
         <v>47</v>
       </c>
       <c r="B302">
-        <v>103.3886426123624</v>
+        <v>103.4044491198119</v>
       </c>
       <c r="C302">
         <v>102.9882889998444</v>
       </c>
       <c r="D302">
-        <v>0.4003536125180318</v>
+        <v>0.4161601199675005</v>
       </c>
       <c r="E302" t="s">
         <v>80</v>
@@ -5756,13 +5756,13 @@
         <v>48</v>
       </c>
       <c r="B303">
-        <v>102.0536782164587</v>
+        <v>102.0641171102639</v>
       </c>
       <c r="C303">
         <v>96.73657358217318</v>
       </c>
       <c r="D303">
-        <v>5.317104634285499</v>
+        <v>5.327543528090757</v>
       </c>
       <c r="E303" t="s">
         <v>74</v>
@@ -5773,13 +5773,13 @@
         <v>48</v>
       </c>
       <c r="B304">
-        <v>100.3799677676872</v>
+        <v>100.3902354605524</v>
       </c>
       <c r="C304">
         <v>89.08045558949017</v>
       </c>
       <c r="D304">
-        <v>11.29951217819702</v>
+        <v>11.30977987106225</v>
       </c>
       <c r="E304" t="s">
         <v>75</v>
@@ -5790,13 +5790,13 @@
         <v>48</v>
       </c>
       <c r="B305">
-        <v>103.7552956941786</v>
+        <v>103.7659086434853</v>
       </c>
       <c r="C305">
         <v>105.0844951852933</v>
       </c>
       <c r="D305">
-        <v>-1.329199491114707</v>
+        <v>-1.318586541807974</v>
       </c>
       <c r="E305" t="s">
         <v>76</v>
@@ -5807,13 +5807,13 @@
         <v>48</v>
       </c>
       <c r="B306">
-        <v>103.3132018022943</v>
+        <v>103.3237695305834</v>
       </c>
       <c r="C306">
         <v>98.57034220795927</v>
       </c>
       <c r="D306">
-        <v>4.742859594335002</v>
+        <v>4.753427322624091</v>
       </c>
       <c r="E306" t="s">
         <v>77</v>
@@ -5824,13 +5824,13 @@
         <v>48</v>
       </c>
       <c r="B307">
-        <v>100.4636842304242</v>
+        <v>100.4739604865013</v>
       </c>
       <c r="C307">
         <v>93.3453152525788</v>
       </c>
       <c r="D307">
-        <v>7.118368977845407</v>
+        <v>7.128645233922526</v>
       </c>
       <c r="E307" t="s">
         <v>78</v>
@@ -5841,13 +5841,13 @@
         <v>48</v>
       </c>
       <c r="B308">
-        <v>99.98056842977243</v>
+        <v>99.99079526877189</v>
       </c>
       <c r="C308">
         <v>90.81591538109396</v>
       </c>
       <c r="D308">
-        <v>9.164653048678474</v>
+        <v>9.174879887677932</v>
       </c>
       <c r="E308" t="s">
         <v>79</v>
@@ -5858,13 +5858,13 @@
         <v>48</v>
       </c>
       <c r="B309">
-        <v>104.1697741979141</v>
+        <v>104.1804295435084</v>
       </c>
       <c r="C309">
         <v>103.0556091016367</v>
       </c>
       <c r="D309">
-        <v>1.114165096277404</v>
+        <v>1.124820441871677</v>
       </c>
       <c r="E309" t="s">
         <v>80</v>
@@ -5875,13 +5875,13 @@
         <v>49</v>
       </c>
       <c r="B310">
-        <v>100.8899392901467</v>
+        <v>100.9123406204251</v>
       </c>
       <c r="C310">
         <v>97.91949908951956</v>
       </c>
       <c r="D310">
-        <v>2.970440200627138</v>
+        <v>2.992841530905523</v>
       </c>
       <c r="E310" t="s">
         <v>74</v>
@@ -5892,13 +5892,13 @@
         <v>49</v>
       </c>
       <c r="B311">
-        <v>96.64713815558258</v>
+        <v>96.66856706614503</v>
       </c>
       <c r="C311">
         <v>90.83867845077272</v>
       </c>
       <c r="D311">
-        <v>5.808459704809863</v>
+        <v>5.829888615372312</v>
       </c>
       <c r="E311" t="s">
         <v>75</v>
@@ -5909,13 +5909,13 @@
         <v>49</v>
       </c>
       <c r="B312">
-        <v>105.3257683576553</v>
+        <v>105.3491866464562</v>
       </c>
       <c r="C312">
         <v>105.5852606224958</v>
       </c>
       <c r="D312">
-        <v>-0.2594922648405174</v>
+        <v>-0.2360739760395489</v>
       </c>
       <c r="E312" t="s">
         <v>76</v>
@@ -5926,13 +5926,13 @@
         <v>49</v>
       </c>
       <c r="B313">
-        <v>103.1016551756061</v>
+        <v>103.1245609742362</v>
       </c>
       <c r="C313">
         <v>99.91494484209504</v>
       </c>
       <c r="D313">
-        <v>3.18671033351103</v>
+        <v>3.209616132141207</v>
       </c>
       <c r="E313" t="s">
         <v>77</v>
@@ -5943,13 +5943,13 @@
         <v>49</v>
       </c>
       <c r="B314">
-        <v>97.85511466821148</v>
+        <v>97.87682294071293</v>
       </c>
       <c r="C314">
         <v>94.49754764399202</v>
       </c>
       <c r="D314">
-        <v>3.357567024219463</v>
+        <v>3.379275296720905</v>
       </c>
       <c r="E314" t="s">
         <v>78</v>
@@ -5960,13 +5960,13 @@
         <v>49</v>
       </c>
       <c r="B315">
-        <v>96.55807441827834</v>
+        <v>96.57948524123711</v>
       </c>
       <c r="C315">
         <v>92.18726691718005</v>
       </c>
       <c r="D315">
-        <v>4.370807501098284</v>
+        <v>4.392218324057055</v>
       </c>
       <c r="E315" t="s">
         <v>79</v>
@@ -5977,13 +5977,13 @@
         <v>49</v>
       </c>
       <c r="B316">
-        <v>105.4222084540784</v>
+        <v>105.4456464831587</v>
       </c>
       <c r="C316">
         <v>104.0239456230154</v>
       </c>
       <c r="D316">
-        <v>1.39826283106305</v>
+        <v>1.421700860143289</v>
       </c>
       <c r="E316" t="s">
         <v>80</v>
@@ -5994,13 +5994,13 @@
         <v>50</v>
       </c>
       <c r="B317">
-        <v>103.417056044732</v>
+        <v>103.4229624758217</v>
       </c>
       <c r="C317">
         <v>100.4741530670275</v>
       </c>
       <c r="D317">
-        <v>2.942902977704506</v>
+        <v>2.948809408794233</v>
       </c>
       <c r="E317" t="s">
         <v>74</v>
@@ -6011,13 +6011,13 @@
         <v>50</v>
       </c>
       <c r="B318">
-        <v>102.515049819947</v>
+        <v>102.5209047349927</v>
       </c>
       <c r="C318">
         <v>96.26451836385705</v>
       </c>
       <c r="D318">
-        <v>6.250531456089988</v>
+        <v>6.256386371135662</v>
       </c>
       <c r="E318" t="s">
         <v>75</v>
@@ -6028,13 +6028,13 @@
         <v>50</v>
       </c>
       <c r="B319">
-        <v>104.3269988137705</v>
+        <v>104.332957214182</v>
       </c>
       <c r="C319">
         <v>104.8744832587372</v>
       </c>
       <c r="D319">
-        <v>-0.5474844449666705</v>
+        <v>-0.5415260445552121</v>
       </c>
       <c r="E319" t="s">
         <v>76</v>
@@ -6045,13 +6045,13 @@
         <v>50</v>
       </c>
       <c r="B320">
-        <v>104.1566454336127</v>
+        <v>104.1625941046765</v>
       </c>
       <c r="C320">
         <v>102.6747395349172</v>
       </c>
       <c r="D320">
-        <v>1.481905898695587</v>
+        <v>1.487854569759321</v>
       </c>
       <c r="E320" t="s">
         <v>77</v>
@@ -6062,13 +6062,13 @@
         <v>50</v>
       </c>
       <c r="B321">
-        <v>102.495583470557</v>
+        <v>102.5014372738262</v>
       </c>
       <c r="C321">
         <v>97.45698362387363</v>
       </c>
       <c r="D321">
-        <v>5.038599846683397</v>
+        <v>5.044453649952615</v>
       </c>
       <c r="E321" t="s">
         <v>78</v>
@@ -6079,13 +6079,13 @@
         <v>50</v>
       </c>
       <c r="B322">
-        <v>102.2393652710679</v>
+        <v>102.2452044410146</v>
       </c>
       <c r="C322">
         <v>96.17056964434164</v>
       </c>
       <c r="D322">
-        <v>6.068795626726271</v>
+        <v>6.074634796672953</v>
       </c>
       <c r="E322" t="s">
         <v>79</v>
@@ -6096,13 +6096,13 @@
         <v>50</v>
       </c>
       <c r="B323">
-        <v>104.6083125868719</v>
+        <v>104.6142870538828</v>
       </c>
       <c r="C323">
         <v>104.9762708372295</v>
       </c>
       <c r="D323">
-        <v>-0.3679582503576455</v>
+        <v>-0.3619837833467727</v>
       </c>
       <c r="E323" t="s">
         <v>80</v>
@@ -6113,13 +6113,13 @@
         <v>51</v>
       </c>
       <c r="B324">
-        <v>103.3191004834655</v>
+        <v>103.325001320045</v>
       </c>
       <c r="C324">
         <v>100.2855385457774</v>
       </c>
       <c r="D324">
-        <v>3.033561937688049</v>
+        <v>3.039462774267562</v>
       </c>
       <c r="E324" t="s">
         <v>74</v>
@@ -6130,13 +6130,13 @@
         <v>51</v>
       </c>
       <c r="B325">
-        <v>102.4179486296072</v>
+        <v>102.4237979989382</v>
       </c>
       <c r="C325">
         <v>96.08072356009376</v>
       </c>
       <c r="D325">
-        <v>6.337225069513465</v>
+        <v>6.343074438844425</v>
       </c>
       <c r="E325" t="s">
         <v>75</v>
@@ -6147,13 +6147,13 @@
         <v>51</v>
       </c>
       <c r="B326">
-        <v>104.228181364165</v>
+        <v>104.2341341208414</v>
       </c>
       <c r="C326">
         <v>104.6808606087796</v>
       </c>
       <c r="D326">
-        <v>-0.4526792446146004</v>
+        <v>-0.4467264879381503</v>
       </c>
       <c r="E326" t="s">
         <v>76</v>
@@ -6164,13 +6164,13 @@
         <v>51</v>
       </c>
       <c r="B327">
-        <v>104.0579893409593</v>
+        <v>104.0639323775036</v>
       </c>
       <c r="C327">
         <v>102.4833611683356</v>
       </c>
       <c r="D327">
-        <v>1.574628172623676</v>
+        <v>1.580571209167999</v>
       </c>
       <c r="E327" t="s">
         <v>77</v>
@@ -6181,13 +6181,13 @@
         <v>51</v>
       </c>
       <c r="B328">
-        <v>102.3985007185411</v>
+        <v>102.4043489771487</v>
       </c>
       <c r="C328">
         <v>97.2720741125148</v>
       </c>
       <c r="D328">
-        <v>5.126426606026342</v>
+        <v>5.132274864633928</v>
       </c>
       <c r="E328" t="s">
         <v>78</v>
@@ -6198,13 +6198,13 @@
         <v>51</v>
       </c>
       <c r="B329">
-        <v>102.1425252062692</v>
+        <v>102.1483588454147</v>
       </c>
       <c r="C329">
         <v>95.9871152652273</v>
       </c>
       <c r="D329">
-        <v>6.155409941041896</v>
+        <v>6.161243580187431</v>
       </c>
       <c r="E329" t="s">
         <v>79</v>
@@ -6215,13 +6215,13 @@
         <v>51</v>
       </c>
       <c r="B330">
-        <v>104.5092286797825</v>
+        <v>104.5151974878403</v>
       </c>
       <c r="C330">
         <v>104.7822951307219</v>
       </c>
       <c r="D330">
-        <v>-0.2730664509393961</v>
+        <v>-0.2670976428815948</v>
       </c>
       <c r="E330" t="s">
         <v>80</v>
@@ -6232,13 +6232,13 @@
         <v>52</v>
       </c>
       <c r="B331">
-        <v>101.3034062221292</v>
+        <v>101.314421178272</v>
       </c>
       <c r="C331">
         <v>98.03634966022177</v>
       </c>
       <c r="D331">
-        <v>3.267056561907424</v>
+        <v>3.278071518050268</v>
       </c>
       <c r="E331" t="s">
         <v>74</v>
@@ -6249,13 +6249,13 @@
         <v>52</v>
       </c>
       <c r="B332">
-        <v>99.52437658569382</v>
+        <v>99.535198103786</v>
       </c>
       <c r="C332">
         <v>93.08553082322418</v>
       </c>
       <c r="D332">
-        <v>6.43884576246964</v>
+        <v>6.449667280561826</v>
       </c>
       <c r="E332" t="s">
         <v>75</v>
@@ -6266,13 +6266,13 @@
         <v>52</v>
       </c>
       <c r="B333">
-        <v>103.1142365746896</v>
+        <v>103.1254484266492</v>
       </c>
       <c r="C333">
         <v>103.2567862460835</v>
       </c>
       <c r="D333">
-        <v>-0.1425496713939651</v>
+        <v>-0.1313378194343215</v>
       </c>
       <c r="E333" t="s">
         <v>76</v>
@@ -6283,13 +6283,13 @@
         <v>52</v>
       </c>
       <c r="B334">
-        <v>102.6232513476681</v>
+        <v>102.6344098136564</v>
       </c>
       <c r="C334">
         <v>100.3058327268112</v>
       </c>
       <c r="D334">
-        <v>2.317418620856955</v>
+        <v>2.328577086845243</v>
       </c>
       <c r="E334" t="s">
         <v>77</v>
@@ -6300,13 +6300,13 @@
         <v>52</v>
       </c>
       <c r="B335">
-        <v>99.63314147777669</v>
+        <v>99.64397482212983</v>
       </c>
       <c r="C335">
         <v>94.80087043833355</v>
       </c>
       <c r="D335">
-        <v>4.832271039443143</v>
+        <v>4.843104383796287</v>
       </c>
       <c r="E335" t="s">
         <v>78</v>
@@ -6317,13 +6317,13 @@
         <v>52</v>
       </c>
       <c r="B336">
-        <v>99.11829886018315</v>
+        <v>99.12907622449509</v>
       </c>
       <c r="C336">
         <v>93.26244286823581</v>
       </c>
       <c r="D336">
-        <v>5.855855991947337</v>
+        <v>5.866633356259285</v>
       </c>
       <c r="E336" t="s">
         <v>79</v>
@@ -6334,13 +6334,13 @@
         <v>52</v>
       </c>
       <c r="B337">
-        <v>103.5366852560889</v>
+        <v>103.5479430418811</v>
       </c>
       <c r="C337">
         <v>103.058890875465</v>
       </c>
       <c r="D337">
-        <v>0.4777943806238341</v>
+        <v>0.4890521664160303</v>
       </c>
       <c r="E337" t="s">
         <v>80</v>
@@ -6351,13 +6351,13 @@
         <v>53</v>
       </c>
       <c r="B338">
-        <v>103.5150116059986</v>
+        <v>103.5209236315985</v>
       </c>
       <c r="C338">
         <v>100.6627675882776</v>
       </c>
       <c r="D338">
-        <v>2.852244017720977</v>
+        <v>2.858156043320847</v>
       </c>
       <c r="E338" t="s">
         <v>74</v>
@@ -6368,13 +6368,13 @@
         <v>53</v>
       </c>
       <c r="B339">
-        <v>102.6121510102869</v>
+        <v>102.6180114710472</v>
       </c>
       <c r="C339">
         <v>96.44831316762044</v>
       </c>
       <c r="D339">
-        <v>6.16383784266641</v>
+        <v>6.169698303426799</v>
       </c>
       <c r="E339" t="s">
         <v>75</v>
@@ -6385,13 +6385,13 @@
         <v>53</v>
       </c>
       <c r="B340">
-        <v>104.4258162633761</v>
+        <v>104.4317803075226</v>
       </c>
       <c r="C340">
         <v>105.0681059086949</v>
       </c>
       <c r="D340">
-        <v>-0.6422896453187406</v>
+        <v>-0.6363256011723166</v>
       </c>
       <c r="E340" t="s">
         <v>76</v>
@@ -6402,13 +6402,13 @@
         <v>53</v>
       </c>
       <c r="B341">
-        <v>104.2553015262662</v>
+        <v>104.2612558318494</v>
       </c>
       <c r="C341">
         <v>102.8661179014986</v>
       </c>
       <c r="D341">
-        <v>1.38918362476754</v>
+        <v>1.395137930350742</v>
       </c>
       <c r="E341" t="s">
         <v>77</v>
@@ -6419,13 +6419,13 @@
         <v>53</v>
       </c>
       <c r="B342">
-        <v>102.5926662225729</v>
+        <v>102.5985255705038</v>
       </c>
       <c r="C342">
         <v>97.64189313523245</v>
       </c>
       <c r="D342">
-        <v>4.950773087340437</v>
+        <v>4.956632435271331</v>
       </c>
       <c r="E342" t="s">
         <v>78</v>
@@ -6436,13 +6436,13 @@
         <v>53</v>
       </c>
       <c r="B343">
-        <v>102.3362053358667</v>
+        <v>102.3420500366144</v>
       </c>
       <c r="C343">
         <v>96.35402402345605</v>
       </c>
       <c r="D343">
-        <v>5.982181312410603</v>
+        <v>5.988026013158361</v>
       </c>
       <c r="E343" t="s">
         <v>79</v>
@@ -6453,13 +6453,13 @@
         <v>53</v>
       </c>
       <c r="B344">
-        <v>104.7073964939613</v>
+        <v>104.7133766199252</v>
       </c>
       <c r="C344">
         <v>105.1702465437371</v>
       </c>
       <c r="D344">
-        <v>-0.4628500497758381</v>
+        <v>-0.4568699238118938</v>
       </c>
       <c r="E344" t="s">
         <v>80</v>
@@ -6470,13 +6470,13 @@
         <v>54</v>
       </c>
       <c r="B345">
-        <v>103.5333170080907</v>
+        <v>103.5384107094634</v>
       </c>
       <c r="C345">
         <v>103.4716031667094</v>
       </c>
       <c r="D345">
-        <v>0.06171384138131941</v>
+        <v>0.06680754275406287</v>
       </c>
       <c r="E345" t="s">
         <v>74</v>
@@ -6487,13 +6487,13 @@
         <v>54</v>
       </c>
       <c r="B346">
-        <v>102.7046185903909</v>
+        <v>102.7096715209047</v>
       </c>
       <c r="C346">
         <v>102.6433987171754</v>
       </c>
       <c r="D346">
-        <v>0.06121987321550648</v>
+        <v>0.06627280372929079</v>
       </c>
       <c r="E346" t="s">
         <v>75</v>
@@ -6504,13 +6504,13 @@
         <v>54</v>
       </c>
       <c r="B347">
-        <v>104.368701990396</v>
+        <v>104.3738367915978</v>
       </c>
       <c r="C347">
         <v>104.3064901951407</v>
       </c>
       <c r="D347">
-        <v>0.06221179525530829</v>
+        <v>0.06734659645714203</v>
       </c>
       <c r="E347" t="s">
         <v>76</v>
@@ -6521,13 +6521,13 @@
         <v>54</v>
       </c>
       <c r="B348">
-        <v>104.163152996588</v>
+        <v>104.1682776850529</v>
       </c>
       <c r="C348">
         <v>104.1010637243849</v>
       </c>
       <c r="D348">
-        <v>0.0620892722030959</v>
+        <v>0.06721396066804175</v>
       </c>
       <c r="E348" t="s">
         <v>77</v>
@@ -6538,13 +6538,13 @@
         <v>54</v>
       </c>
       <c r="B349">
-        <v>102.7464262258569</v>
+        <v>102.7514812132506</v>
       </c>
       <c r="C349">
         <v>102.6851814320664</v>
       </c>
       <c r="D349">
-        <v>0.06124479379049319</v>
+        <v>0.0662997811842132</v>
       </c>
       <c r="E349" t="s">
         <v>78</v>
@@ -6555,13 +6555,13 @@
         <v>54</v>
       </c>
       <c r="B350">
-        <v>102.5256769026706</v>
+        <v>102.5307210294914</v>
       </c>
       <c r="C350">
         <v>102.4645636925008</v>
       </c>
       <c r="D350">
-        <v>0.06111321016975069</v>
+        <v>0.06615733699061366</v>
       </c>
       <c r="E350" t="s">
         <v>79</v>
@@ -6572,13 +6572,13 @@
         <v>54</v>
       </c>
       <c r="B351">
-        <v>104.5508603749446</v>
+        <v>104.5560041380964</v>
       </c>
       <c r="C351">
         <v>104.4885399992442</v>
       </c>
       <c r="D351">
-        <v>0.06232037570048021</v>
+        <v>0.06746413885228719</v>
       </c>
       <c r="E351" t="s">
         <v>80</v>
@@ -6589,13 +6589,13 @@
         <v>55</v>
       </c>
       <c r="B352">
-        <v>101.4341160863708</v>
+        <v>101.4557555094532</v>
       </c>
       <c r="C352">
         <v>101.1722336912382</v>
       </c>
       <c r="D352">
-        <v>0.2618823951325595</v>
+        <v>0.2835218182149504</v>
       </c>
       <c r="E352" t="s">
         <v>74</v>
@@ -6606,13 +6606,13 @@
         <v>55</v>
       </c>
       <c r="B353">
-        <v>96.9379650684229</v>
+        <v>96.95861044296933</v>
       </c>
       <c r="C353">
         <v>96.68811262075958</v>
       </c>
       <c r="D353">
-        <v>0.249852447663315</v>
+        <v>0.2704978222097481</v>
       </c>
       <c r="E353" t="s">
         <v>75</v>
@@ -6623,13 +6623,13 @@
         <v>55</v>
       </c>
       <c r="B354">
-        <v>106.1472036352963</v>
+        <v>106.1698853466027</v>
       </c>
       <c r="C354">
         <v>105.8727074982987</v>
       </c>
       <c r="D354">
-        <v>0.2744961369975982</v>
+        <v>0.29717784830396</v>
       </c>
       <c r="E354" t="s">
         <v>76</v>
@@ -6640,13 +6640,13 @@
         <v>55</v>
       </c>
       <c r="B355">
-        <v>103.5321103912679</v>
+        <v>103.5542118670625</v>
       </c>
       <c r="C355">
         <v>103.2646362410304</v>
       </c>
       <c r="D355">
-        <v>0.2674741502375184</v>
+        <v>0.2895756260321036</v>
       </c>
       <c r="E355" t="s">
         <v>77</v>
@@ -6657,13 +6657,13 @@
         <v>55</v>
       </c>
       <c r="B356">
-        <v>98.52214963855405</v>
+        <v>98.54314706960467</v>
       </c>
       <c r="C356">
         <v>98.26803661919055</v>
       </c>
       <c r="D356">
-        <v>0.2541130193635013</v>
+        <v>0.2751104504141182</v>
       </c>
       <c r="E356" t="s">
         <v>78</v>
@@ -6674,13 +6674,13 @@
         <v>55</v>
       </c>
       <c r="B357">
-        <v>97.23918022575904</v>
+        <v>97.25989382364037</v>
       </c>
       <c r="C357">
         <v>96.98850214681079</v>
       </c>
       <c r="D357">
-        <v>0.2506780789482548</v>
+        <v>0.2713916768295803</v>
       </c>
       <c r="E357" t="s">
         <v>79</v>
@@ -6691,13 +6691,13 @@
         <v>55</v>
       </c>
       <c r="B358">
-        <v>105.8165853384076</v>
+        <v>105.8391922627919</v>
       </c>
       <c r="C358">
         <v>105.5429942648275</v>
       </c>
       <c r="D358">
-        <v>0.2735910735800502</v>
+        <v>0.2961979979643132</v>
       </c>
       <c r="E358" t="s">
         <v>80</v>
@@ -6708,13 +6708,13 @@
         <v>56</v>
       </c>
       <c r="B359">
-        <v>99.72008187185904</v>
+        <v>99.7397588067557</v>
       </c>
       <c r="C359">
         <v>99.48192384116453</v>
       </c>
       <c r="D359">
-        <v>0.2381580306945068</v>
+        <v>0.2578349655911722</v>
       </c>
       <c r="E359" t="s">
         <v>74</v>
@@ -6725,13 +6725,13 @@
         <v>56</v>
       </c>
       <c r="B360">
-        <v>95.73116623378078</v>
+        <v>95.75002834347166</v>
       </c>
       <c r="C360">
         <v>95.50287033371336</v>
       </c>
       <c r="D360">
-        <v>0.2282959000674225</v>
+        <v>0.2471580097582944</v>
       </c>
       <c r="E360" t="s">
         <v>75</v>
@@ -6742,13 +6742,13 @@
         <v>56</v>
       </c>
       <c r="B361">
-        <v>103.8814274124459</v>
+        <v>103.9019544676952</v>
       </c>
       <c r="C361">
         <v>103.6329800610002</v>
       </c>
       <c r="D361">
-        <v>0.2484473514457477</v>
+        <v>0.26897440669498</v>
       </c>
       <c r="E361" t="s">
         <v>76</v>
@@ -6759,13 +6759,13 @@
         <v>56</v>
       </c>
       <c r="B362">
-        <v>101.7084849053729</v>
+        <v>101.7285676082941</v>
       </c>
       <c r="C362">
         <v>101.4654157138243</v>
       </c>
       <c r="D362">
-        <v>0.2430691915485852</v>
+        <v>0.2631518944698286</v>
       </c>
       <c r="E362" t="s">
         <v>77</v>
@@ -6776,13 +6776,13 @@
         <v>56</v>
       </c>
       <c r="B363">
-        <v>97.01306156451253</v>
+        <v>97.03218594982293</v>
       </c>
       <c r="C363">
         <v>96.78159124617753</v>
       </c>
       <c r="D363">
-        <v>0.2314703183349991</v>
+        <v>0.2505947036454046</v>
       </c>
       <c r="E363" t="s">
         <v>78</v>
@@ -6793,13 +6793,13 @@
         <v>56</v>
       </c>
       <c r="B364">
-        <v>95.88846145584959</v>
+        <v>95.90735607569633</v>
       </c>
       <c r="C364">
         <v>95.65977207379642</v>
       </c>
       <c r="D364">
-        <v>0.2286893820531759</v>
+        <v>0.2475840018999094</v>
       </c>
       <c r="E364" t="s">
         <v>79</v>
@@ -6810,13 +6810,13 @@
         <v>56</v>
       </c>
       <c r="B365">
-        <v>103.7103712030716</v>
+        <v>103.7308629294247</v>
       </c>
       <c r="C365">
         <v>103.4623514498608</v>
       </c>
       <c r="D365">
-        <v>0.2480197532108122</v>
+        <v>0.2685114795638412</v>
       </c>
       <c r="E365" t="s">
         <v>80</v>
@@ -6827,13 +6827,13 @@
         <v>57</v>
       </c>
       <c r="B366">
-        <v>99.87977749343608</v>
+        <v>99.89457280027143</v>
       </c>
       <c r="C366">
         <v>99.70063801409661</v>
       </c>
       <c r="D366">
-        <v>0.1791394793394687</v>
+        <v>0.1939347861748217</v>
       </c>
       <c r="E366" t="s">
         <v>74</v>
@@ -6844,13 +6844,13 @@
         <v>57</v>
       </c>
       <c r="B367">
-        <v>97.09532860905291</v>
+        <v>97.10971145225803</v>
       </c>
       <c r="C367">
         <v>96.92118318092099</v>
       </c>
       <c r="D367">
-        <v>0.1741454281319221</v>
+        <v>0.1885282713370344</v>
       </c>
       <c r="E367" t="s">
         <v>75</v>
@@ -6861,13 +6861,13 @@
         <v>57</v>
       </c>
       <c r="B368">
-        <v>102.7440773418235</v>
+        <v>102.7592969407046</v>
       </c>
       <c r="C368">
         <v>102.5598005944966</v>
       </c>
       <c r="D368">
-        <v>0.1842767473269191</v>
+        <v>0.1994963462079937</v>
       </c>
       <c r="E368" t="s">
         <v>76</v>
@@ -6878,13 +6878,13 @@
         <v>57</v>
       </c>
       <c r="B369">
-        <v>101.5426855865486</v>
+        <v>101.557727221881</v>
       </c>
       <c r="C369">
         <v>101.3605635966603</v>
       </c>
       <c r="D369">
-        <v>0.1821219898882873</v>
+        <v>0.1971636252206963</v>
       </c>
       <c r="E369" t="s">
         <v>77</v>
@@ -6895,13 +6895,13 @@
         <v>57</v>
       </c>
       <c r="B370">
-        <v>97.71820550299064</v>
+        <v>97.73268061366964</v>
       </c>
       <c r="C370">
         <v>97.54294291335439</v>
       </c>
       <c r="D370">
-        <v>0.1752625896362474</v>
+        <v>0.1897377003152485</v>
       </c>
       <c r="E370" t="s">
         <v>78</v>
@@ -6912,13 +6912,13 @@
         <v>57</v>
       </c>
       <c r="B371">
-        <v>96.96190058144863</v>
+        <v>96.97626365980584</v>
       </c>
       <c r="C371">
         <v>96.78799446329511</v>
       </c>
       <c r="D371">
-        <v>0.1739061181535249</v>
+        <v>0.1882691965107313</v>
       </c>
       <c r="E371" t="s">
         <v>79</v>
@@ -6929,13 +6929,13 @@
         <v>57</v>
       </c>
       <c r="B372">
-        <v>102.8854621486964</v>
+        <v>102.9007026910723</v>
       </c>
       <c r="C372">
         <v>102.7009318205013</v>
       </c>
       <c r="D372">
-        <v>0.1845303281950947</v>
+        <v>0.1997708705710295</v>
       </c>
       <c r="E372" t="s">
         <v>80</v>
@@ -6946,13 +6946,13 @@
         <v>58</v>
       </c>
       <c r="B373">
-        <v>100.6991911122437</v>
+        <v>100.7134265762798</v>
       </c>
       <c r="C373">
         <v>100.5268224843882</v>
       </c>
       <c r="D373">
-        <v>0.1723686278554908</v>
+        <v>0.1866040918916383</v>
       </c>
       <c r="E373" t="s">
         <v>74</v>
@@ -6963,13 +6963,13 @@
         <v>58</v>
       </c>
       <c r="B374">
-        <v>98.30951374952693</v>
+        <v>98.32341139390653</v>
       </c>
       <c r="C374">
         <v>98.14123557566097</v>
       </c>
       <c r="D374">
-        <v>0.1682781738659571</v>
+        <v>0.182175818245554</v>
       </c>
       <c r="E374" t="s">
         <v>75</v>
@@ -6980,13 +6980,13 @@
         <v>58</v>
       </c>
       <c r="B375">
-        <v>103.1469560158309</v>
+        <v>103.1615375111396</v>
       </c>
       <c r="C375">
         <v>102.9703975044909</v>
       </c>
       <c r="D375">
-        <v>0.1765585113399339</v>
+        <v>0.1911400066486664</v>
       </c>
       <c r="E375" t="s">
         <v>76</v>
@@ -6997,13 +6997,13 @@
         <v>58</v>
       </c>
       <c r="B376">
-        <v>102.3436836611559</v>
+        <v>102.358151600888</v>
       </c>
       <c r="C376">
         <v>102.1685001256428</v>
       </c>
       <c r="D376">
-        <v>0.1751835355131135</v>
+        <v>0.1896514752451566</v>
       </c>
       <c r="E376" t="s">
         <v>77</v>
@@ -7014,13 +7014,13 @@
         <v>58</v>
       </c>
       <c r="B377">
-        <v>98.58877444527434</v>
+        <v>98.60271156768297</v>
       </c>
       <c r="C377">
         <v>98.42001825582153</v>
       </c>
       <c r="D377">
-        <v>0.1687561894528073</v>
+        <v>0.182693311861442</v>
       </c>
       <c r="E377" t="s">
         <v>78</v>
@@ -7031,13 +7031,13 @@
         <v>58</v>
       </c>
       <c r="B378">
-        <v>97.88815617381852</v>
+        <v>97.9019942524702</v>
       </c>
       <c r="C378">
         <v>97.72059924534065</v>
       </c>
       <c r="D378">
-        <v>0.1675569284778646</v>
+        <v>0.1813950071295523</v>
       </c>
       <c r="E378" t="s">
         <v>79</v>
@@ -7048,13 +7048,13 @@
         <v>58</v>
       </c>
       <c r="B379">
-        <v>103.5909499884148</v>
+        <v>103.6055942494732</v>
       </c>
       <c r="C379">
         <v>103.4136314845566</v>
       </c>
       <c r="D379">
-        <v>0.1773185038581744</v>
+        <v>0.1919627649166245</v>
       </c>
       <c r="E379" t="s">
         <v>80</v>
@@ -7065,13 +7065,13 @@
         <v>59</v>
       </c>
       <c r="B380">
-        <v>101.03906787582</v>
+        <v>101.053203203101</v>
       </c>
       <c r="C380">
         <v>100.8679100974179</v>
       </c>
       <c r="D380">
-        <v>0.1711577784020761</v>
+        <v>0.1852931056831153</v>
       </c>
       <c r="E380" t="s">
         <v>74</v>
@@ -7082,13 +7082,13 @@
         <v>59</v>
       </c>
       <c r="B381">
-        <v>98.4054603417803</v>
+        <v>98.419227228366</v>
       </c>
       <c r="C381">
         <v>98.2387638319171</v>
       </c>
       <c r="D381">
-        <v>0.1666965098632005</v>
+        <v>0.1804633964489</v>
       </c>
       <c r="E381" t="s">
         <v>75</v>
@@ -7099,13 +7099,13 @@
         <v>59</v>
       </c>
       <c r="B382">
-        <v>103.7431581718859</v>
+        <v>103.7576718003739</v>
       </c>
       <c r="C382">
         <v>103.567419728822</v>
       </c>
       <c r="D382">
-        <v>0.1757384430638496</v>
+        <v>0.190252071551825</v>
       </c>
       <c r="E382" t="s">
         <v>76</v>
@@ -7116,13 +7116,13 @@
         <v>59</v>
       </c>
       <c r="B383">
-        <v>102.6475626330077</v>
+        <v>102.6619229880953</v>
       </c>
       <c r="C383">
         <v>102.4736801027349</v>
       </c>
       <c r="D383">
-        <v>0.1738825302728202</v>
+        <v>0.1882428853604239</v>
       </c>
       <c r="E383" t="s">
         <v>77</v>
@@ -7133,13 +7133,13 @@
         <v>59</v>
       </c>
       <c r="B384">
-        <v>98.95876145272331</v>
+        <v>98.97260574592458</v>
       </c>
       <c r="C384">
         <v>98.79112766393494</v>
       </c>
       <c r="D384">
-        <v>0.1676337887883648</v>
+        <v>0.1814780819896384</v>
       </c>
       <c r="E384" t="s">
         <v>78</v>
@@ -7150,13 +7150,13 @@
         <v>59</v>
       </c>
       <c r="B385">
-        <v>98.2470858798995</v>
+        <v>98.26083060995799</v>
       </c>
       <c r="C385">
         <v>98.08065765260874</v>
       </c>
       <c r="D385">
-        <v>0.1664282272907656</v>
+        <v>0.1801729573492565</v>
       </c>
       <c r="E385" t="s">
         <v>79</v>
@@ -7167,13 +7167,13 @@
         <v>59</v>
       </c>
       <c r="B386">
-        <v>103.9103923112208</v>
+        <v>103.9249293357015</v>
       </c>
       <c r="C386">
         <v>103.7343705775016</v>
       </c>
       <c r="D386">
-        <v>0.1760217337192387</v>
+        <v>0.1905587581998844</v>
       </c>
       <c r="E386" t="s">
         <v>80</v>
@@ -7184,13 +7184,13 @@
         <v>60</v>
       </c>
       <c r="B387">
-        <v>101.254587535802</v>
+        <v>101.2682032608185</v>
       </c>
       <c r="C387">
         <v>101.0897154979228</v>
       </c>
       <c r="D387">
-        <v>0.1648720378792774</v>
+        <v>0.1784877628957133</v>
       </c>
       <c r="E387" t="s">
         <v>74</v>
@@ -7201,13 +7201,13 @@
         <v>60</v>
       </c>
       <c r="B388">
-        <v>98.73431290498024</v>
+        <v>98.74758972815361</v>
       </c>
       <c r="C388">
         <v>98.5735446101956</v>
       </c>
       <c r="D388">
-        <v>0.1607682947846456</v>
+        <v>0.1740451179580162</v>
       </c>
       <c r="E388" t="s">
         <v>75</v>
@@ -7218,13 +7218,13 @@
         <v>60</v>
       </c>
       <c r="B389">
-        <v>103.8391942516699</v>
+        <v>103.853157529278</v>
       </c>
       <c r="C389">
         <v>103.6701137192746</v>
       </c>
       <c r="D389">
-        <v>0.1690805323952134</v>
+        <v>0.1830438100033973</v>
       </c>
       <c r="E389" t="s">
         <v>76</v>
@@ -7235,13 +7235,13 @@
         <v>60</v>
       </c>
       <c r="B390">
-        <v>102.8158812784443</v>
+        <v>102.8297069509485</v>
       </c>
       <c r="C390">
         <v>102.6484669984075</v>
       </c>
       <c r="D390">
-        <v>0.1674142800367946</v>
+        <v>0.1812399525409489</v>
       </c>
       <c r="E390" t="s">
         <v>77</v>
@@ -7252,13 +7252,13 @@
         <v>60</v>
       </c>
       <c r="B391">
-        <v>99.24160250656446</v>
+        <v>99.2549475450739</v>
       </c>
       <c r="C391">
         <v>99.08000819616468</v>
       </c>
       <c r="D391">
-        <v>0.1615943103997779</v>
+        <v>0.1749393489092199</v>
       </c>
       <c r="E391" t="s">
         <v>78</v>
@@ -7269,13 +7269,13 @@
         <v>60</v>
       </c>
       <c r="B392">
-        <v>98.56280198611475</v>
+        <v>98.57605574617989</v>
       </c>
       <c r="C392">
         <v>98.40231296119231</v>
       </c>
       <c r="D392">
-        <v>0.1604890249224411</v>
+        <v>0.1737427849875814</v>
       </c>
       <c r="E392" t="s">
         <v>79</v>
@@ -7286,13 +7286,13 @@
         <v>60</v>
       </c>
       <c r="B393">
-        <v>104.0198867163876</v>
+        <v>104.0338742917483</v>
       </c>
       <c r="C393">
         <v>103.8505119638922</v>
       </c>
       <c r="D393">
-        <v>0.1693747524953579</v>
+        <v>0.1833623278560594</v>
       </c>
       <c r="E393" t="s">
         <v>80</v>
@@ -7303,13 +7303,13 @@
         <v>61</v>
       </c>
       <c r="B394">
-        <v>103.4189487253326</v>
+        <v>103.426868564517</v>
       </c>
       <c r="C394">
         <v>103.323011430116</v>
       </c>
       <c r="D394">
-        <v>0.09593729521658645</v>
+        <v>0.1038571344009966</v>
       </c>
       <c r="E394" t="s">
         <v>74</v>
@@ -7320,13 +7320,13 @@
         <v>61</v>
       </c>
       <c r="B395">
-        <v>102.1844711909779</v>
+        <v>102.1922964936807</v>
       </c>
       <c r="C395">
         <v>102.0896790672905</v>
       </c>
       <c r="D395">
-        <v>0.09479212368746914</v>
+        <v>0.1026174263902391</v>
       </c>
       <c r="E395" t="s">
         <v>75</v>
@@ -7337,13 +7337,13 @@
         <v>61</v>
       </c>
       <c r="B396">
-        <v>104.6683398249782</v>
+        <v>104.6763553427274</v>
       </c>
       <c r="C396">
         <v>104.5712435235616</v>
       </c>
       <c r="D396">
-        <v>0.09709630141657044</v>
+        <v>0.1051118191657565</v>
       </c>
       <c r="E396" t="s">
         <v>76</v>
@@ -7354,13 +7354,13 @@
         <v>61</v>
       </c>
       <c r="B397">
-        <v>104.3979469026787</v>
+        <v>104.4059417136959</v>
       </c>
       <c r="C397">
         <v>104.3011014331061</v>
       </c>
       <c r="D397">
-        <v>0.09684546957259954</v>
+        <v>0.1048402805897979</v>
       </c>
       <c r="E397" t="s">
         <v>77</v>
@@ -7371,13 +7371,13 @@
         <v>61</v>
       </c>
       <c r="B398">
-        <v>102.1934854213856</v>
+        <v>102.2013114143995</v>
       </c>
       <c r="C398">
         <v>102.0986849355856</v>
       </c>
       <c r="D398">
-        <v>0.09480048579997913</v>
+        <v>0.1026264788139173</v>
       </c>
       <c r="E398" t="s">
         <v>78</v>
@@ -7388,13 +7388,13 @@
         <v>61</v>
       </c>
       <c r="B399">
-        <v>101.8406091261763</v>
+        <v>101.8484080958686</v>
       </c>
       <c r="C399">
         <v>101.7461359884854</v>
       </c>
       <c r="D399">
-        <v>0.0944731376908976</v>
+        <v>0.1022721073832429</v>
       </c>
       <c r="E399" t="s">
         <v>79</v>
@@ -7405,13 +7405,13 @@
         <v>61</v>
       </c>
       <c r="B400">
-        <v>105.021749646074</v>
+        <v>105.0297922280023</v>
       </c>
       <c r="C400">
         <v>104.9243255016195</v>
       </c>
       <c r="D400">
-        <v>0.09742414445457825</v>
+        <v>0.1054667263828719</v>
       </c>
       <c r="E400" t="s">
         <v>80</v>
@@ -7422,13 +7422,13 @@
         <v>62</v>
       </c>
       <c r="B401">
-        <v>100.4744615424649</v>
+        <v>100.4895367593306</v>
       </c>
       <c r="C401">
         <v>98.30911163888629</v>
       </c>
       <c r="D401">
-        <v>2.165349903578559</v>
+        <v>2.18042512044434</v>
       </c>
       <c r="E401" t="s">
         <v>74</v>
@@ -7439,13 +7439,13 @@
         <v>62</v>
       </c>
       <c r="B402">
-        <v>97.95570538619775</v>
+        <v>97.97040268817142</v>
       </c>
       <c r="C402">
         <v>92.68330045745356</v>
       </c>
       <c r="D402">
-        <v>5.272404928744194</v>
+        <v>5.287102230717863</v>
       </c>
       <c r="E402" t="s">
         <v>75</v>
@@ -7456,13 +7456,13 @@
         <v>62</v>
       </c>
       <c r="B403">
-        <v>103.0579830184213</v>
+        <v>103.0734458675862</v>
       </c>
       <c r="C403">
         <v>104.2833693902022</v>
       </c>
       <c r="D403">
-        <v>-1.2253863717809</v>
+        <v>-1.209923522616037</v>
       </c>
       <c r="E403" t="s">
         <v>76</v>
@@ -7473,13 +7473,13 @@
         <v>62</v>
       </c>
       <c r="B404">
-        <v>102.1999068201647</v>
+        <v>102.215240923332</v>
       </c>
       <c r="C404">
         <v>100.6258899200998</v>
       </c>
       <c r="D404">
-        <v>1.574016900064947</v>
+        <v>1.589351003232252</v>
       </c>
       <c r="E404" t="s">
         <v>77</v>
@@ -7490,13 +7490,13 @@
         <v>62</v>
       </c>
       <c r="B405">
-        <v>98.25270944553792</v>
+        <v>98.26745131008532</v>
       </c>
       <c r="C405">
         <v>94.87614582462668</v>
       </c>
       <c r="D405">
-        <v>3.376563620911242</v>
+        <v>3.391305485458645</v>
       </c>
       <c r="E405" t="s">
         <v>78</v>
@@ -7507,13 +7507,13 @@
         <v>62</v>
       </c>
       <c r="B406">
-        <v>97.50252012726173</v>
+        <v>97.5171494331899</v>
       </c>
       <c r="C406">
         <v>93.08656937297501</v>
       </c>
       <c r="D406">
-        <v>4.415950754286726</v>
+        <v>4.430580060214893</v>
       </c>
       <c r="E406" t="s">
         <v>79</v>
@@ -7524,13 +7524,13 @@
         <v>62</v>
       </c>
       <c r="B407">
-        <v>103.5369897011068</v>
+        <v>103.5525244205709</v>
       </c>
       <c r="C407">
         <v>103.8283761944696</v>
       </c>
       <c r="D407">
-        <v>-0.2913864933628361</v>
+        <v>-0.2758517738987081</v>
       </c>
       <c r="E407" t="s">
         <v>80</v>
@@ -7541,13 +7541,13 @@
         <v>63</v>
       </c>
       <c r="B408">
-        <v>100.3517748859405</v>
+        <v>100.367164446419</v>
       </c>
       <c r="C408">
         <v>98.16450043735968</v>
       </c>
       <c r="D408">
-        <v>2.187274448580808</v>
+        <v>2.202664009059362</v>
       </c>
       <c r="E408" t="s">
         <v>74</v>
@@ -7558,13 +7558,13 @@
         <v>63</v>
       </c>
       <c r="B409">
-        <v>97.76975357358961</v>
+        <v>97.78474716525558</v>
       </c>
       <c r="C409">
         <v>92.48424971221009</v>
       </c>
       <c r="D409">
-        <v>5.285503861379524</v>
+        <v>5.300497453045494</v>
       </c>
       <c r="E409" t="s">
         <v>75</v>
@@ -7575,13 +7575,13 @@
         <v>63</v>
       </c>
       <c r="B410">
-        <v>103.0019853244142</v>
+        <v>103.0177813109262</v>
       </c>
       <c r="C410">
         <v>104.2005836944579</v>
       </c>
       <c r="D410">
-        <v>-1.198598370043683</v>
+        <v>-1.182802383531623</v>
       </c>
       <c r="E410" t="s">
         <v>76</v>
@@ -7592,13 +7592,13 @@
         <v>63</v>
       </c>
       <c r="B411">
-        <v>102.1051131379343</v>
+        <v>102.120771583593</v>
       </c>
       <c r="C411">
         <v>100.4763502446808</v>
       </c>
       <c r="D411">
-        <v>1.628762893253494</v>
+        <v>1.64442133891221</v>
       </c>
       <c r="E411" t="s">
         <v>77</v>
@@ -7609,13 +7609,13 @@
         <v>63</v>
       </c>
       <c r="B412">
-        <v>98.09004951673442</v>
+        <v>98.10509222774876</v>
       </c>
       <c r="C412">
         <v>94.72484684445956</v>
       </c>
       <c r="D412">
-        <v>3.365202672274862</v>
+        <v>3.380245383289193</v>
       </c>
       <c r="E412" t="s">
         <v>78</v>
@@ -7626,13 +7626,13 @@
         <v>63</v>
       </c>
       <c r="B413">
-        <v>97.31996051759789</v>
+        <v>97.33488513073863</v>
       </c>
       <c r="C413">
         <v>92.91572039091145</v>
       </c>
       <c r="D413">
-        <v>4.404240126686446</v>
+        <v>4.419164739827181</v>
       </c>
       <c r="E413" t="s">
         <v>79</v>
@@ -7643,13 +7643,13 @@
         <v>63</v>
       </c>
       <c r="B414">
-        <v>103.4780395429515</v>
+        <v>103.4939085352992</v>
       </c>
       <c r="C414">
         <v>103.7134087577081</v>
       </c>
       <c r="D414">
-        <v>-0.2353692147566733</v>
+        <v>-0.2195002224089393</v>
       </c>
       <c r="E414" t="s">
         <v>80</v>
@@ -7660,13 +7660,13 @@
         <v>64</v>
       </c>
       <c r="B415">
-        <v>104.7591816758067</v>
+        <v>104.7611432656351</v>
       </c>
       <c r="C415">
         <v>99.52884070917594</v>
       </c>
       <c r="D415">
-        <v>5.230340966630806</v>
+        <v>5.232302556459132</v>
       </c>
       <c r="E415" t="s">
         <v>74</v>
@@ -7677,13 +7677,13 @@
         <v>64</v>
       </c>
       <c r="B416">
-        <v>104.4382215282078</v>
+        <v>104.4401771081365</v>
       </c>
       <c r="C416">
         <v>92.17851851274344</v>
       </c>
       <c r="D416">
-        <v>12.25970301546435</v>
+        <v>12.26165859539309</v>
       </c>
       <c r="E416" t="s">
         <v>75</v>
@@ -7694,13 +7694,13 @@
         <v>64</v>
       </c>
       <c r="B417">
-        <v>105.0811281999912</v>
+        <v>105.0830958181887</v>
       </c>
       <c r="C417">
         <v>107.506477727425</v>
       </c>
       <c r="D417">
-        <v>-2.425349527433752</v>
+        <v>-2.423381909236227</v>
       </c>
       <c r="E417" t="s">
         <v>76</v>
@@ -7711,13 +7711,13 @@
         <v>64</v>
       </c>
       <c r="B418">
-        <v>104.9929971580358</v>
+        <v>104.9949631260013</v>
       </c>
       <c r="C418">
         <v>101.4309263662164</v>
       </c>
       <c r="D418">
-        <v>3.562070791819423</v>
+        <v>3.564036759784941</v>
       </c>
       <c r="E418" t="s">
         <v>77</v>
@@ -7728,13 +7728,13 @@
         <v>64</v>
       </c>
       <c r="B419">
-        <v>104.4654847300322</v>
+        <v>104.4674408204577</v>
       </c>
       <c r="C419">
         <v>96.22475480001103</v>
       </c>
       <c r="D419">
-        <v>8.240729930021189</v>
+        <v>8.242686020446641</v>
       </c>
       <c r="E419" t="s">
         <v>78</v>
@@ -7745,13 +7745,13 @@
         <v>64</v>
       </c>
       <c r="B420">
-        <v>104.3823896810694</v>
+        <v>104.3843442155606</v>
       </c>
       <c r="C420">
         <v>93.95293434970716</v>
       </c>
       <c r="D420">
-        <v>10.42945533136228</v>
+        <v>10.43140986585345</v>
       </c>
       <c r="E420" t="s">
         <v>79</v>
@@ -7762,13 +7762,13 @@
         <v>64</v>
       </c>
       <c r="B421">
-        <v>105.1373337870132</v>
+        <v>105.1393024576465</v>
       </c>
       <c r="C421">
         <v>105.4552444485367</v>
       </c>
       <c r="D421">
-        <v>-0.3179106615234417</v>
+        <v>-0.3159419908901668</v>
       </c>
       <c r="E421" t="s">
         <v>80</v>
@@ -7779,13 +7779,13 @@
         <v>65</v>
       </c>
       <c r="B422">
-        <v>104.8147385647942</v>
+        <v>104.8163562272807</v>
       </c>
       <c r="C422">
         <v>99.49410837998029</v>
       </c>
       <c r="D422">
-        <v>5.320630184813922</v>
+        <v>5.32224784730046</v>
       </c>
       <c r="E422" t="s">
         <v>74</v>
@@ -7796,13 +7796,13 @@
         <v>65</v>
       </c>
       <c r="B423">
-        <v>104.5508806638169</v>
+        <v>104.5524942540418</v>
       </c>
       <c r="C423">
         <v>92.18312431965747</v>
       </c>
       <c r="D423">
-        <v>12.36775634415939</v>
+        <v>12.36936993438438</v>
       </c>
       <c r="E423" t="s">
         <v>75</v>
@@ -7813,13 +7813,13 @@
         <v>65</v>
       </c>
       <c r="B424">
-        <v>105.0792623711324</v>
+        <v>105.0808841161577</v>
       </c>
       <c r="C424">
         <v>107.4259278384135</v>
       </c>
       <c r="D424">
-        <v>-2.346665467281127</v>
+        <v>-2.345043722255795</v>
       </c>
       <c r="E424" t="s">
         <v>76</v>
@@ -7830,13 +7830,13 @@
         <v>65</v>
       </c>
       <c r="B425">
-        <v>105.0068648779038</v>
+        <v>105.0084855055795</v>
       </c>
       <c r="C425">
         <v>101.401378420365</v>
       </c>
       <c r="D425">
-        <v>3.605486457538774</v>
+        <v>3.607107085214494</v>
       </c>
       <c r="E425" t="s">
         <v>77</v>
@@ -7847,13 +7847,13 @@
         <v>65</v>
       </c>
       <c r="B426">
-        <v>104.5732990718542</v>
+        <v>104.5749130080746</v>
       </c>
       <c r="C426">
         <v>96.19331285171384</v>
       </c>
       <c r="D426">
-        <v>8.379986220140395</v>
+        <v>8.381600156360776</v>
       </c>
       <c r="E426" t="s">
         <v>78</v>
@@ -7864,13 +7864,13 @@
         <v>65</v>
       </c>
       <c r="B427">
-        <v>104.5049671255889</v>
+        <v>104.5065800072054</v>
       </c>
       <c r="C427">
         <v>93.93554191410101</v>
       </c>
       <c r="D427">
-        <v>10.56942521148788</v>
+        <v>10.57103809310443</v>
       </c>
       <c r="E427" t="s">
         <v>79</v>
@@ -7881,13 +7881,13 @@
         <v>65</v>
       </c>
       <c r="B428">
-        <v>105.1254282220248</v>
+        <v>105.1270506795527</v>
       </c>
       <c r="C428">
         <v>105.401360313686</v>
       </c>
       <c r="D428">
-        <v>-0.2759320916611756</v>
+        <v>-0.2743096341333171</v>
       </c>
       <c r="E428" t="s">
         <v>80</v>
@@ -7898,13 +7898,13 @@
         <v>66</v>
       </c>
       <c r="B429">
-        <v>100.2647415198301</v>
+        <v>100.2803532611757</v>
       </c>
       <c r="C429">
         <v>100.0757261543504</v>
       </c>
       <c r="D429">
-        <v>0.1890153654796762</v>
+        <v>0.2046271068253418</v>
       </c>
       <c r="E429" t="s">
         <v>74</v>
@@ -7915,13 +7915,13 @@
         <v>66</v>
       </c>
       <c r="B430">
-        <v>97.29880482311761</v>
+        <v>97.31395475270523</v>
       </c>
       <c r="C430">
         <v>97.11538073130228</v>
       </c>
       <c r="D430">
-        <v>0.1834240918153256</v>
+        <v>0.1985740214029477</v>
       </c>
       <c r="E430" t="s">
         <v>75</v>
@@ -7932,13 +7932,13 @@
         <v>66</v>
       </c>
       <c r="B431">
-        <v>103.3210881707542</v>
+        <v>103.3371758011577</v>
       </c>
       <c r="C431">
         <v>103.1263110941237</v>
       </c>
       <c r="D431">
-        <v>0.1947770766305155</v>
+        <v>0.2108647070340339</v>
       </c>
       <c r="E431" t="s">
         <v>76</v>
@@ -7949,13 +7949,13 @@
         <v>66</v>
       </c>
       <c r="B432">
-        <v>101.9980881079738</v>
+        <v>102.0139697403918</v>
       </c>
       <c r="C432">
         <v>101.805805101907</v>
       </c>
       <c r="D432">
-        <v>0.192283006066873</v>
+        <v>0.208164638484817</v>
       </c>
       <c r="E432" t="s">
         <v>77</v>
@@ -7966,13 +7966,13 @@
         <v>66</v>
       </c>
       <c r="B433">
-        <v>98.00023728224485</v>
+        <v>98.01549642851177</v>
       </c>
       <c r="C433">
         <v>97.81549087601859</v>
       </c>
       <c r="D433">
-        <v>0.1847464062262674</v>
+        <v>0.200005552493181</v>
       </c>
       <c r="E433" t="s">
         <v>78</v>
@@ -7983,13 +7983,13 @@
         <v>66</v>
       </c>
       <c r="B434">
-        <v>97.19072700950906</v>
+        <v>97.20586011081936</v>
       </c>
       <c r="C434">
         <v>97.00750666197243</v>
       </c>
       <c r="D434">
-        <v>0.1832203475366327</v>
+        <v>0.1983534488469303</v>
       </c>
       <c r="E434" t="s">
         <v>79</v>
@@ -8000,13 +8000,13 @@
         <v>66</v>
       </c>
       <c r="B435">
-        <v>103.4359830547904</v>
+        <v>103.4520885749245</v>
       </c>
       <c r="C435">
         <v>103.2409893825933</v>
       </c>
       <c r="D435">
-        <v>0.1949936721971</v>
+        <v>0.2110991923312469</v>
       </c>
       <c r="E435" t="s">
         <v>80</v>
@@ -8017,13 +8017,13 @@
         <v>67</v>
       </c>
       <c r="B436">
-        <v>102.5779142019728</v>
+        <v>102.5867058018612</v>
       </c>
       <c r="C436">
         <v>99.73218787064766</v>
       </c>
       <c r="D436">
-        <v>2.845726331325181</v>
+        <v>2.854517931213493</v>
       </c>
       <c r="E436" t="s">
         <v>74</v>
@@ -8034,13 +8034,13 @@
         <v>67</v>
       </c>
       <c r="B437">
-        <v>101.1939816022151</v>
+        <v>101.2026545900047</v>
       </c>
       <c r="C437">
         <v>95.10009706873075</v>
       </c>
       <c r="D437">
-        <v>6.093884533484371</v>
+        <v>6.102557521273937</v>
       </c>
       <c r="E437" t="s">
         <v>75</v>
@@ -8051,13 +8051,13 @@
         <v>67</v>
       </c>
       <c r="B438">
-        <v>103.9807735146669</v>
+        <v>103.9896853487974</v>
       </c>
       <c r="C438">
         <v>104.5967030541549</v>
       </c>
       <c r="D438">
-        <v>-0.6159295394879223</v>
+        <v>-0.6070177053575065</v>
       </c>
       <c r="E438" t="s">
         <v>76</v>
@@ -8068,13 +8068,13 @@
         <v>67</v>
       </c>
       <c r="B439">
-        <v>103.6560079834012</v>
+        <v>103.664891982996</v>
       </c>
       <c r="C439">
         <v>101.9952176634393</v>
       </c>
       <c r="D439">
-        <v>1.660790319961905</v>
+        <v>1.669674319556691</v>
       </c>
       <c r="E439" t="s">
         <v>77</v>
@@ -8085,13 +8085,13 @@
         <v>67</v>
       </c>
       <c r="B440">
-        <v>101.2246742563808</v>
+        <v>101.233349874732</v>
       </c>
       <c r="C440">
         <v>96.56826382741338</v>
       </c>
       <c r="D440">
-        <v>4.656410428967405</v>
+        <v>4.665086047318653</v>
       </c>
       <c r="E440" t="s">
         <v>78</v>
@@ -8102,13 +8102,13 @@
         <v>67</v>
       </c>
       <c r="B441">
-        <v>100.8277434748535</v>
+        <v>100.8363850736339</v>
       </c>
       <c r="C441">
         <v>95.14020374119367</v>
       </c>
       <c r="D441">
-        <v>5.68753973365979</v>
+        <v>5.696181332440204</v>
       </c>
       <c r="E441" t="s">
         <v>79</v>
@@ -8119,13 +8119,13 @@
         <v>67</v>
       </c>
       <c r="B442">
-        <v>104.3584644404103</v>
+        <v>104.3674086451298</v>
       </c>
       <c r="C442">
         <v>104.5510748344042</v>
       </c>
       <c r="D442">
-        <v>-0.1926103939938884</v>
+        <v>-0.1836661892744615</v>
       </c>
       <c r="E442" t="s">
         <v>80</v>
@@ -8136,13 +8136,13 @@
         <v>68</v>
       </c>
       <c r="B443">
-        <v>100.9640645012595</v>
+        <v>100.9876626674387</v>
       </c>
       <c r="C443">
         <v>100.6785130747671</v>
       </c>
       <c r="D443">
-        <v>0.2855514264924466</v>
+        <v>0.3091495926716448</v>
       </c>
       <c r="E443" t="s">
         <v>74</v>
@@ -8153,13 +8153,13 @@
         <v>68</v>
       </c>
       <c r="B444">
-        <v>95.91223280746347</v>
+        <v>95.9346162233509</v>
       </c>
       <c r="C444">
         <v>95.64138034563754</v>
       </c>
       <c r="D444">
-        <v>0.2708524618259247</v>
+        <v>0.2932358777133572</v>
       </c>
       <c r="E444" t="s">
         <v>75</v>
@@ -8170,13 +8170,13 @@
         <v>68</v>
       </c>
       <c r="B445">
-        <v>106.290932391227</v>
+        <v>106.31581194559</v>
       </c>
       <c r="C445">
         <v>105.9898756579987</v>
       </c>
       <c r="D445">
-        <v>0.3010567332282506</v>
+        <v>0.3259362875912757</v>
       </c>
       <c r="E445" t="s">
         <v>76</v>
@@ -8187,13 +8187,13 @@
         <v>68</v>
       </c>
       <c r="B446">
-        <v>103.131769602359</v>
+        <v>103.1558855914455</v>
       </c>
       <c r="C446">
         <v>102.8399522904718</v>
       </c>
       <c r="D446">
-        <v>0.2918173118872005</v>
+        <v>0.3159333009736969</v>
       </c>
       <c r="E446" t="s">
         <v>77</v>
@@ -8204,13 +8204,13 @@
         <v>68</v>
       </c>
       <c r="B447">
-        <v>97.87536039640902</v>
+        <v>97.89821926664135</v>
       </c>
       <c r="C447">
         <v>97.59875476764918</v>
       </c>
       <c r="D447">
-        <v>0.2766056287598389</v>
+        <v>0.2994644989921653</v>
       </c>
       <c r="E447" t="s">
         <v>78</v>
@@ -8221,13 +8221,13 @@
         <v>68</v>
       </c>
       <c r="B448">
-        <v>96.41318916961117</v>
+        <v>96.43569609412987</v>
       </c>
       <c r="C448">
         <v>96.14084222264673</v>
       </c>
       <c r="D448">
-        <v>0.2723469469644471</v>
+        <v>0.2948538714831415</v>
       </c>
       <c r="E448" t="s">
         <v>79</v>
@@ -8238,13 +8238,13 @@
         <v>68</v>
       </c>
       <c r="B449">
-        <v>105.7355851697393</v>
+        <v>105.7603279511082</v>
       </c>
       <c r="C449">
         <v>105.4361834246069</v>
       </c>
       <c r="D449">
-        <v>0.2994017451324567</v>
+        <v>0.3241445265013283</v>
       </c>
       <c r="E449" t="s">
         <v>80</v>
@@ -8255,13 +8255,13 @@
         <v>69</v>
       </c>
       <c r="B450">
-        <v>97.88550710663453</v>
+        <v>97.91270195384118</v>
       </c>
       <c r="C450">
         <v>97.5565230893941</v>
       </c>
       <c r="D450">
-        <v>0.3289840172404297</v>
+        <v>0.3561788644470738</v>
       </c>
       <c r="E450" t="s">
         <v>74</v>
@@ -8272,13 +8272,13 @@
         <v>69</v>
       </c>
       <c r="B451">
-        <v>91.63783919535435</v>
+        <v>91.663272058541</v>
       </c>
       <c r="C451">
         <v>91.33017009728241</v>
       </c>
       <c r="D451">
-        <v>0.3076690980719405</v>
+        <v>0.3331019612585919</v>
       </c>
       <c r="E451" t="s">
         <v>75</v>
@@ -8289,13 +8289,13 @@
         <v>69</v>
       </c>
       <c r="B452">
-        <v>104.5676824444478</v>
+        <v>104.5967626482247</v>
       </c>
       <c r="C452">
         <v>104.2158910662863</v>
       </c>
       <c r="D452">
-        <v>0.3517913781615221</v>
+        <v>0.3808715819383934</v>
       </c>
       <c r="E452" t="s">
         <v>76</v>
@@ -8306,13 +8306,13 @@
         <v>69</v>
       </c>
       <c r="B453">
-        <v>100.0245483087293</v>
+        <v>100.0523412286869</v>
       </c>
       <c r="C453">
         <v>99.68832927640418</v>
       </c>
       <c r="D453">
-        <v>0.3362190323251042</v>
+        <v>0.3640119522826808</v>
       </c>
       <c r="E453" t="s">
         <v>77</v>
@@ -8323,13 +8323,13 @@
         <v>69</v>
       </c>
       <c r="B454">
-        <v>94.58374311371699</v>
+        <v>94.61001183121718</v>
       </c>
       <c r="C454">
         <v>94.26596265180898</v>
       </c>
       <c r="D454">
-        <v>0.3177804619080149</v>
+        <v>0.3440491794082021</v>
       </c>
       <c r="E454" t="s">
         <v>78</v>
@@ -8340,13 +8340,13 @@
         <v>69</v>
       </c>
       <c r="B455">
-        <v>92.71458896895098</v>
+        <v>92.74032998183951</v>
       </c>
       <c r="C455">
         <v>92.40319220250726</v>
       </c>
       <c r="D455">
-        <v>0.3113967664437212</v>
+        <v>0.3371377793322523</v>
       </c>
       <c r="E455" t="s">
         <v>79</v>
@@ -8357,13 +8357,13 @@
         <v>69</v>
       </c>
       <c r="B456">
-        <v>103.3484278489289</v>
+        <v>103.3771591911515</v>
       </c>
       <c r="C456">
         <v>103.000856628797</v>
       </c>
       <c r="D456">
-        <v>0.3475712201319396</v>
+        <v>0.3763025623544962</v>
       </c>
       <c r="E456" t="s">
         <v>80</v>
@@ -8374,13 +8374,13 @@
         <v>70</v>
       </c>
       <c r="B457">
-        <v>102.9967094206872</v>
+        <v>103.0035753346285</v>
       </c>
       <c r="C457">
         <v>98.07963942065354</v>
       </c>
       <c r="D457">
-        <v>4.917070000033704</v>
+        <v>4.923935913974958</v>
       </c>
       <c r="E457" t="s">
         <v>74</v>
@@ -8391,13 +8391,13 @@
         <v>70</v>
       </c>
       <c r="B458">
-        <v>101.9540665407483</v>
+        <v>101.9608629505634</v>
       </c>
       <c r="C458">
         <v>90.94896631136262</v>
       </c>
       <c r="D458">
-        <v>11.0051002293857</v>
+        <v>11.01189663920078</v>
       </c>
       <c r="E458" t="s">
         <v>75</v>
@@ -8408,13 +8408,13 @@
         <v>70</v>
       </c>
       <c r="B459">
-        <v>104.050014986402</v>
+        <v>104.0569511152599</v>
       </c>
       <c r="C459">
         <v>105.8002534333668</v>
       </c>
       <c r="D459">
-        <v>-1.750238446964815</v>
+        <v>-1.743302318106899</v>
       </c>
       <c r="E459" t="s">
         <v>76</v>
@@ -8425,13 +8425,13 @@
         <v>70</v>
       </c>
       <c r="B460">
-        <v>103.8529740503932</v>
+        <v>103.859897044209</v>
       </c>
       <c r="C460">
         <v>100.0912312150907</v>
       </c>
       <c r="D460">
-        <v>3.761742835302456</v>
+        <v>3.768665829118319</v>
       </c>
       <c r="E460" t="s">
         <v>77</v>
@@ -8442,13 +8442,13 @@
         <v>70</v>
       </c>
       <c r="B461">
-        <v>101.9282208714518</v>
+        <v>101.9350155583561</v>
       </c>
       <c r="C461">
         <v>94.61851075981637</v>
       </c>
       <c r="D461">
-        <v>7.309710111635397</v>
+        <v>7.316504798539711</v>
       </c>
       <c r="E461" t="s">
         <v>78</v>
@@ -8459,13 +8459,13 @@
         <v>70</v>
       </c>
       <c r="B462">
-        <v>101.627026934455</v>
+        <v>101.6338015433232</v>
       </c>
       <c r="C462">
         <v>92.27044586073794</v>
       </c>
       <c r="D462">
-        <v>9.356581073717095</v>
+        <v>9.363355682585251</v>
       </c>
       <c r="E462" t="s">
         <v>79</v>
@@ -8476,13 +8476,13 @@
         <v>70</v>
       </c>
       <c r="B463">
-        <v>104.3848518596475</v>
+        <v>104.3918103092297</v>
       </c>
       <c r="C463">
         <v>104.2691093193437</v>
       </c>
       <c r="D463">
-        <v>0.1157425403037848</v>
+        <v>0.1227009898859848</v>
       </c>
       <c r="E463" t="s">
         <v>80</v>
@@ -8493,13 +8493,13 @@
         <v>71</v>
       </c>
       <c r="B464">
-        <v>100.0846406077867</v>
+        <v>100.0999419849726</v>
       </c>
       <c r="C464">
         <v>99.89937947441882</v>
       </c>
       <c r="D464">
-        <v>0.1852611333678738</v>
+        <v>0.2005625105537376</v>
       </c>
       <c r="E464" t="s">
         <v>74</v>
@@ -8510,13 +8510,13 @@
         <v>71</v>
       </c>
       <c r="B465">
-        <v>97.18791486313323</v>
+        <v>97.20277337622977</v>
       </c>
       <c r="C465">
         <v>97.00801569830766</v>
       </c>
       <c r="D465">
-        <v>0.1798991648255708</v>
+        <v>0.1947576779221123</v>
       </c>
       <c r="E465" t="s">
         <v>75</v>
@@ -8527,13 +8527,13 @@
         <v>71</v>
       </c>
       <c r="B466">
-        <v>103.0677044537521</v>
+        <v>103.0834618947735</v>
       </c>
       <c r="C466">
         <v>102.8769215361657</v>
       </c>
       <c r="D466">
-        <v>0.1907829175863611</v>
+        <v>0.2065403586077537</v>
       </c>
       <c r="E466" t="s">
         <v>76</v>
@@ -8544,13 +8544,13 @@
         <v>71</v>
       </c>
       <c r="B467">
-        <v>101.7914529005441</v>
+        <v>101.8070152226513</v>
       </c>
       <c r="C467">
         <v>101.6030323815013</v>
       </c>
       <c r="D467">
-        <v>0.1884205190427792</v>
+        <v>0.2039828411500508</v>
       </c>
       <c r="E467" t="s">
         <v>77</v>
@@ -8561,13 +8561,13 @@
         <v>71</v>
       </c>
       <c r="B468">
-        <v>97.85907992658819</v>
+        <v>97.87404105033229</v>
       </c>
       <c r="C468">
         <v>97.6779384052974</v>
       </c>
       <c r="D468">
-        <v>0.1811415212907974</v>
+        <v>0.1961026450348982</v>
       </c>
       <c r="E468" t="s">
         <v>78</v>
@@ -8578,13 +8578,13 @@
         <v>71</v>
       </c>
       <c r="B469">
-        <v>97.06989552030528</v>
+        <v>97.08473599008892</v>
       </c>
       <c r="C469">
         <v>96.89021481454672</v>
       </c>
       <c r="D469">
-        <v>0.1796807057585568</v>
+        <v>0.1945211755421923</v>
       </c>
       <c r="E469" t="s">
         <v>79</v>
@@ -8595,13 +8595,13 @@
         <v>71</v>
       </c>
       <c r="B470">
-        <v>103.1930160416674</v>
+        <v>103.2087926408719</v>
       </c>
       <c r="C470">
         <v>103.0020011667432</v>
       </c>
       <c r="D470">
-        <v>0.1910148749242211</v>
+        <v>0.2067914741287211</v>
       </c>
       <c r="E470" t="s">
         <v>80</v>
@@ -8612,13 +8612,13 @@
         <v>72</v>
       </c>
       <c r="B471">
-        <v>97.55832784528229</v>
+        <v>97.58465595669971</v>
       </c>
       <c r="C471">
         <v>97.2398125684642</v>
       </c>
       <c r="D471">
-        <v>0.3185152768180899</v>
+        <v>0.3448433882355033</v>
       </c>
       <c r="E471" t="s">
         <v>74</v>
@@ -8629,13 +8629,13 @@
         <v>72</v>
       </c>
       <c r="B472">
-        <v>91.59570684095206</v>
+        <v>91.62040066811299</v>
       </c>
       <c r="C472">
         <v>91.2969627221531</v>
       </c>
       <c r="D472">
-        <v>0.2987441187989646</v>
+        <v>0.3234379459598955</v>
       </c>
       <c r="E472" t="s">
         <v>75</v>
@@ -8646,13 +8646,13 @@
         <v>72</v>
       </c>
       <c r="B473">
-        <v>103.9169428415191</v>
+        <v>103.9450144809543</v>
       </c>
       <c r="C473">
         <v>103.5773348108763</v>
       </c>
       <c r="D473">
-        <v>0.3396080306427507</v>
+        <v>0.3676796700780187</v>
       </c>
       <c r="E473" t="s">
         <v>76</v>
@@ -8663,13 +8663,13 @@
         <v>72</v>
       </c>
       <c r="B474">
-        <v>99.70403711756964</v>
+        <v>99.73094885655439</v>
       </c>
       <c r="C474">
         <v>99.37846121352756</v>
       </c>
       <c r="D474">
-        <v>0.3255759040420827</v>
+        <v>0.3524876430268336</v>
       </c>
       <c r="E474" t="s">
         <v>77</v>
@@ -8680,13 +8680,13 @@
         <v>72</v>
       </c>
       <c r="B475">
-        <v>94.30812927252407</v>
+        <v>94.33357092496581</v>
       </c>
       <c r="C475">
         <v>94.00033819967503</v>
       </c>
       <c r="D475">
-        <v>0.3077910728490423</v>
+        <v>0.3332327252907845</v>
       </c>
       <c r="E475" t="s">
         <v>78</v>
@@ -8697,13 +8697,13 @@
         <v>72</v>
       </c>
       <c r="B476">
-        <v>92.53621854158642</v>
+        <v>92.56117405321736</v>
       </c>
       <c r="C476">
         <v>92.23430867225342</v>
       </c>
       <c r="D476">
-        <v>0.3019098693330022</v>
+        <v>0.3268653809639375</v>
       </c>
       <c r="E476" t="s">
         <v>79</v>
@@ -8714,13 +8714,13 @@
         <v>72</v>
       </c>
       <c r="B477">
-        <v>102.8566289652959</v>
+        <v>102.8844056737828</v>
       </c>
       <c r="C477">
         <v>102.5205888882608</v>
       </c>
       <c r="D477">
-        <v>0.3360400770350793</v>
+        <v>0.3638167855219336</v>
       </c>
       <c r="E477" t="s">
         <v>80</v>
@@ -8731,13 +8731,13 @@
         <v>73</v>
       </c>
       <c r="B478">
-        <v>100.5373645457409</v>
+        <v>100.551577132967</v>
       </c>
       <c r="C478">
         <v>100.365272919348</v>
       </c>
       <c r="D478">
-        <v>0.17209162639287</v>
+        <v>0.1863042136189819</v>
       </c>
       <c r="E478" t="s">
         <v>74</v>
@@ -8748,13 +8748,13 @@
         <v>73</v>
       </c>
       <c r="B479">
-        <v>97.88464748469518</v>
+        <v>97.89848506733672</v>
       </c>
       <c r="C479">
         <v>97.71709656210388</v>
       </c>
       <c r="D479">
-        <v>0.1675509225913032</v>
+        <v>0.1813885052328459</v>
       </c>
       <c r="E479" t="s">
         <v>75</v>
@@ -8765,13 +8765,13 @@
         <v>73</v>
       </c>
       <c r="B480">
-        <v>103.2619714075551</v>
+        <v>103.276569162155</v>
       </c>
       <c r="C480">
         <v>103.0852160222876</v>
       </c>
       <c r="D480">
-        <v>0.1767553852674695</v>
+        <v>0.1913531398674309</v>
       </c>
       <c r="E480" t="s">
         <v>76</v>
@@ -8782,13 +8782,13 @@
         <v>73</v>
       </c>
       <c r="B481">
-        <v>102.1512000324655</v>
+        <v>102.1656407615145</v>
       </c>
       <c r="C481">
         <v>101.9763459746632</v>
       </c>
       <c r="D481">
-        <v>0.1748540578023494</v>
+        <v>0.1892947868513488</v>
       </c>
       <c r="E481" t="s">
         <v>77</v>
@@ -8799,13 +8799,13 @@
         <v>73</v>
       </c>
       <c r="B482">
-        <v>98.44833448604454</v>
+        <v>98.46225175498691</v>
       </c>
       <c r="C482">
         <v>98.27981869021158</v>
       </c>
       <c r="D482">
-        <v>0.1685157958329597</v>
+        <v>0.1824330647753243</v>
       </c>
       <c r="E482" t="s">
         <v>78</v>
@@ -8816,13 +8816,13 @@
         <v>73</v>
       </c>
       <c r="B483">
-        <v>97.73084702326901</v>
+        <v>97.74466286372069</v>
       </c>
       <c r="C483">
         <v>97.56355936371102</v>
       </c>
       <c r="D483">
-        <v>0.1672876595579851</v>
+        <v>0.1811035000096695</v>
       </c>
       <c r="E483" t="s">
         <v>79</v>
@@ -8833,13 +8833,13 @@
         <v>73</v>
       </c>
       <c r="B484">
-        <v>103.4244762802129</v>
+        <v>103.4390970075125</v>
       </c>
       <c r="C484">
         <v>103.2474427324138</v>
       </c>
       <c r="D484">
-        <v>0.1770335477990557</v>
+        <v>0.1916542750986423</v>
       </c>
       <c r="E484" t="s">
         <v>80</v>
